--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R7" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B8" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>126022313</v>
       </c>
       <c r="B24" t="n">
-        <v>91698</v>
+        <v>91701</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022312</v>
+        <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R26" t="n">
-        <v>6798594</v>
+        <v>6798570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B7" t="n">
-        <v>79586</v>
+        <v>78727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R7" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B8" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R8" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022304</v>
       </c>
       <c r="B2" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022297</v>
       </c>
       <c r="B3" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022294</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022293</v>
       </c>
       <c r="B5" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022306</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B7" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R7" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B8" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,7 +1463,7 @@
         <v>126022290</v>
       </c>
       <c r="B10" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126022291</v>
       </c>
       <c r="B11" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>126022301</v>
       </c>
       <c r="B12" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>126022316</v>
       </c>
       <c r="B13" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022310</v>
+        <v>126022322</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426877</v>
+        <v>426961</v>
       </c>
       <c r="R14" t="n">
-        <v>6798560</v>
+        <v>6798659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022322</v>
+        <v>126022310</v>
       </c>
       <c r="B15" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426961</v>
+        <v>426877</v>
       </c>
       <c r="R15" t="n">
-        <v>6798659</v>
+        <v>6798560</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2045,7 @@
         <v>126022321</v>
       </c>
       <c r="B16" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>126022284</v>
       </c>
       <c r="B17" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>126022289</v>
       </c>
       <c r="B18" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>126022315</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126022285</v>
       </c>
       <c r="B23" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126022313</v>
       </c>
       <c r="B24" t="n">
-        <v>91701</v>
+        <v>91705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126022318</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>126022296</v>
       </c>
       <c r="B28" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>126022288</v>
       </c>
       <c r="B29" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>126022317</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B19" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R19" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R20" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022301</v>
+        <v>126022316</v>
       </c>
       <c r="B12" t="n">
-        <v>91182</v>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
         <v>427033</v>
       </c>
       <c r="R12" t="n">
-        <v>6798637</v>
+        <v>6798630</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126022316</v>
+        <v>126022301</v>
       </c>
       <c r="B13" t="n">
-        <v>78730</v>
+        <v>91182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>427033</v>
       </c>
       <c r="R13" t="n">
-        <v>6798630</v>
+        <v>6798637</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R19" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R20" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R26" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022312</v>
+        <v>126022296</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798594</v>
+        <v>6798596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022296</v>
+        <v>126022292</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>79590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R28" t="n">
-        <v>6798596</v>
+        <v>6798570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022312</v>
+        <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R26" t="n">
-        <v>6798594</v>
+        <v>6798570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022296</v>
+        <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>78731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798596</v>
+        <v>6798594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022292</v>
+        <v>126022296</v>
       </c>
       <c r="B28" t="n">
-        <v>79590</v>
+        <v>79561</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R28" t="n">
-        <v>6798570</v>
+        <v>6798596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022304</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022297</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022294</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022293</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022306</v>
       </c>
       <c r="B6" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B7" t="n">
-        <v>79590</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R7" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B8" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R8" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>126022299</v>
       </c>
       <c r="B9" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>126022290</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126022291</v>
       </c>
       <c r="B11" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022316</v>
+        <v>126022301</v>
       </c>
       <c r="B12" t="n">
-        <v>78730</v>
+        <v>91184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
         <v>427033</v>
       </c>
       <c r="R12" t="n">
-        <v>6798630</v>
+        <v>6798637</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126022301</v>
+        <v>126022316</v>
       </c>
       <c r="B13" t="n">
-        <v>91182</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>427033</v>
       </c>
       <c r="R13" t="n">
-        <v>6798637</v>
+        <v>6798630</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>126022322</v>
       </c>
       <c r="B14" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>126022310</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>126022321</v>
       </c>
       <c r="B16" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>126022284</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>126022289</v>
       </c>
       <c r="B18" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B19" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R19" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B20" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R20" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>126022315</v>
       </c>
       <c r="B21" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126022298</v>
       </c>
       <c r="B22" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126022285</v>
       </c>
       <c r="B23" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126022313</v>
       </c>
       <c r="B24" t="n">
-        <v>91705</v>
+        <v>91707</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126022318</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>126022296</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>126022288</v>
       </c>
       <c r="B29" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>126022317</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B7" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R7" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B8" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>126022301</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
+        <v>91186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R19" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R20" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
         <v>126022313</v>
       </c>
       <c r="B24" t="n">
-        <v>91707</v>
+        <v>91709</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>126022301</v>
       </c>
       <c r="B12" t="n">
-        <v>91186</v>
+        <v>91188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126022313</v>
       </c>
       <c r="B24" t="n">
-        <v>91709</v>
+        <v>91711</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022312</v>
+        <v>126022296</v>
       </c>
       <c r="B27" t="n">
-        <v>78732</v>
+        <v>79562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798594</v>
+        <v>6798596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022296</v>
+        <v>126022312</v>
       </c>
       <c r="B28" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
         <v>426982</v>
       </c>
       <c r="R28" t="n">
-        <v>6798596</v>
+        <v>6798594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B7" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R7" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R8" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5072,52 +5072,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126340047</v>
+        <v>126337209</v>
       </c>
       <c r="B46" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427588</v>
+        <v>427026</v>
       </c>
       <c r="R46" t="n">
-        <v>6798380</v>
+        <v>6798692</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5146,7 +5142,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5156,12 +5152,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5170,67 +5161,70 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126337209</v>
+        <v>126340047</v>
       </c>
       <c r="B47" t="n">
-        <v>79595</v>
+        <v>98266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427026</v>
+        <v>427588</v>
       </c>
       <c r="R47" t="n">
-        <v>6798692</v>
+        <v>6798380</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5259,7 +5253,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5269,7 +5263,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5278,18 +5277,19 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126336092</v>
+        <v>126339028</v>
       </c>
       <c r="B50" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,37 +5521,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427026</v>
+        <v>427113</v>
       </c>
       <c r="R50" t="n">
-        <v>6798692</v>
+        <v>6798674</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,22 +5605,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126335481</v>
+        <v>126340584</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>78735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5628,39 +5628,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427042</v>
+        <v>427242</v>
       </c>
       <c r="R51" t="n">
-        <v>6798684</v>
+        <v>6798350</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5690,9 +5685,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5707,22 +5712,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126339028</v>
+        <v>126339364</v>
       </c>
       <c r="B52" t="n">
-        <v>78736</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,37 +5735,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427113</v>
+        <v>427073</v>
       </c>
       <c r="R52" t="n">
-        <v>6798674</v>
+        <v>6798822</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5787,19 +5797,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5814,19 +5814,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126340584</v>
+        <v>126336092</v>
       </c>
       <c r="B53" t="n">
         <v>78735</v>
@@ -5861,13 +5861,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427242</v>
+        <v>427026</v>
       </c>
       <c r="R53" t="n">
-        <v>6798350</v>
+        <v>6798692</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5921,22 +5921,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126339364</v>
+        <v>126335481</v>
       </c>
       <c r="B54" t="n">
-        <v>57653</v>
+        <v>57656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,16 +5944,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5964,19 +5964,19 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427073</v>
+        <v>427042</v>
       </c>
       <c r="R54" t="n">
-        <v>6798822</v>
+        <v>6798684</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,12 +6023,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6570,45 +6570,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126335973</v>
+        <v>126337677</v>
       </c>
       <c r="B60" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427023</v>
+        <v>427092</v>
       </c>
       <c r="R60" t="n">
-        <v>6798681</v>
+        <v>6798859</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6638,19 +6638,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6665,22 +6655,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126334876</v>
+        <v>126340359</v>
       </c>
       <c r="B61" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6688,37 +6678,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427084</v>
+        <v>427116</v>
       </c>
       <c r="R61" t="n">
-        <v>6798578</v>
+        <v>6798627</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6747,7 +6737,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6757,7 +6747,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6772,22 +6762,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126335831</v>
+        <v>126335973</v>
       </c>
       <c r="B62" t="n">
-        <v>8447</v>
+        <v>98266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6795,21 +6785,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6819,10 +6809,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427005</v>
+        <v>427023</v>
       </c>
       <c r="R62" t="n">
-        <v>6798710</v>
+        <v>6798681</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6854,7 +6844,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6864,12 +6854,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Gnagspår i tallåga</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6884,22 +6869,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126337677</v>
+        <v>126334331</v>
       </c>
       <c r="B63" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6907,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6931,13 +6916,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427092</v>
+        <v>427079</v>
       </c>
       <c r="R63" t="n">
-        <v>6798859</v>
+        <v>6798569</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6964,9 +6949,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6981,60 +6976,64 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126339304</v>
+        <v>126335072</v>
       </c>
       <c r="B64" t="n">
-        <v>79595</v>
+        <v>98266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427299</v>
+        <v>427079</v>
       </c>
       <c r="R64" t="n">
-        <v>6798540</v>
+        <v>6798569</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7063,7 +7062,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7073,7 +7072,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7088,22 +7087,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126340359</v>
+        <v>126337872</v>
       </c>
       <c r="B65" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7111,37 +7110,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427116</v>
+        <v>427103</v>
       </c>
       <c r="R65" t="n">
-        <v>6798627</v>
+        <v>6798836</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7168,19 +7167,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7195,22 +7184,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126334331</v>
+        <v>126334876</v>
       </c>
       <c r="B66" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7218,34 +7207,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427079</v>
+        <v>427084</v>
       </c>
       <c r="R66" t="n">
-        <v>6798569</v>
+        <v>6798578</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7277,7 +7266,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7287,7 +7276,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7302,22 +7291,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126335072</v>
+        <v>126335831</v>
       </c>
       <c r="B67" t="n">
-        <v>98266</v>
+        <v>8447</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7325,41 +7314,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427079</v>
+        <v>427005</v>
       </c>
       <c r="R67" t="n">
-        <v>6798569</v>
+        <v>6798710</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7388,7 +7373,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7398,7 +7383,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7413,22 +7403,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126337872</v>
+        <v>126339304</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7436,37 +7426,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427103</v>
+        <v>427299</v>
       </c>
       <c r="R68" t="n">
-        <v>6798836</v>
+        <v>6798540</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7493,9 +7483,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,22 +7510,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126340365</v>
+        <v>126338801</v>
       </c>
       <c r="B69" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,21 +7533,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7557,10 +7557,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427116</v>
+        <v>426933</v>
       </c>
       <c r="R69" t="n">
-        <v>6798627</v>
+        <v>6798926</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7629,10 +7629,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126339773</v>
+        <v>126339757</v>
       </c>
       <c r="B70" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7640,34 +7640,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426959</v>
+        <v>426981</v>
       </c>
       <c r="R70" t="n">
-        <v>6798956</v>
+        <v>6798995</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7724,22 +7724,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126339757</v>
+        <v>126339529</v>
       </c>
       <c r="B71" t="n">
-        <v>78735</v>
+        <v>79072</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7747,37 +7747,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426981</v>
+        <v>427360</v>
       </c>
       <c r="R71" t="n">
-        <v>6798995</v>
+        <v>6798574</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7804,19 +7804,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7831,60 +7821,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126339529</v>
+        <v>126336097</v>
       </c>
       <c r="B72" t="n">
-        <v>79072</v>
+        <v>98266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>967</v>
+        <v>219790</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427360</v>
+        <v>427038</v>
       </c>
       <c r="R72" t="n">
-        <v>6798574</v>
+        <v>6798675</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7911,9 +7901,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7928,44 +7928,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126336097</v>
+        <v>126336082</v>
       </c>
       <c r="B73" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7975,13 +7975,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427038</v>
+        <v>426993</v>
       </c>
       <c r="R73" t="n">
-        <v>6798675</v>
+        <v>6798667</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8035,22 +8035,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126338801</v>
+        <v>126335972</v>
       </c>
       <c r="B74" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,34 +8058,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426933</v>
+        <v>426988</v>
       </c>
       <c r="R74" t="n">
-        <v>6798926</v>
+        <v>6798730</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,12 +8142,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8261,7 +8261,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126336082</v>
+        <v>126340365</v>
       </c>
       <c r="B76" t="n">
         <v>79595</v>
@@ -8292,17 +8292,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426993</v>
+        <v>427116</v>
       </c>
       <c r="R76" t="n">
-        <v>6798667</v>
+        <v>6798627</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8356,19 +8356,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126335972</v>
+        <v>126339773</v>
       </c>
       <c r="B77" t="n">
         <v>79595</v>
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426988</v>
+        <v>426959</v>
       </c>
       <c r="R77" t="n">
-        <v>6798730</v>
+        <v>6798956</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8475,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126339121</v>
+        <v>126337563</v>
       </c>
       <c r="B78" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,34 +8486,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427243</v>
+        <v>427101</v>
       </c>
       <c r="R78" t="n">
-        <v>6798666</v>
+        <v>6798845</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,19 +8543,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8570,19 +8560,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126337563</v>
+        <v>126335508</v>
       </c>
       <c r="B79" t="n">
         <v>78736</v>
@@ -8611,19 +8601,22 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427101</v>
+        <v>427079</v>
       </c>
       <c r="R79" t="n">
-        <v>6798845</v>
+        <v>6798512</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8650,39 +8643,55 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126335508</v>
+        <v>126336234</v>
       </c>
       <c r="B80" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8690,37 +8699,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427079</v>
+        <v>427008</v>
       </c>
       <c r="R80" t="n">
-        <v>6798512</v>
+        <v>6798762</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -8750,55 +8756,39 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126336234</v>
+        <v>126337970</v>
       </c>
       <c r="B81" t="n">
-        <v>78735</v>
+        <v>57653</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8806,37 +8796,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427008</v>
+        <v>427138</v>
       </c>
       <c r="R81" t="n">
-        <v>6798762</v>
+        <v>6798830</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8863,9 +8858,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8880,22 +8885,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126337970</v>
+        <v>126337748</v>
       </c>
       <c r="B82" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8903,39 +8908,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427138</v>
+        <v>427082</v>
       </c>
       <c r="R82" t="n">
-        <v>6798830</v>
+        <v>6798910</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8992,19 +8992,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126337748</v>
+        <v>126339121</v>
       </c>
       <c r="B83" t="n">
         <v>79595</v>
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427082</v>
+        <v>427243</v>
       </c>
       <c r="R83" t="n">
-        <v>6798910</v>
+        <v>6798666</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9539,7 +9539,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126335672</v>
+        <v>126340385</v>
       </c>
       <c r="B88" t="n">
         <v>78977</v>
@@ -9570,14 +9570,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427042</v>
+        <v>427538</v>
       </c>
       <c r="R88" t="n">
-        <v>6798684</v>
+        <v>6798367</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9607,9 +9607,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9624,57 +9634,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126334959</v>
+        <v>126335672</v>
       </c>
       <c r="B89" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427059</v>
+        <v>427042</v>
       </c>
       <c r="R89" t="n">
-        <v>6798635</v>
+        <v>6798684</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9704,24 +9714,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ett ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9736,44 +9731,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126340385</v>
+        <v>126334959</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>98370</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9783,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427538</v>
+        <v>427059</v>
       </c>
       <c r="R90" t="n">
-        <v>6798367</v>
+        <v>6798635</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9818,7 +9813,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9828,7 +9823,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ett ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9843,12 +9843,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10360,10 +10360,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126338455</v>
+        <v>126337979</v>
       </c>
       <c r="B96" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10371,34 +10371,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427173</v>
+        <v>427138</v>
       </c>
       <c r="R96" t="n">
-        <v>6798821</v>
+        <v>6798830</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10455,22 +10455,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126339416</v>
+        <v>126338455</v>
       </c>
       <c r="B97" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10478,34 +10478,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427360</v>
+        <v>427173</v>
       </c>
       <c r="R97" t="n">
-        <v>6798573</v>
+        <v>6798821</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10537,7 +10537,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10562,22 +10562,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126336279</v>
+        <v>126339416</v>
       </c>
       <c r="B98" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10585,37 +10585,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427018</v>
+        <v>427360</v>
       </c>
       <c r="R98" t="n">
-        <v>6798762</v>
+        <v>6798573</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10642,9 +10642,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10659,19 +10669,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126337979</v>
+        <v>126336279</v>
       </c>
       <c r="B99" t="n">
         <v>78736</v>
@@ -10702,17 +10712,17 @@
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427138</v>
+        <v>427018</v>
       </c>
       <c r="R99" t="n">
-        <v>6798830</v>
+        <v>6798762</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10739,19 +10749,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10766,19 +10766,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126336252</v>
+        <v>126338799</v>
       </c>
       <c r="B100" t="n">
         <v>79595</v>
@@ -10809,17 +10809,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427008</v>
+        <v>426933</v>
       </c>
       <c r="R100" t="n">
-        <v>6798762</v>
+        <v>6798926</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10846,9 +10846,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10863,22 +10873,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126335762</v>
+        <v>126337016</v>
       </c>
       <c r="B101" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10886,21 +10896,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10910,13 +10920,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426996</v>
+        <v>427012</v>
       </c>
       <c r="R101" t="n">
-        <v>6798633</v>
+        <v>6798760</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10945,7 +10955,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10955,7 +10965,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10970,19 +10980,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126334576</v>
+        <v>126337254</v>
       </c>
       <c r="B102" t="n">
         <v>79595</v>
@@ -11013,17 +11023,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427115</v>
+        <v>427057</v>
       </c>
       <c r="R102" t="n">
-        <v>6798555</v>
+        <v>6798827</v>
       </c>
       <c r="S102" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11052,7 +11062,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11062,7 +11072,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11077,19 +11087,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126337810</v>
+        <v>126334576</v>
       </c>
       <c r="B103" t="n">
         <v>79595</v>
@@ -11120,17 +11130,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427108</v>
+        <v>427115</v>
       </c>
       <c r="R103" t="n">
-        <v>6798841</v>
+        <v>6798555</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11157,9 +11167,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11174,19 +11194,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126338799</v>
+        <v>126335762</v>
       </c>
       <c r="B104" t="n">
         <v>79595</v>
@@ -11217,17 +11237,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426933</v>
+        <v>426996</v>
       </c>
       <c r="R104" t="n">
-        <v>6798926</v>
+        <v>6798633</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11256,7 +11276,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11266,7 +11286,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11281,22 +11301,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126337016</v>
+        <v>126337810</v>
       </c>
       <c r="B105" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11304,34 +11324,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427012</v>
+        <v>427108</v>
       </c>
       <c r="R105" t="n">
-        <v>6798760</v>
+        <v>6798841</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11361,19 +11381,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11388,19 +11398,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126337254</v>
+        <v>126336252</v>
       </c>
       <c r="B106" t="n">
         <v>79595</v>
@@ -11431,17 +11441,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427057</v>
+        <v>427008</v>
       </c>
       <c r="R106" t="n">
-        <v>6798827</v>
+        <v>6798762</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11468,19 +11478,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11495,57 +11495,61 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126339015</v>
+        <v>126334915</v>
       </c>
       <c r="B107" t="n">
-        <v>79566</v>
+        <v>98266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>426894</v>
+        <v>427060</v>
       </c>
       <c r="R107" t="n">
-        <v>6798935</v>
+        <v>6798614</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11577,7 +11581,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11587,7 +11591,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11596,67 +11605,64 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126334915</v>
+        <v>126335795</v>
       </c>
       <c r="B108" t="n">
-        <v>98266</v>
+        <v>78736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427060</v>
+        <v>426989</v>
       </c>
       <c r="R108" t="n">
-        <v>6798614</v>
+        <v>6798666</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11688,7 +11694,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11698,12 +11704,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11712,7 +11713,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11731,10 +11731,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126335795</v>
+        <v>126337975</v>
       </c>
       <c r="B109" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11742,34 +11742,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426989</v>
+        <v>427138</v>
       </c>
       <c r="R109" t="n">
-        <v>6798666</v>
+        <v>6798830</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11801,7 +11801,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11826,22 +11826,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126337975</v>
+        <v>126339015</v>
       </c>
       <c r="B110" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11849,21 +11849,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11873,10 +11873,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427138</v>
+        <v>426894</v>
       </c>
       <c r="R110" t="n">
-        <v>6798830</v>
+        <v>6798935</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126334241</v>
+        <v>126336022</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>98266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12812,34 +12812,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427095</v>
+        <v>427026</v>
       </c>
       <c r="R119" t="n">
-        <v>6798448</v>
+        <v>6798688</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12869,14 +12869,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12891,22 +12896,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126334762</v>
+        <v>126334554</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12914,21 +12919,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12938,10 +12943,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426962</v>
+        <v>427075</v>
       </c>
       <c r="R120" t="n">
-        <v>6798805</v>
+        <v>6798591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12973,7 +12978,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12983,12 +12988,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13003,57 +13003,60 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126336022</v>
+        <v>126335754</v>
       </c>
       <c r="B121" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427026</v>
+        <v>426984</v>
       </c>
       <c r="R121" t="n">
-        <v>6798688</v>
+        <v>6798652</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13085,7 +13088,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13095,7 +13098,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13104,6 +13107,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13122,45 +13126,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126334554</v>
+        <v>126334241</v>
       </c>
       <c r="B122" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427075</v>
+        <v>427095</v>
       </c>
       <c r="R122" t="n">
-        <v>6798591</v>
+        <v>6798448</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13190,19 +13194,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13217,22 +13216,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126335754</v>
+        <v>126334762</v>
       </c>
       <c r="B123" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13240,37 +13239,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426984</v>
+        <v>426962</v>
       </c>
       <c r="R123" t="n">
-        <v>6798652</v>
+        <v>6798805</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13302,7 +13298,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13312,7 +13308,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13321,19 +13322,18 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -13845,10 +13845,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126335852</v>
+        <v>126337688</v>
       </c>
       <c r="B129" t="n">
-        <v>57816</v>
+        <v>78735</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13856,42 +13856,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427053</v>
+        <v>427092</v>
       </c>
       <c r="R129" t="n">
-        <v>6798729</v>
+        <v>6798859</v>
       </c>
       <c r="S129" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13947,7 +13942,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126334548</v>
+        <v>126335594</v>
       </c>
       <c r="B130" t="n">
         <v>79595</v>
@@ -13978,14 +13973,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426962</v>
+        <v>427042</v>
       </c>
       <c r="R130" t="n">
-        <v>6798805</v>
+        <v>6798684</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14015,19 +14010,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14042,22 +14027,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126337688</v>
+        <v>126335567</v>
       </c>
       <c r="B131" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14065,34 +14050,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427092</v>
+        <v>427022</v>
       </c>
       <c r="R131" t="n">
-        <v>6798859</v>
+        <v>6798674</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14122,9 +14107,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14139,22 +14134,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126335594</v>
+        <v>126335852</v>
       </c>
       <c r="B132" t="n">
-        <v>79595</v>
+        <v>57816</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14162,37 +14157,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427042</v>
+        <v>427053</v>
       </c>
       <c r="R132" t="n">
-        <v>6798684</v>
+        <v>6798729</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14248,10 +14248,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126335567</v>
+        <v>126334548</v>
       </c>
       <c r="B133" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14259,21 +14259,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14283,10 +14283,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427022</v>
+        <v>426962</v>
       </c>
       <c r="R133" t="n">
-        <v>6798674</v>
+        <v>6798805</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14343,22 +14343,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126335603</v>
+        <v>126335337</v>
       </c>
       <c r="B134" t="n">
-        <v>79566</v>
+        <v>58135</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14366,37 +14366,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>229821</v>
+        <v>103018</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427042</v>
+        <v>427023</v>
       </c>
       <c r="R134" t="n">
-        <v>6798684</v>
+        <v>6798652</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14452,10 +14457,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126337227</v>
+        <v>126335603</v>
       </c>
       <c r="B135" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14463,21 +14468,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14487,10 +14492,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427067</v>
+        <v>427042</v>
       </c>
       <c r="R135" t="n">
-        <v>6798806</v>
+        <v>6798684</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14549,10 +14554,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126339616</v>
+        <v>126337227</v>
       </c>
       <c r="B136" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14560,34 +14565,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427329</v>
+        <v>427067</v>
       </c>
       <c r="R136" t="n">
-        <v>6798435</v>
+        <v>6798806</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14617,19 +14622,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14644,22 +14639,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126340434</v>
+        <v>126339616</v>
       </c>
       <c r="B137" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14667,21 +14662,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14691,10 +14686,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427486</v>
+        <v>427329</v>
       </c>
       <c r="R137" t="n">
-        <v>6798404</v>
+        <v>6798435</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14726,7 +14721,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14736,7 +14731,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14763,7 +14758,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126334764</v>
+        <v>126340434</v>
       </c>
       <c r="B138" t="n">
         <v>78977</v>
@@ -14798,10 +14793,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427055</v>
+        <v>427486</v>
       </c>
       <c r="R138" t="n">
-        <v>6798616</v>
+        <v>6798404</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14833,7 +14828,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -14843,7 +14838,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14870,10 +14865,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126335337</v>
+        <v>126334764</v>
       </c>
       <c r="B139" t="n">
-        <v>58135</v>
+        <v>78977</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14881,42 +14876,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427023</v>
+        <v>427055</v>
       </c>
       <c r="R139" t="n">
-        <v>6798652</v>
+        <v>6798616</v>
       </c>
       <c r="S139" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14943,9 +14933,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14960,15 +14960,443 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>126364364</v>
+      </c>
+      <c r="B140" t="n">
+        <v>75072</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>426970</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6798728</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>126366166</v>
+      </c>
+      <c r="B141" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>426970</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6798728</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>126364681</v>
+      </c>
+      <c r="B142" t="n">
+        <v>80109</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>426970</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6798728</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>126365118</v>
+      </c>
+      <c r="B143" t="n">
+        <v>96605</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>53</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>426970</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6798728</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R7" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022301</v>
+        <v>126022316</v>
       </c>
       <c r="B12" t="n">
-        <v>91192</v>
+        <v>78735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
         <v>427033</v>
       </c>
       <c r="R12" t="n">
-        <v>6798637</v>
+        <v>6798630</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126022316</v>
+        <v>126022301</v>
       </c>
       <c r="B13" t="n">
-        <v>78735</v>
+        <v>91192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>427033</v>
       </c>
       <c r="R13" t="n">
-        <v>6798630</v>
+        <v>6798637</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R19" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R20" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B26" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R26" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022312</v>
+        <v>126022296</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798594</v>
+        <v>6798596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022296</v>
+        <v>126022292</v>
       </c>
       <c r="B28" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R28" t="n">
-        <v>6798596</v>
+        <v>6798570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126340383</v>
+        <v>126340016</v>
       </c>
       <c r="B31" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,34 +3508,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427116</v>
+        <v>427570</v>
       </c>
       <c r="R31" t="n">
-        <v>6798627</v>
+        <v>6798393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,22 +3592,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126340016</v>
+        <v>126340383</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3615,34 +3615,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427570</v>
+        <v>427116</v>
       </c>
       <c r="R32" t="n">
-        <v>6798393</v>
+        <v>6798627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3699,12 +3699,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126339444</v>
+        <v>126334889</v>
       </c>
       <c r="B34" t="n">
         <v>79595</v>
@@ -3849,17 +3849,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>426858</v>
+        <v>427084</v>
       </c>
       <c r="R34" t="n">
-        <v>6799009</v>
+        <v>6798578</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3913,19 +3913,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126334889</v>
+        <v>126339444</v>
       </c>
       <c r="B35" t="n">
         <v>79595</v>
@@ -3956,17 +3956,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427084</v>
+        <v>426858</v>
       </c>
       <c r="R35" t="n">
-        <v>6798578</v>
+        <v>6799009</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4020,22 +4020,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126335214</v>
+        <v>126340669</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,21 +4043,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4067,13 +4067,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427080</v>
+        <v>427162</v>
       </c>
       <c r="R36" t="n">
-        <v>6798606</v>
+        <v>6798406</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4127,22 +4127,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126338818</v>
+        <v>126335214</v>
       </c>
       <c r="B37" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4150,37 +4150,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427244</v>
+        <v>427080</v>
       </c>
       <c r="R37" t="n">
-        <v>6798791</v>
+        <v>6798606</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4207,9 +4207,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4224,19 +4234,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126340669</v>
+        <v>126338818</v>
       </c>
       <c r="B38" t="n">
         <v>78735</v>
@@ -4267,14 +4277,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427162</v>
+        <v>427244</v>
       </c>
       <c r="R38" t="n">
-        <v>6798406</v>
+        <v>6798791</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,19 +4314,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4331,57 +4331,57 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126338600</v>
+        <v>126339860</v>
       </c>
       <c r="B39" t="n">
-        <v>91503</v>
+        <v>79595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426972</v>
+        <v>427301</v>
       </c>
       <c r="R39" t="n">
-        <v>6798921</v>
+        <v>6798343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4438,22 +4438,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126337222</v>
+        <v>126334237</v>
       </c>
       <c r="B40" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,37 +4461,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427067</v>
+        <v>427084</v>
       </c>
       <c r="R40" t="n">
-        <v>6798806</v>
+        <v>6798524</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4518,9 +4518,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4535,22 +4545,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126339860</v>
+        <v>126336106</v>
       </c>
       <c r="B41" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4558,34 +4568,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427301</v>
+        <v>426970</v>
       </c>
       <c r="R41" t="n">
-        <v>6798343</v>
+        <v>6798728</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4617,7 +4627,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4627,7 +4637,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4642,22 +4652,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126336106</v>
+        <v>126337222</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,21 +4675,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4689,10 +4699,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>426970</v>
+        <v>427067</v>
       </c>
       <c r="R42" t="n">
-        <v>6798728</v>
+        <v>6798806</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,19 +4732,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4749,60 +4749,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126334237</v>
+        <v>126338600</v>
       </c>
       <c r="B43" t="n">
-        <v>79595</v>
+        <v>91503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427084</v>
+        <v>426972</v>
       </c>
       <c r="R43" t="n">
-        <v>6798524</v>
+        <v>6798921</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4856,12 +4856,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5179,49 +5179,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126340047</v>
+        <v>126334857</v>
       </c>
       <c r="B47" t="n">
-        <v>98266</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427588</v>
+        <v>427060</v>
       </c>
       <c r="R47" t="n">
-        <v>6798380</v>
+        <v>6798612</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5253,7 +5249,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5263,12 +5259,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5277,7 +5268,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5296,45 +5286,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126334857</v>
+        <v>126340047</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427060</v>
+        <v>427588</v>
       </c>
       <c r="R48" t="n">
-        <v>6798612</v>
+        <v>6798380</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5366,7 +5360,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5376,7 +5370,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5385,6 +5384,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126339028</v>
+        <v>126340584</v>
       </c>
       <c r="B50" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,37 +5521,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427113</v>
+        <v>427242</v>
       </c>
       <c r="R50" t="n">
-        <v>6798674</v>
+        <v>6798350</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,19 +5605,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126340584</v>
+        <v>126336092</v>
       </c>
       <c r="B51" t="n">
         <v>78735</v>
@@ -5652,13 +5652,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427242</v>
+        <v>427026</v>
       </c>
       <c r="R51" t="n">
-        <v>6798350</v>
+        <v>6798692</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5712,12 +5712,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126336092</v>
+        <v>126339028</v>
       </c>
       <c r="B53" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,37 +5837,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427026</v>
+        <v>427113</v>
       </c>
       <c r="R53" t="n">
-        <v>6798692</v>
+        <v>6798674</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6035,10 +6035,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126339407</v>
+        <v>126335625</v>
       </c>
       <c r="B55" t="n">
-        <v>78736</v>
+        <v>96605</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6046,37 +6046,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427359</v>
+        <v>427079</v>
       </c>
       <c r="R55" t="n">
-        <v>6798572</v>
+        <v>6798569</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6130,57 +6130,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126340128</v>
+        <v>126339407</v>
       </c>
       <c r="B56" t="n">
-        <v>98266</v>
+        <v>78736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427631</v>
+        <v>427359</v>
       </c>
       <c r="R56" t="n">
-        <v>6798401</v>
+        <v>6798572</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6237,12 +6237,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126335625</v>
+        <v>126338668</v>
       </c>
       <c r="B58" t="n">
-        <v>96602</v>
+        <v>78735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6391,13 +6391,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427079</v>
+        <v>426958</v>
       </c>
       <c r="R58" t="n">
-        <v>6798569</v>
+        <v>6798928</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6451,57 +6451,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126338668</v>
+        <v>126340128</v>
       </c>
       <c r="B59" t="n">
-        <v>78735</v>
+        <v>98269</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426958</v>
+        <v>427631</v>
       </c>
       <c r="R59" t="n">
-        <v>6798928</v>
+        <v>6798401</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6558,12 +6558,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6774,48 +6774,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126335973</v>
+        <v>126334331</v>
       </c>
       <c r="B62" t="n">
-        <v>98266</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427023</v>
+        <v>427079</v>
       </c>
       <c r="R62" t="n">
-        <v>6798681</v>
+        <v>6798569</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6869,22 +6869,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126334331</v>
+        <v>126339304</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,37 +6892,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427079</v>
+        <v>427299</v>
       </c>
       <c r="R63" t="n">
-        <v>6798569</v>
+        <v>6798540</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,22 +6976,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126335072</v>
+        <v>126335973</v>
       </c>
       <c r="B64" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7016,24 +7016,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427079</v>
+        <v>427023</v>
       </c>
       <c r="R64" t="n">
-        <v>6798569</v>
+        <v>6798681</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7062,7 +7058,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7072,7 +7068,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7087,57 +7083,61 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126337872</v>
+        <v>126335072</v>
       </c>
       <c r="B65" t="n">
-        <v>79566</v>
+        <v>98269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427103</v>
+        <v>427079</v>
       </c>
       <c r="R65" t="n">
-        <v>6798836</v>
+        <v>6798569</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7167,9 +7167,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7184,22 +7194,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126334876</v>
+        <v>126337872</v>
       </c>
       <c r="B66" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7207,34 +7217,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427084</v>
+        <v>427103</v>
       </c>
       <c r="R66" t="n">
-        <v>6798578</v>
+        <v>6798836</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7264,19 +7274,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7291,12 +7291,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7415,10 +7415,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126339304</v>
+        <v>126334876</v>
       </c>
       <c r="B68" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,21 +7426,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7450,13 +7450,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427299</v>
+        <v>427084</v>
       </c>
       <c r="R68" t="n">
-        <v>6798540</v>
+        <v>6798578</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,22 +7510,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126338801</v>
+        <v>126339529</v>
       </c>
       <c r="B69" t="n">
-        <v>78735</v>
+        <v>79072</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,37 +7533,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426933</v>
+        <v>427360</v>
       </c>
       <c r="R69" t="n">
-        <v>6798926</v>
+        <v>6798574</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7590,19 +7590,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7617,57 +7607,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126339757</v>
+        <v>126336097</v>
       </c>
       <c r="B70" t="n">
-        <v>78735</v>
+        <v>98269</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426981</v>
+        <v>427038</v>
       </c>
       <c r="R70" t="n">
-        <v>6798995</v>
+        <v>6798675</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7699,7 +7689,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7709,7 +7699,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7724,22 +7714,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126339529</v>
+        <v>126338801</v>
       </c>
       <c r="B71" t="n">
-        <v>79072</v>
+        <v>78735</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7747,37 +7737,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427360</v>
+        <v>426933</v>
       </c>
       <c r="R71" t="n">
-        <v>6798574</v>
+        <v>6798926</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7804,9 +7794,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7821,57 +7821,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126336097</v>
+        <v>126340365</v>
       </c>
       <c r="B72" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427038</v>
+        <v>427116</v>
       </c>
       <c r="R72" t="n">
-        <v>6798675</v>
+        <v>6798627</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7928,12 +7928,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8047,7 +8047,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126335972</v>
+        <v>126339773</v>
       </c>
       <c r="B74" t="n">
         <v>79595</v>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426988</v>
+        <v>426959</v>
       </c>
       <c r="R74" t="n">
-        <v>6798730</v>
+        <v>6798956</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126340365</v>
+        <v>126339757</v>
       </c>
       <c r="B76" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8272,21 +8272,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427116</v>
+        <v>426981</v>
       </c>
       <c r="R76" t="n">
-        <v>6798627</v>
+        <v>6798995</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126339773</v>
+        <v>126335972</v>
       </c>
       <c r="B77" t="n">
         <v>79595</v>
@@ -8403,10 +8403,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426959</v>
+        <v>426988</v>
       </c>
       <c r="R77" t="n">
-        <v>6798956</v>
+        <v>6798730</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8475,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126337563</v>
+        <v>126337748</v>
       </c>
       <c r="B78" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,34 +8486,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427101</v>
+        <v>427082</v>
       </c>
       <c r="R78" t="n">
-        <v>6798845</v>
+        <v>6798910</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8543,9 +8543,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8560,22 +8570,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126335508</v>
+        <v>126339121</v>
       </c>
       <c r="B79" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8583,40 +8593,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427079</v>
+        <v>427243</v>
       </c>
       <c r="R79" t="n">
-        <v>6798512</v>
+        <v>6798666</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8645,7 +8652,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8655,12 +8662,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8669,7 +8671,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8897,10 +8898,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126337748</v>
+        <v>126335508</v>
       </c>
       <c r="B82" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8908,37 +8909,40 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427082</v>
+        <v>427079</v>
       </c>
       <c r="R82" t="n">
-        <v>6798910</v>
+        <v>6798512</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8967,7 +8971,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8977,7 +8981,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8986,6 +8995,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9004,10 +9014,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126339121</v>
+        <v>126337563</v>
       </c>
       <c r="B83" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9015,34 +9025,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427243</v>
+        <v>427101</v>
       </c>
       <c r="R83" t="n">
-        <v>6798666</v>
+        <v>6798845</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9072,19 +9082,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9099,22 +9099,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126338355</v>
+        <v>126335672</v>
       </c>
       <c r="B84" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9122,34 +9122,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427171</v>
+        <v>427042</v>
       </c>
       <c r="R84" t="n">
-        <v>6798818</v>
+        <v>6798684</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9179,19 +9179,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9206,22 +9196,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126338430</v>
+        <v>126340385</v>
       </c>
       <c r="B85" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9229,34 +9219,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427157</v>
+        <v>427538</v>
       </c>
       <c r="R85" t="n">
-        <v>6798766</v>
+        <v>6798367</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9288,7 +9278,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9298,7 +9288,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9313,12 +9303,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9432,10 +9422,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126337274</v>
+        <v>126338355</v>
       </c>
       <c r="B87" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9443,34 +9433,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427056</v>
+        <v>427171</v>
       </c>
       <c r="R87" t="n">
-        <v>6798834</v>
+        <v>6798818</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9502,7 +9492,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9512,7 +9502,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9527,22 +9517,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126340385</v>
+        <v>126338430</v>
       </c>
       <c r="B88" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9550,34 +9540,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427538</v>
+        <v>427157</v>
       </c>
       <c r="R88" t="n">
-        <v>6798367</v>
+        <v>6798766</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9609,7 +9599,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9619,7 +9609,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9634,22 +9624,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126335672</v>
+        <v>126337274</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9657,34 +9647,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427042</v>
+        <v>427056</v>
       </c>
       <c r="R89" t="n">
-        <v>6798684</v>
+        <v>6798834</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9714,9 +9704,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9731,57 +9731,57 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126334959</v>
+        <v>126333986</v>
       </c>
       <c r="B90" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427059</v>
+        <v>427095</v>
       </c>
       <c r="R90" t="n">
-        <v>6798635</v>
+        <v>6798448</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9811,24 +9811,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ett ex</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9843,22 +9828,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126337681</v>
+        <v>126337982</v>
       </c>
       <c r="B91" t="n">
-        <v>79566</v>
+        <v>78735</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9866,21 +9851,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9890,10 +9875,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427092</v>
+        <v>427138</v>
       </c>
       <c r="R91" t="n">
-        <v>6798859</v>
+        <v>6798830</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9923,9 +9908,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9952,32 +9947,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126333986</v>
+        <v>126335099</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>98269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9987,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427095</v>
+        <v>427044</v>
       </c>
       <c r="R92" t="n">
-        <v>6798448</v>
+        <v>6798644</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10049,45 +10044,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126335099</v>
+        <v>126335896</v>
       </c>
       <c r="B93" t="n">
-        <v>98266</v>
+        <v>78736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427044</v>
+        <v>426993</v>
       </c>
       <c r="R93" t="n">
-        <v>6798644</v>
+        <v>6798667</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10117,9 +10112,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10134,22 +10139,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126335896</v>
+        <v>126337681</v>
       </c>
       <c r="B94" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10157,34 +10162,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426993</v>
+        <v>427092</v>
       </c>
       <c r="R94" t="n">
-        <v>6798667</v>
+        <v>6798859</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10214,19 +10219,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10241,22 +10236,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126337982</v>
+        <v>126336279</v>
       </c>
       <c r="B95" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10264,37 +10259,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427138</v>
+        <v>427018</v>
       </c>
       <c r="R95" t="n">
-        <v>6798830</v>
+        <v>6798762</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10321,19 +10316,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10348,12 +10333,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10681,10 +10666,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126336279</v>
+        <v>126334576</v>
       </c>
       <c r="B99" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10692,21 +10677,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10716,13 +10701,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427018</v>
+        <v>427115</v>
       </c>
       <c r="R99" t="n">
-        <v>6798762</v>
+        <v>6798555</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10749,9 +10734,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10766,22 +10761,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126338799</v>
+        <v>126337016</v>
       </c>
       <c r="B100" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10789,34 +10784,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>426933</v>
+        <v>427012</v>
       </c>
       <c r="R100" t="n">
-        <v>6798926</v>
+        <v>6798760</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10848,7 +10843,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10858,7 +10853,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10873,22 +10868,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126337016</v>
+        <v>126337810</v>
       </c>
       <c r="B101" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10896,34 +10891,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427012</v>
+        <v>427108</v>
       </c>
       <c r="R101" t="n">
-        <v>6798760</v>
+        <v>6798841</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10953,19 +10948,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10980,19 +10965,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126337254</v>
+        <v>126335762</v>
       </c>
       <c r="B102" t="n">
         <v>79595</v>
@@ -11023,17 +11008,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427057</v>
+        <v>426996</v>
       </c>
       <c r="R102" t="n">
-        <v>6798827</v>
+        <v>6798633</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11062,7 +11047,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11072,7 +11057,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11087,19 +11072,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126334576</v>
+        <v>126336252</v>
       </c>
       <c r="B103" t="n">
         <v>79595</v>
@@ -11134,13 +11119,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427115</v>
+        <v>427008</v>
       </c>
       <c r="R103" t="n">
-        <v>6798555</v>
+        <v>6798762</v>
       </c>
       <c r="S103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11167,19 +11152,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11194,19 +11169,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126335762</v>
+        <v>126338799</v>
       </c>
       <c r="B104" t="n">
         <v>79595</v>
@@ -11237,17 +11212,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426996</v>
+        <v>426933</v>
       </c>
       <c r="R104" t="n">
-        <v>6798633</v>
+        <v>6798926</v>
       </c>
       <c r="S104" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11276,7 +11251,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11286,7 +11261,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11301,19 +11276,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126337810</v>
+        <v>126337254</v>
       </c>
       <c r="B105" t="n">
         <v>79595</v>
@@ -11348,10 +11323,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427108</v>
+        <v>427057</v>
       </c>
       <c r="R105" t="n">
-        <v>6798841</v>
+        <v>6798827</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11381,9 +11356,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11398,22 +11383,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126336252</v>
+        <v>126339015</v>
       </c>
       <c r="B106" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11421,37 +11406,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427008</v>
+        <v>426894</v>
       </c>
       <c r="R106" t="n">
-        <v>6798762</v>
+        <v>6798935</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11478,9 +11463,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11495,61 +11490,57 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126334915</v>
+        <v>126337975</v>
       </c>
       <c r="B107" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427060</v>
+        <v>427138</v>
       </c>
       <c r="R107" t="n">
-        <v>6798614</v>
+        <v>6798830</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11581,7 +11572,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11591,12 +11582,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11605,64 +11591,67 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126335795</v>
+        <v>126334915</v>
       </c>
       <c r="B108" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426989</v>
+        <v>427060</v>
       </c>
       <c r="R108" t="n">
-        <v>6798666</v>
+        <v>6798614</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11694,7 +11683,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11704,7 +11693,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11713,6 +11707,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11731,10 +11726,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126337975</v>
+        <v>126335795</v>
       </c>
       <c r="B109" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11742,34 +11737,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427138</v>
+        <v>426989</v>
       </c>
       <c r="R109" t="n">
-        <v>6798830</v>
+        <v>6798666</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11801,7 +11796,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11811,7 +11806,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11826,22 +11821,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126339015</v>
+        <v>126337286</v>
       </c>
       <c r="B110" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11849,34 +11844,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>426894</v>
+        <v>427056</v>
       </c>
       <c r="R110" t="n">
-        <v>6798935</v>
+        <v>6798834</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11908,7 +11903,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11918,7 +11913,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11933,19 +11928,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126337286</v>
+        <v>126339588</v>
       </c>
       <c r="B111" t="n">
         <v>78736</v>
@@ -11976,14 +11971,14 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427056</v>
+        <v>427328</v>
       </c>
       <c r="R111" t="n">
-        <v>6798834</v>
+        <v>6798426</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12015,7 +12010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12025,7 +12020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12040,12 +12035,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12159,10 +12154,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126339588</v>
+        <v>126337559</v>
       </c>
       <c r="B113" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12170,21 +12165,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12194,10 +12189,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427328</v>
+        <v>427047</v>
       </c>
       <c r="R113" t="n">
-        <v>6798426</v>
+        <v>6798896</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12229,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12239,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12266,45 +12261,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126337559</v>
+        <v>126334241</v>
       </c>
       <c r="B114" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427047</v>
+        <v>427095</v>
       </c>
       <c r="R114" t="n">
-        <v>6798896</v>
+        <v>6798448</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12334,19 +12329,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>13:30</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12361,22 +12351,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126338320</v>
+        <v>126338943</v>
       </c>
       <c r="B115" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12384,37 +12374,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427072</v>
+        <v>427026</v>
       </c>
       <c r="R115" t="n">
-        <v>6798879</v>
+        <v>6798692</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12443,7 +12433,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12453,7 +12443,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12468,19 +12458,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126338943</v>
+        <v>126339857</v>
       </c>
       <c r="B116" t="n">
         <v>78736</v>
@@ -12511,17 +12501,17 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427026</v>
+        <v>427004</v>
       </c>
       <c r="R116" t="n">
-        <v>6798692</v>
+        <v>6798987</v>
       </c>
       <c r="S116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12550,7 +12540,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12560,7 +12550,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12575,19 +12565,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126339405</v>
+        <v>126338320</v>
       </c>
       <c r="B117" t="n">
         <v>79595</v>
@@ -12622,10 +12612,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426855</v>
+        <v>427072</v>
       </c>
       <c r="R117" t="n">
-        <v>6798979</v>
+        <v>6798879</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12694,10 +12684,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126339857</v>
+        <v>126339405</v>
       </c>
       <c r="B118" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12705,21 +12695,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12729,10 +12719,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427004</v>
+        <v>426855</v>
       </c>
       <c r="R118" t="n">
-        <v>6798987</v>
+        <v>6798979</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12801,32 +12791,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126336022</v>
+        <v>126334554</v>
       </c>
       <c r="B119" t="n">
-        <v>98266</v>
+        <v>79595</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12836,10 +12826,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427026</v>
+        <v>427075</v>
       </c>
       <c r="R119" t="n">
-        <v>6798688</v>
+        <v>6798591</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12871,7 +12861,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12881,7 +12871,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12908,10 +12898,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126334554</v>
+        <v>126334762</v>
       </c>
       <c r="B120" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12919,21 +12909,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12943,10 +12933,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427075</v>
+        <v>426962</v>
       </c>
       <c r="R120" t="n">
-        <v>6798591</v>
+        <v>6798805</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12978,7 +12968,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12988,7 +12978,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13003,12 +12998,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
@@ -13126,10 +13121,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126334241</v>
+        <v>126336022</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>98269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13137,34 +13132,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427095</v>
+        <v>427026</v>
       </c>
       <c r="R122" t="n">
-        <v>6798448</v>
+        <v>6798688</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13194,14 +13189,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13216,22 +13216,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126334762</v>
+        <v>126335998</v>
       </c>
       <c r="B123" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13239,34 +13239,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>426962</v>
+        <v>427015</v>
       </c>
       <c r="R123" t="n">
-        <v>6798805</v>
+        <v>6798754</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13296,24 +13296,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13328,19 +13313,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126339770</v>
+        <v>126335881</v>
       </c>
       <c r="B124" t="n">
         <v>78735</v>
@@ -13371,17 +13356,17 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427450</v>
+        <v>426993</v>
       </c>
       <c r="R124" t="n">
-        <v>6798525</v>
+        <v>6798667</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13408,9 +13393,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13425,22 +13420,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126335998</v>
+        <v>126339770</v>
       </c>
       <c r="B125" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13448,37 +13443,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427015</v>
+        <v>427450</v>
       </c>
       <c r="R125" t="n">
-        <v>6798754</v>
+        <v>6798525</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13522,22 +13517,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126335881</v>
+        <v>126335613</v>
       </c>
       <c r="B126" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13545,34 +13540,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426993</v>
+        <v>427042</v>
       </c>
       <c r="R126" t="n">
-        <v>6798667</v>
+        <v>6798684</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13602,19 +13597,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13629,22 +13614,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126335613</v>
+        <v>126338823</v>
       </c>
       <c r="B127" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13652,21 +13637,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13676,10 +13661,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427042</v>
+        <v>426933</v>
       </c>
       <c r="R127" t="n">
-        <v>6798684</v>
+        <v>6798926</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13709,9 +13694,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13738,10 +13733,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126338823</v>
+        <v>126335594</v>
       </c>
       <c r="B128" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13749,21 +13744,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13773,10 +13768,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>426933</v>
+        <v>427042</v>
       </c>
       <c r="R128" t="n">
-        <v>6798926</v>
+        <v>6798684</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13806,19 +13801,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13942,7 +13927,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126335594</v>
+        <v>126334548</v>
       </c>
       <c r="B130" t="n">
         <v>79595</v>
@@ -13973,14 +13958,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427042</v>
+        <v>426962</v>
       </c>
       <c r="R130" t="n">
-        <v>6798684</v>
+        <v>6798805</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14010,9 +13995,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14027,22 +14022,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126335567</v>
+        <v>126335852</v>
       </c>
       <c r="B131" t="n">
-        <v>78736</v>
+        <v>57816</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14050,37 +14045,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427022</v>
+        <v>427053</v>
       </c>
       <c r="R131" t="n">
-        <v>6798674</v>
+        <v>6798729</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14107,19 +14107,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14134,22 +14124,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126335852</v>
+        <v>126335567</v>
       </c>
       <c r="B132" t="n">
-        <v>57816</v>
+        <v>78736</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14157,42 +14147,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427053</v>
+        <v>427022</v>
       </c>
       <c r="R132" t="n">
-        <v>6798729</v>
+        <v>6798674</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14219,9 +14204,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14236,22 +14231,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126334548</v>
+        <v>126339616</v>
       </c>
       <c r="B133" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14259,21 +14254,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14283,10 +14278,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>426962</v>
+        <v>427329</v>
       </c>
       <c r="R133" t="n">
-        <v>6798805</v>
+        <v>6798435</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14318,7 +14313,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14328,7 +14323,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14343,22 +14338,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126335337</v>
+        <v>126334764</v>
       </c>
       <c r="B134" t="n">
-        <v>58135</v>
+        <v>78977</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14366,42 +14361,37 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427023</v>
+        <v>427055</v>
       </c>
       <c r="R134" t="n">
-        <v>6798652</v>
+        <v>6798616</v>
       </c>
       <c r="S134" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14428,9 +14418,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14445,22 +14445,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126335603</v>
+        <v>126340434</v>
       </c>
       <c r="B135" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14468,34 +14468,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427042</v>
+        <v>427486</v>
       </c>
       <c r="R135" t="n">
-        <v>6798684</v>
+        <v>6798404</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14525,9 +14525,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14542,12 +14552,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
@@ -14651,10 +14661,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126339616</v>
+        <v>126335337</v>
       </c>
       <c r="B137" t="n">
-        <v>78735</v>
+        <v>58135</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14662,37 +14672,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>103018</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427329</v>
+        <v>427023</v>
       </c>
       <c r="R137" t="n">
-        <v>6798435</v>
+        <v>6798652</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14719,19 +14734,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14746,22 +14751,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126340434</v>
+        <v>126335603</v>
       </c>
       <c r="B138" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14769,34 +14774,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427486</v>
+        <v>427042</v>
       </c>
       <c r="R138" t="n">
-        <v>6798404</v>
+        <v>6798684</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14826,19 +14831,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14853,22 +14848,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126334764</v>
+        <v>126364364</v>
       </c>
       <c r="B139" t="n">
-        <v>78977</v>
+        <v>75072</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14876,34 +14871,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427055</v>
+        <v>426970</v>
       </c>
       <c r="R139" t="n">
-        <v>6798616</v>
+        <v>6798728</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14930,22 +14925,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14960,22 +14955,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126364364</v>
+        <v>126366166</v>
       </c>
       <c r="B140" t="n">
-        <v>75072</v>
+        <v>78735</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14983,21 +14978,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15042,7 +15037,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15052,7 +15047,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15079,32 +15074,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126366166</v>
+        <v>126364681</v>
       </c>
       <c r="B141" t="n">
-        <v>78735</v>
+        <v>80109</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15149,7 +15144,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15159,7 +15154,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15186,32 +15181,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126364681</v>
+        <v>126365118</v>
       </c>
       <c r="B142" t="n">
-        <v>80109</v>
+        <v>96605</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15256,7 +15251,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15266,7 +15261,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15293,10 +15288,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126365118</v>
+        <v>126377455</v>
       </c>
       <c r="B143" t="n">
-        <v>96605</v>
+        <v>78736</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15304,37 +15299,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Rytterbygget, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>426970</v>
+        <v>427122</v>
       </c>
       <c r="R143" t="n">
-        <v>6798728</v>
+        <v>6798636</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15358,22 +15353,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15388,15 +15373,1679 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>126377429</v>
+      </c>
+      <c r="B144" t="n">
+        <v>56848</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>427013</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6798730</v>
+      </c>
+      <c r="S144" t="n">
+        <v>1</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>126377431</v>
+      </c>
+      <c r="B145" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>427033</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6798599</v>
+      </c>
+      <c r="S145" t="n">
+        <v>1</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>126377421</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>427122</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6798636</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>126377459</v>
+      </c>
+      <c r="B147" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>427033</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6798631</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>126377425</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>427080</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6798785</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>126377508</v>
+      </c>
+      <c r="B149" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>427079</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6798568</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>126377458</v>
+      </c>
+      <c r="B150" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>427105</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6798838</v>
+      </c>
+      <c r="S150" t="n">
+        <v>1</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>126377479</v>
+      </c>
+      <c r="B151" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>427035</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6798632</v>
+      </c>
+      <c r="S151" t="n">
+        <v>1</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>126377457</v>
+      </c>
+      <c r="B152" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>427145</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6798817</v>
+      </c>
+      <c r="S152" t="n">
+        <v>1</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>126377423</v>
+      </c>
+      <c r="B153" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>427002</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6798834</v>
+      </c>
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>126377456</v>
+      </c>
+      <c r="B154" t="n">
+        <v>78736</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>427162</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6798768</v>
+      </c>
+      <c r="S154" t="n">
+        <v>1</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>126377507</v>
+      </c>
+      <c r="B155" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>427034</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6798588</v>
+      </c>
+      <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>126377424</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>427113</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6798838</v>
+      </c>
+      <c r="S156" t="n">
+        <v>1</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>126377430</v>
+      </c>
+      <c r="B157" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>427063</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6798634</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>40 ex</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>126377478</v>
+      </c>
+      <c r="B158" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>427122</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6798636</v>
+      </c>
+      <c r="S158" t="n">
+        <v>1</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>126377427</v>
+      </c>
+      <c r="B159" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>427091</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6798545</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>126377426</v>
+      </c>
+      <c r="B160" t="n">
+        <v>79595</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Rytterbygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>427035</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6798632</v>
+      </c>
+      <c r="S160" t="n">
+        <v>1</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R7" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R8" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022312</v>
+        <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R26" t="n">
-        <v>6798594</v>
+        <v>6798570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022296</v>
+        <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798596</v>
+        <v>6798594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022292</v>
+        <v>126022296</v>
       </c>
       <c r="B28" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R28" t="n">
-        <v>6798570</v>
+        <v>6798596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4343,45 +4343,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126339860</v>
+        <v>126338600</v>
       </c>
       <c r="B39" t="n">
-        <v>79595</v>
+        <v>91503</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427301</v>
+        <v>426972</v>
       </c>
       <c r="R39" t="n">
-        <v>6798343</v>
+        <v>6798921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4438,22 +4438,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126334237</v>
+        <v>126337222</v>
       </c>
       <c r="B40" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,37 +4461,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427084</v>
+        <v>427067</v>
       </c>
       <c r="R40" t="n">
-        <v>6798524</v>
+        <v>6798806</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4518,19 +4518,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4545,22 +4535,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126336106</v>
+        <v>126339860</v>
       </c>
       <c r="B41" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4568,34 +4558,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>426970</v>
+        <v>427301</v>
       </c>
       <c r="R41" t="n">
-        <v>6798728</v>
+        <v>6798343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4627,7 +4617,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4637,7 +4627,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4652,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126337222</v>
+        <v>126334237</v>
       </c>
       <c r="B42" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,37 +4665,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427067</v>
+        <v>427084</v>
       </c>
       <c r="R42" t="n">
-        <v>6798806</v>
+        <v>6798524</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4732,9 +4722,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4749,44 +4749,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126338600</v>
+        <v>126336106</v>
       </c>
       <c r="B43" t="n">
-        <v>91503</v>
+        <v>78736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426972</v>
+        <v>426970</v>
       </c>
       <c r="R43" t="n">
-        <v>6798921</v>
+        <v>6798728</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4856,12 +4856,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5072,48 +5072,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126337209</v>
+        <v>126340047</v>
       </c>
       <c r="B46" t="n">
-        <v>79595</v>
+        <v>98269</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427026</v>
+        <v>427588</v>
       </c>
       <c r="R46" t="n">
-        <v>6798692</v>
+        <v>6798380</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5142,7 +5146,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5152,7 +5156,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,28 +5170,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126334857</v>
+        <v>126334541</v>
       </c>
       <c r="B47" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5190,21 +5200,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5214,10 +5224,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427060</v>
+        <v>426962</v>
       </c>
       <c r="R47" t="n">
-        <v>6798612</v>
+        <v>6798805</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5249,7 +5259,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5259,7 +5269,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,64 +5284,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126340047</v>
+        <v>126337209</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>79595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427588</v>
+        <v>427026</v>
       </c>
       <c r="R48" t="n">
-        <v>6798380</v>
+        <v>6798692</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5360,7 +5366,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5370,12 +5376,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,29 +5385,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126334541</v>
+        <v>126334857</v>
       </c>
       <c r="B49" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5414,21 +5414,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426962</v>
+        <v>427060</v>
       </c>
       <c r="R49" t="n">
-        <v>6798805</v>
+        <v>6798612</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5498,22 +5498,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126340584</v>
+        <v>126339364</v>
       </c>
       <c r="B50" t="n">
-        <v>78735</v>
+        <v>57653</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,34 +5521,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427242</v>
+        <v>427073</v>
       </c>
       <c r="R50" t="n">
-        <v>6798350</v>
+        <v>6798822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,19 +5583,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,22 +5600,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126336092</v>
+        <v>126339028</v>
       </c>
       <c r="B51" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5628,37 +5623,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427026</v>
+        <v>427113</v>
       </c>
       <c r="R51" t="n">
-        <v>6798692</v>
+        <v>6798674</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5697,7 +5692,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5712,22 +5707,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126339364</v>
+        <v>126340584</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>78735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5735,39 +5730,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427073</v>
+        <v>427242</v>
       </c>
       <c r="R52" t="n">
-        <v>6798822</v>
+        <v>6798350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5797,9 +5787,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5814,22 +5814,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126339028</v>
+        <v>126336092</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,37 +5837,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427113</v>
+        <v>427026</v>
       </c>
       <c r="R53" t="n">
-        <v>6798674</v>
+        <v>6798692</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5921,12 +5921,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126337677</v>
+        <v>126334331</v>
       </c>
       <c r="B60" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6581,21 +6581,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6605,13 +6605,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427092</v>
+        <v>427079</v>
       </c>
       <c r="R60" t="n">
-        <v>6798859</v>
+        <v>6798569</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6638,9 +6638,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6655,22 +6665,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126340359</v>
+        <v>126339304</v>
       </c>
       <c r="B61" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6678,34 +6688,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427116</v>
+        <v>427299</v>
       </c>
       <c r="R61" t="n">
-        <v>6798627</v>
+        <v>6798540</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6737,7 +6747,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6747,7 +6757,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6762,22 +6772,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126334331</v>
+        <v>126337677</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6785,21 +6795,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6809,13 +6819,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427079</v>
+        <v>427092</v>
       </c>
       <c r="R62" t="n">
-        <v>6798569</v>
+        <v>6798859</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6842,19 +6852,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6869,22 +6869,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126339304</v>
+        <v>126340359</v>
       </c>
       <c r="B63" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,34 +6892,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427299</v>
+        <v>427116</v>
       </c>
       <c r="R63" t="n">
-        <v>6798540</v>
+        <v>6798627</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,22 +6976,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126335973</v>
+        <v>126335831</v>
       </c>
       <c r="B64" t="n">
-        <v>98269</v>
+        <v>8447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427023</v>
+        <v>427005</v>
       </c>
       <c r="R64" t="n">
-        <v>6798681</v>
+        <v>6798710</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7068,7 +7068,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7083,19 +7088,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126335072</v>
+        <v>126335973</v>
       </c>
       <c r="B65" t="n">
         <v>98269</v>
@@ -7123,24 +7128,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427079</v>
+        <v>427023</v>
       </c>
       <c r="R65" t="n">
-        <v>6798569</v>
+        <v>6798681</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7169,7 +7170,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7179,7 +7180,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7194,57 +7195,61 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126337872</v>
+        <v>126335072</v>
       </c>
       <c r="B66" t="n">
-        <v>79566</v>
+        <v>98269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427103</v>
+        <v>427079</v>
       </c>
       <c r="R66" t="n">
-        <v>6798836</v>
+        <v>6798569</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7274,9 +7279,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7291,44 +7306,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126335831</v>
+        <v>126334876</v>
       </c>
       <c r="B67" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7338,13 +7353,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427005</v>
+        <v>427084</v>
       </c>
       <c r="R67" t="n">
-        <v>6798710</v>
+        <v>6798578</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7373,7 +7388,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7383,12 +7398,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gnagspår i tallåga</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7403,22 +7413,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126334876</v>
+        <v>126337872</v>
       </c>
       <c r="B68" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,34 +7436,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427084</v>
+        <v>427103</v>
       </c>
       <c r="R68" t="n">
-        <v>6798578</v>
+        <v>6798836</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7483,19 +7493,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,60 +7510,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126339529</v>
+        <v>126336097</v>
       </c>
       <c r="B69" t="n">
-        <v>79072</v>
+        <v>98269</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>967</v>
+        <v>219790</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427360</v>
+        <v>427038</v>
       </c>
       <c r="R69" t="n">
-        <v>6798574</v>
+        <v>6798675</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7590,9 +7590,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,60 +7617,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126336097</v>
+        <v>126339529</v>
       </c>
       <c r="B70" t="n">
-        <v>98269</v>
+        <v>79072</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219790</v>
+        <v>967</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427038</v>
+        <v>427360</v>
       </c>
       <c r="R70" t="n">
-        <v>6798675</v>
+        <v>6798574</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7687,19 +7697,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7714,12 +7714,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126336279</v>
+        <v>126338455</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10283,13 +10283,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427018</v>
+        <v>427173</v>
       </c>
       <c r="R95" t="n">
-        <v>6798762</v>
+        <v>6798821</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10316,9 +10316,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10333,22 +10343,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126337979</v>
+        <v>126339416</v>
       </c>
       <c r="B96" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10356,34 +10366,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427138</v>
+        <v>427360</v>
       </c>
       <c r="R96" t="n">
-        <v>6798830</v>
+        <v>6798573</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10415,7 +10425,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10425,7 +10435,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10440,22 +10450,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126338455</v>
+        <v>126336279</v>
       </c>
       <c r="B97" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10463,21 +10473,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10487,13 +10497,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427173</v>
+        <v>427018</v>
       </c>
       <c r="R97" t="n">
-        <v>6798821</v>
+        <v>6798762</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10520,19 +10530,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10547,22 +10547,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126339416</v>
+        <v>126337979</v>
       </c>
       <c r="B98" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10570,34 +10570,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427360</v>
+        <v>427138</v>
       </c>
       <c r="R98" t="n">
-        <v>6798573</v>
+        <v>6798830</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10654,12 +10654,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11833,10 +11833,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126337286</v>
+        <v>126338324</v>
       </c>
       <c r="B110" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11844,34 +11844,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427056</v>
+        <v>427072</v>
       </c>
       <c r="R110" t="n">
-        <v>6798834</v>
+        <v>6798879</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11928,22 +11928,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126339588</v>
+        <v>126337559</v>
       </c>
       <c r="B111" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,21 +11951,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427328</v>
+        <v>427047</v>
       </c>
       <c r="R111" t="n">
-        <v>6798426</v>
+        <v>6798896</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12047,10 +12047,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126338324</v>
+        <v>126337286</v>
       </c>
       <c r="B112" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12058,34 +12058,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427072</v>
+        <v>427056</v>
       </c>
       <c r="R112" t="n">
-        <v>6798879</v>
+        <v>6798834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12142,22 +12142,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126337559</v>
+        <v>126339588</v>
       </c>
       <c r="B113" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12165,21 +12165,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12189,10 +12189,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427047</v>
+        <v>427328</v>
       </c>
       <c r="R113" t="n">
-        <v>6798896</v>
+        <v>6798426</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12261,32 +12261,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126334241</v>
+        <v>126338320</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427095</v>
+        <v>427072</v>
       </c>
       <c r="R114" t="n">
-        <v>6798448</v>
+        <v>6798879</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12329,14 +12329,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12363,10 +12368,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126338943</v>
+        <v>126339405</v>
       </c>
       <c r="B115" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12374,37 +12379,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427026</v>
+        <v>426855</v>
       </c>
       <c r="R115" t="n">
-        <v>6798692</v>
+        <v>6798979</v>
       </c>
       <c r="S115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12433,7 +12438,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12443,7 +12448,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12458,22 +12463,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126339857</v>
+        <v>126334554</v>
       </c>
       <c r="B116" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12481,34 +12486,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427004</v>
+        <v>427075</v>
       </c>
       <c r="R116" t="n">
-        <v>6798987</v>
+        <v>6798591</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12540,7 +12545,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12550,7 +12555,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12565,22 +12570,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126338320</v>
+        <v>126334762</v>
       </c>
       <c r="B117" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12588,34 +12593,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427072</v>
+        <v>426962</v>
       </c>
       <c r="R117" t="n">
-        <v>6798879</v>
+        <v>6798805</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12647,7 +12652,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12657,7 +12662,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12672,19 +12682,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126339405</v>
+        <v>126335754</v>
       </c>
       <c r="B118" t="n">
         <v>79595</v>
@@ -12713,16 +12723,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426855</v>
+        <v>426984</v>
       </c>
       <c r="R118" t="n">
-        <v>6798979</v>
+        <v>6798652</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12754,7 +12767,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12764,7 +12777,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12773,63 +12786,64 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126334554</v>
+        <v>126334241</v>
       </c>
       <c r="B119" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427075</v>
+        <v>427095</v>
       </c>
       <c r="R119" t="n">
-        <v>6798591</v>
+        <v>6798448</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12859,19 +12873,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12886,22 +12895,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126334762</v>
+        <v>126338943</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12909,21 +12918,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12933,13 +12942,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>426962</v>
+        <v>427026</v>
       </c>
       <c r="R120" t="n">
-        <v>6798805</v>
+        <v>6798692</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12968,7 +12977,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12978,12 +12987,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12998,22 +13002,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126335754</v>
+        <v>126339857</v>
       </c>
       <c r="B121" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13021,37 +13025,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426984</v>
+        <v>427004</v>
       </c>
       <c r="R121" t="n">
-        <v>6798652</v>
+        <v>6798987</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13083,7 +13084,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13093,7 +13094,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13102,19 +13103,18 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13325,10 +13325,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126335881</v>
+        <v>126335613</v>
       </c>
       <c r="B124" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13336,34 +13336,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426993</v>
+        <v>427042</v>
       </c>
       <c r="R124" t="n">
-        <v>6798667</v>
+        <v>6798684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13393,19 +13393,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13420,22 +13410,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126339770</v>
+        <v>126338823</v>
       </c>
       <c r="B125" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13443,37 +13433,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427450</v>
+        <v>426933</v>
       </c>
       <c r="R125" t="n">
-        <v>6798525</v>
+        <v>6798926</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13500,9 +13490,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13517,22 +13517,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126335613</v>
+        <v>126335881</v>
       </c>
       <c r="B126" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13540,34 +13540,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427042</v>
+        <v>426993</v>
       </c>
       <c r="R126" t="n">
-        <v>6798684</v>
+        <v>6798667</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13597,9 +13597,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13614,22 +13624,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126338823</v>
+        <v>126339770</v>
       </c>
       <c r="B127" t="n">
-        <v>79566</v>
+        <v>78735</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13637,37 +13647,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>426933</v>
+        <v>427450</v>
       </c>
       <c r="R127" t="n">
-        <v>6798926</v>
+        <v>6798525</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13694,19 +13704,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13721,12 +13721,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -14034,10 +14034,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126335852</v>
+        <v>126335567</v>
       </c>
       <c r="B131" t="n">
-        <v>57816</v>
+        <v>78736</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14045,42 +14045,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427053</v>
+        <v>427022</v>
       </c>
       <c r="R131" t="n">
-        <v>6798729</v>
+        <v>6798674</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14107,9 +14102,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14124,22 +14129,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126335567</v>
+        <v>126335852</v>
       </c>
       <c r="B132" t="n">
-        <v>78736</v>
+        <v>57816</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14147,37 +14152,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427022</v>
+        <v>427053</v>
       </c>
       <c r="R132" t="n">
-        <v>6798674</v>
+        <v>6798729</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14204,19 +14214,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14231,12 +14231,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R7" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126022316</v>
+        <v>126022301</v>
       </c>
       <c r="B12" t="n">
-        <v>78735</v>
+        <v>91192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1665,21 +1665,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1692,7 +1692,7 @@
         <v>427033</v>
       </c>
       <c r="R12" t="n">
-        <v>6798630</v>
+        <v>6798637</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126022301</v>
+        <v>126022316</v>
       </c>
       <c r="B13" t="n">
-        <v>91192</v>
+        <v>78735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1762,21 +1762,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         <v>427033</v>
       </c>
       <c r="R13" t="n">
-        <v>6798637</v>
+        <v>6798630</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B19" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R19" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B20" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R20" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022312</v>
+        <v>126022296</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798594</v>
+        <v>6798596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022296</v>
+        <v>126022312</v>
       </c>
       <c r="B28" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
         <v>426982</v>
       </c>
       <c r="R28" t="n">
-        <v>6798596</v>
+        <v>6798594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126340016</v>
+        <v>126340383</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,34 +3508,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427570</v>
+        <v>427116</v>
       </c>
       <c r="R31" t="n">
-        <v>6798393</v>
+        <v>6798627</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,19 +3592,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126340383</v>
+        <v>126339643</v>
       </c>
       <c r="B32" t="n">
         <v>79566</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427116</v>
+        <v>426885</v>
       </c>
       <c r="R32" t="n">
-        <v>6798627</v>
+        <v>6799018</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126339643</v>
+        <v>126340016</v>
       </c>
       <c r="B33" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426885</v>
+        <v>427570</v>
       </c>
       <c r="R33" t="n">
-        <v>6799018</v>
+        <v>6798393</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3806,22 +3806,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126334889</v>
+        <v>126335214</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,21 +3829,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427084</v>
+        <v>427080</v>
       </c>
       <c r="R34" t="n">
-        <v>6798578</v>
+        <v>6798606</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3913,19 +3913,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126339444</v>
+        <v>126334889</v>
       </c>
       <c r="B35" t="n">
         <v>79595</v>
@@ -3956,17 +3956,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>426858</v>
+        <v>427084</v>
       </c>
       <c r="R35" t="n">
-        <v>6799009</v>
+        <v>6798578</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4020,22 +4020,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126340669</v>
+        <v>126339444</v>
       </c>
       <c r="B36" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,34 +4043,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427162</v>
+        <v>426858</v>
       </c>
       <c r="R36" t="n">
-        <v>6798406</v>
+        <v>6799009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4127,22 +4127,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126335214</v>
+        <v>126340669</v>
       </c>
       <c r="B37" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4150,21 +4150,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427080</v>
+        <v>427162</v>
       </c>
       <c r="R37" t="n">
-        <v>6798606</v>
+        <v>6798406</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4234,12 +4234,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4450,10 +4450,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126337222</v>
+        <v>126339860</v>
       </c>
       <c r="B40" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,34 +4461,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427067</v>
+        <v>427301</v>
       </c>
       <c r="R40" t="n">
-        <v>6798806</v>
+        <v>6798343</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4518,9 +4518,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4535,19 +4545,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126339860</v>
+        <v>126334237</v>
       </c>
       <c r="B41" t="n">
         <v>79595</v>
@@ -4582,13 +4592,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427301</v>
+        <v>427084</v>
       </c>
       <c r="R41" t="n">
-        <v>6798343</v>
+        <v>6798524</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4617,7 +4627,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4627,7 +4637,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4642,22 +4652,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126334237</v>
+        <v>126337222</v>
       </c>
       <c r="B42" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,37 +4675,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427084</v>
+        <v>427067</v>
       </c>
       <c r="R42" t="n">
-        <v>6798524</v>
+        <v>6798806</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4722,19 +4732,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4749,12 +4749,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126339934</v>
+        <v>126335181</v>
       </c>
       <c r="B44" t="n">
         <v>78977</v>
@@ -4899,14 +4899,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427360</v>
+        <v>427044</v>
       </c>
       <c r="R44" t="n">
-        <v>6798573</v>
+        <v>6798644</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4936,19 +4936,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4963,19 +4953,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126335181</v>
+        <v>126339934</v>
       </c>
       <c r="B45" t="n">
         <v>78977</v>
@@ -5006,14 +4996,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427044</v>
+        <v>427360</v>
       </c>
       <c r="R45" t="n">
-        <v>6798644</v>
+        <v>6798573</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5043,9 +5033,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5060,61 +5060,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126340047</v>
+        <v>126334857</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427588</v>
+        <v>427060</v>
       </c>
       <c r="R46" t="n">
-        <v>6798380</v>
+        <v>6798612</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5146,7 +5142,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5156,12 +5152,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5170,7 +5161,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5189,10 +5179,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126334541</v>
+        <v>126337209</v>
       </c>
       <c r="B47" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,21 +5190,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5224,13 +5214,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426962</v>
+        <v>427026</v>
       </c>
       <c r="R47" t="n">
-        <v>6798805</v>
+        <v>6798692</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5259,7 +5249,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5269,7 +5259,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5284,60 +5274,64 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126337209</v>
+        <v>126340047</v>
       </c>
       <c r="B48" t="n">
-        <v>79595</v>
+        <v>98269</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427026</v>
+        <v>427588</v>
       </c>
       <c r="R48" t="n">
-        <v>6798692</v>
+        <v>6798380</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5366,7 +5360,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5376,7 +5370,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5385,28 +5384,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126334857</v>
+        <v>126334541</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5414,21 +5414,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427060</v>
+        <v>426962</v>
       </c>
       <c r="R49" t="n">
-        <v>6798612</v>
+        <v>6798805</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5498,22 +5498,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126339364</v>
+        <v>126340584</v>
       </c>
       <c r="B50" t="n">
-        <v>57653</v>
+        <v>78735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,39 +5521,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427073</v>
+        <v>427242</v>
       </c>
       <c r="R50" t="n">
-        <v>6798822</v>
+        <v>6798350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,9 +5578,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5600,22 +5605,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126339028</v>
+        <v>126336092</v>
       </c>
       <c r="B51" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5623,37 +5628,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427113</v>
+        <v>427026</v>
       </c>
       <c r="R51" t="n">
-        <v>6798674</v>
+        <v>6798692</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5682,7 +5687,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5692,7 +5697,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5707,22 +5712,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126340584</v>
+        <v>126335481</v>
       </c>
       <c r="B52" t="n">
-        <v>78735</v>
+        <v>57656</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,34 +5735,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427242</v>
+        <v>427042</v>
       </c>
       <c r="R52" t="n">
-        <v>6798350</v>
+        <v>6798684</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5787,19 +5797,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5814,22 +5814,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126336092</v>
+        <v>126339364</v>
       </c>
       <c r="B53" t="n">
-        <v>78735</v>
+        <v>57653</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,37 +5837,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427026</v>
+        <v>427073</v>
       </c>
       <c r="R53" t="n">
-        <v>6798692</v>
+        <v>6798822</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5894,19 +5899,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5921,22 +5916,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126335481</v>
+        <v>126339028</v>
       </c>
       <c r="B54" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,42 +5939,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427042</v>
+        <v>427113</v>
       </c>
       <c r="R54" t="n">
-        <v>6798684</v>
+        <v>6798674</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6006,9 +5996,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6023,60 +6023,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126335625</v>
+        <v>126340128</v>
       </c>
       <c r="B55" t="n">
-        <v>96605</v>
+        <v>98269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427079</v>
+        <v>427631</v>
       </c>
       <c r="R55" t="n">
-        <v>6798569</v>
+        <v>6798401</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6130,12 +6130,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126338668</v>
+        <v>126335625</v>
       </c>
       <c r="B58" t="n">
-        <v>78735</v>
+        <v>96605</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6391,13 +6391,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426958</v>
+        <v>427079</v>
       </c>
       <c r="R58" t="n">
-        <v>6798928</v>
+        <v>6798569</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6451,57 +6451,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126340128</v>
+        <v>126338668</v>
       </c>
       <c r="B59" t="n">
-        <v>98269</v>
+        <v>78735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427631</v>
+        <v>426958</v>
       </c>
       <c r="R59" t="n">
-        <v>6798401</v>
+        <v>6798928</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6558,12 +6558,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126339304</v>
+        <v>126334876</v>
       </c>
       <c r="B61" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6688,21 +6688,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427299</v>
+        <v>427084</v>
       </c>
       <c r="R61" t="n">
-        <v>6798540</v>
+        <v>6798578</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6772,22 +6772,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126337677</v>
+        <v>126337872</v>
       </c>
       <c r="B62" t="n">
-        <v>79595</v>
+        <v>79566</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6795,37 +6795,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427092</v>
+        <v>427103</v>
       </c>
       <c r="R62" t="n">
-        <v>6798859</v>
+        <v>6798836</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6869,22 +6869,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126340359</v>
+        <v>126339304</v>
       </c>
       <c r="B63" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,34 +6892,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427116</v>
+        <v>427299</v>
       </c>
       <c r="R63" t="n">
-        <v>6798627</v>
+        <v>6798540</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,57 +6976,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126335831</v>
+        <v>126337677</v>
       </c>
       <c r="B64" t="n">
-        <v>8447</v>
+        <v>79595</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427005</v>
+        <v>427092</v>
       </c>
       <c r="R64" t="n">
-        <v>6798710</v>
+        <v>6798859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7056,24 +7056,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7088,57 +7073,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126335973</v>
+        <v>126340359</v>
       </c>
       <c r="B65" t="n">
-        <v>98269</v>
+        <v>78735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427023</v>
+        <v>427116</v>
       </c>
       <c r="R65" t="n">
-        <v>6798681</v>
+        <v>6798627</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7170,7 +7155,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7180,7 +7165,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7195,22 +7180,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126335072</v>
+        <v>126335831</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
+        <v>8447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7218,41 +7203,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427079</v>
+        <v>427005</v>
       </c>
       <c r="R66" t="n">
-        <v>6798569</v>
+        <v>6798710</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7281,7 +7262,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7291,7 +7272,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7306,44 +7292,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126334876</v>
+        <v>126335973</v>
       </c>
       <c r="B67" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7353,13 +7339,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427084</v>
+        <v>427023</v>
       </c>
       <c r="R67" t="n">
-        <v>6798578</v>
+        <v>6798681</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7388,7 +7374,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7398,7 +7384,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7413,57 +7399,61 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126337872</v>
+        <v>126335072</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>98269</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427103</v>
+        <v>427079</v>
       </c>
       <c r="R68" t="n">
-        <v>6798836</v>
+        <v>6798569</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7493,9 +7483,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,57 +7510,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126336097</v>
+        <v>126338801</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>78735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427038</v>
+        <v>426933</v>
       </c>
       <c r="R69" t="n">
-        <v>6798675</v>
+        <v>6798926</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7617,22 +7617,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126339529</v>
+        <v>126340365</v>
       </c>
       <c r="B70" t="n">
-        <v>79072</v>
+        <v>79595</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7640,37 +7640,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427360</v>
+        <v>427116</v>
       </c>
       <c r="R70" t="n">
-        <v>6798574</v>
+        <v>6798627</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7697,9 +7697,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7714,22 +7724,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126338801</v>
+        <v>126336082</v>
       </c>
       <c r="B71" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7737,37 +7747,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426933</v>
+        <v>426993</v>
       </c>
       <c r="R71" t="n">
-        <v>6798926</v>
+        <v>6798667</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7796,7 +7806,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7806,7 +7816,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7821,19 +7831,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126340365</v>
+        <v>126339773</v>
       </c>
       <c r="B72" t="n">
         <v>79595</v>
@@ -7864,14 +7874,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427116</v>
+        <v>426959</v>
       </c>
       <c r="R72" t="n">
-        <v>6798627</v>
+        <v>6798956</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7903,7 +7913,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7913,7 +7923,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7928,19 +7938,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126336082</v>
+        <v>126334052</v>
       </c>
       <c r="B73" t="n">
         <v>79595</v>
@@ -7975,13 +7985,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426993</v>
+        <v>427079</v>
       </c>
       <c r="R73" t="n">
-        <v>6798667</v>
+        <v>6798512</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8010,7 +8020,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8020,7 +8030,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8035,22 +8045,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126339773</v>
+        <v>126339757</v>
       </c>
       <c r="B74" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,34 +8068,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426959</v>
+        <v>426981</v>
       </c>
       <c r="R74" t="n">
-        <v>6798956</v>
+        <v>6798995</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8117,7 +8127,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8127,7 +8137,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,19 +8152,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126334052</v>
+        <v>126335972</v>
       </c>
       <c r="B75" t="n">
         <v>79595</v>
@@ -8189,10 +8199,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427079</v>
+        <v>426988</v>
       </c>
       <c r="R75" t="n">
-        <v>6798512</v>
+        <v>6798730</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8224,7 +8234,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8234,7 +8244,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8249,57 +8259,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126339757</v>
+        <v>126336097</v>
       </c>
       <c r="B76" t="n">
-        <v>78735</v>
+        <v>98269</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426981</v>
+        <v>427038</v>
       </c>
       <c r="R76" t="n">
-        <v>6798995</v>
+        <v>6798675</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8331,7 +8341,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8341,7 +8351,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8356,22 +8366,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126335972</v>
+        <v>126339529</v>
       </c>
       <c r="B77" t="n">
-        <v>79595</v>
+        <v>79072</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8379,37 +8389,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>426988</v>
+        <v>427360</v>
       </c>
       <c r="R77" t="n">
-        <v>6798730</v>
+        <v>6798574</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8436,19 +8446,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8463,12 +8463,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9422,10 +9422,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126338355</v>
+        <v>126337274</v>
       </c>
       <c r="B87" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9433,34 +9433,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427171</v>
+        <v>427056</v>
       </c>
       <c r="R87" t="n">
-        <v>6798818</v>
+        <v>6798834</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9517,19 +9517,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126338430</v>
+        <v>126338355</v>
       </c>
       <c r="B88" t="n">
         <v>78736</v>
@@ -9560,14 +9560,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427157</v>
+        <v>427171</v>
       </c>
       <c r="R88" t="n">
-        <v>6798766</v>
+        <v>6798818</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9624,22 +9624,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126337274</v>
+        <v>126338430</v>
       </c>
       <c r="B89" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9647,34 +9647,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427056</v>
+        <v>427157</v>
       </c>
       <c r="R89" t="n">
-        <v>6798834</v>
+        <v>6798766</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9731,22 +9731,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126333986</v>
+        <v>126337681</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427095</v>
+        <v>427092</v>
       </c>
       <c r="R90" t="n">
-        <v>6798448</v>
+        <v>6798859</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126337982</v>
+        <v>126333986</v>
       </c>
       <c r="B91" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9851,21 +9851,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427138</v>
+        <v>427095</v>
       </c>
       <c r="R91" t="n">
-        <v>6798830</v>
+        <v>6798448</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9908,19 +9908,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9947,32 +9937,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126335099</v>
+        <v>126337982</v>
       </c>
       <c r="B92" t="n">
-        <v>98269</v>
+        <v>78735</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9982,10 +9972,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427044</v>
+        <v>427138</v>
       </c>
       <c r="R92" t="n">
-        <v>6798644</v>
+        <v>6798830</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10015,9 +10005,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10044,45 +10044,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126335896</v>
+        <v>126335099</v>
       </c>
       <c r="B93" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426993</v>
+        <v>427044</v>
       </c>
       <c r="R93" t="n">
-        <v>6798667</v>
+        <v>6798644</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,19 +10112,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10139,22 +10129,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126337681</v>
+        <v>126335896</v>
       </c>
       <c r="B94" t="n">
-        <v>79566</v>
+        <v>78736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10162,34 +10152,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427092</v>
+        <v>426993</v>
       </c>
       <c r="R94" t="n">
-        <v>6798859</v>
+        <v>6798667</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10219,9 +10209,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10236,12 +10236,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10666,10 +10666,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126334576</v>
+        <v>126337016</v>
       </c>
       <c r="B99" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10677,21 +10677,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10701,13 +10701,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427115</v>
+        <v>427012</v>
       </c>
       <c r="R99" t="n">
-        <v>6798555</v>
+        <v>6798760</v>
       </c>
       <c r="S99" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10761,22 +10761,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126337016</v>
+        <v>126334576</v>
       </c>
       <c r="B100" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,21 +10784,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427012</v>
+        <v>427115</v>
       </c>
       <c r="R100" t="n">
-        <v>6798760</v>
+        <v>6798555</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10868,12 +10868,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11395,45 +11395,49 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126339015</v>
+        <v>126334915</v>
       </c>
       <c r="B106" t="n">
-        <v>79566</v>
+        <v>98269</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>219790</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>426894</v>
+        <v>427060</v>
       </c>
       <c r="R106" t="n">
-        <v>6798935</v>
+        <v>6798614</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11465,7 +11469,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11475,7 +11479,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11484,18 +11493,19 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11609,49 +11619,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126334915</v>
+        <v>126335795</v>
       </c>
       <c r="B108" t="n">
-        <v>98269</v>
+        <v>78736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427060</v>
+        <v>426989</v>
       </c>
       <c r="R108" t="n">
-        <v>6798614</v>
+        <v>6798666</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11683,7 +11689,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11693,12 +11699,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11707,7 +11708,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11726,10 +11726,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126335795</v>
+        <v>126339015</v>
       </c>
       <c r="B109" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11737,34 +11737,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426989</v>
+        <v>426894</v>
       </c>
       <c r="R109" t="n">
-        <v>6798666</v>
+        <v>6798935</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11821,12 +11821,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11940,10 +11940,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126337559</v>
+        <v>126339588</v>
       </c>
       <c r="B111" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,21 +11951,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427047</v>
+        <v>427328</v>
       </c>
       <c r="R111" t="n">
-        <v>6798896</v>
+        <v>6798426</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12154,10 +12154,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126339588</v>
+        <v>126337559</v>
       </c>
       <c r="B113" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12165,21 +12165,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12189,10 +12189,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427328</v>
+        <v>427047</v>
       </c>
       <c r="R113" t="n">
-        <v>6798426</v>
+        <v>6798896</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12261,10 +12261,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126338320</v>
+        <v>126334762</v>
       </c>
       <c r="B114" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12272,34 +12272,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427072</v>
+        <v>426962</v>
       </c>
       <c r="R114" t="n">
-        <v>6798879</v>
+        <v>6798805</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12341,7 +12341,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12356,19 +12361,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126339405</v>
+        <v>126338320</v>
       </c>
       <c r="B115" t="n">
         <v>79595</v>
@@ -12403,10 +12408,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426855</v>
+        <v>427072</v>
       </c>
       <c r="R115" t="n">
-        <v>6798979</v>
+        <v>6798879</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12475,7 +12480,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126334554</v>
+        <v>126339405</v>
       </c>
       <c r="B116" t="n">
         <v>79595</v>
@@ -12506,14 +12511,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427075</v>
+        <v>426855</v>
       </c>
       <c r="R116" t="n">
-        <v>6798591</v>
+        <v>6798979</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12545,7 +12550,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12555,7 +12560,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12570,22 +12575,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126334762</v>
+        <v>126334554</v>
       </c>
       <c r="B117" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12593,21 +12598,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12617,10 +12622,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426962</v>
+        <v>427075</v>
       </c>
       <c r="R117" t="n">
-        <v>6798805</v>
+        <v>6798591</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12652,7 +12657,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12662,12 +12667,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12682,12 +12682,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12907,32 +12907,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126338943</v>
+        <v>126336022</v>
       </c>
       <c r="B120" t="n">
-        <v>78736</v>
+        <v>98269</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12945,10 +12945,10 @@
         <v>427026</v>
       </c>
       <c r="R120" t="n">
-        <v>6798692</v>
+        <v>6798688</v>
       </c>
       <c r="S120" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13002,19 +13002,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126339857</v>
+        <v>126338943</v>
       </c>
       <c r="B121" t="n">
         <v>78736</v>
@@ -13045,17 +13045,17 @@
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427004</v>
+        <v>427026</v>
       </c>
       <c r="R121" t="n">
-        <v>6798987</v>
+        <v>6798692</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13094,7 +13094,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13109,57 +13109,57 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126336022</v>
+        <v>126339857</v>
       </c>
       <c r="B122" t="n">
-        <v>98269</v>
+        <v>78736</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427026</v>
+        <v>427004</v>
       </c>
       <c r="R122" t="n">
-        <v>6798688</v>
+        <v>6798987</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13191,7 +13191,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13216,22 +13216,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126335998</v>
+        <v>126335613</v>
       </c>
       <c r="B123" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13239,21 +13239,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427015</v>
+        <v>427042</v>
       </c>
       <c r="R123" t="n">
-        <v>6798754</v>
+        <v>6798684</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13325,10 +13325,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126335613</v>
+        <v>126338823</v>
       </c>
       <c r="B124" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13336,21 +13336,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427042</v>
+        <v>426933</v>
       </c>
       <c r="R124" t="n">
-        <v>6798684</v>
+        <v>6798926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13393,9 +13393,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13422,10 +13432,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126338823</v>
+        <v>126335998</v>
       </c>
       <c r="B125" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13433,21 +13443,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13457,10 +13467,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>426933</v>
+        <v>427015</v>
       </c>
       <c r="R125" t="n">
-        <v>6798926</v>
+        <v>6798754</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13490,19 +13500,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14243,10 +14243,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126339616</v>
+        <v>126334764</v>
       </c>
       <c r="B133" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14254,21 +14254,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427329</v>
+        <v>427055</v>
       </c>
       <c r="R133" t="n">
-        <v>6798435</v>
+        <v>6798616</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14350,7 +14350,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126334764</v>
+        <v>126340434</v>
       </c>
       <c r="B134" t="n">
         <v>78977</v>
@@ -14385,10 +14385,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427055</v>
+        <v>427486</v>
       </c>
       <c r="R134" t="n">
-        <v>6798616</v>
+        <v>6798404</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14457,10 +14457,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126340434</v>
+        <v>126339616</v>
       </c>
       <c r="B135" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14468,21 +14468,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14492,10 +14492,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427486</v>
+        <v>427329</v>
       </c>
       <c r="R135" t="n">
-        <v>6798404</v>
+        <v>6798435</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15487,32 +15487,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126377431</v>
+        <v>126377421</v>
       </c>
       <c r="B145" t="n">
-        <v>98373</v>
+        <v>79595</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15522,10 +15522,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427033</v>
+        <v>427122</v>
       </c>
       <c r="R145" t="n">
-        <v>6798599</v>
+        <v>6798636</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -15558,11 +15558,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15589,32 +15584,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126377421</v>
+        <v>126377431</v>
       </c>
       <c r="B146" t="n">
-        <v>79595</v>
+        <v>98373</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15624,10 +15619,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427122</v>
+        <v>427033</v>
       </c>
       <c r="R146" t="n">
-        <v>6798636</v>
+        <v>6798599</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -15660,6 +15655,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15686,10 +15686,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126377459</v>
+        <v>126377425</v>
       </c>
       <c r="B147" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,21 +15697,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15721,10 +15721,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427033</v>
+        <v>427080</v>
       </c>
       <c r="R147" t="n">
-        <v>6798631</v>
+        <v>6798785</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15783,10 +15783,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126377425</v>
+        <v>126377508</v>
       </c>
       <c r="B148" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15794,21 +15794,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427080</v>
+        <v>427079</v>
       </c>
       <c r="R148" t="n">
-        <v>6798785</v>
+        <v>6798568</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15880,10 +15880,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126377508</v>
+        <v>126377459</v>
       </c>
       <c r="B149" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15891,21 +15891,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427079</v>
+        <v>427033</v>
       </c>
       <c r="R149" t="n">
-        <v>6798568</v>
+        <v>6798631</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -16656,32 +16656,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126377430</v>
+        <v>126377478</v>
       </c>
       <c r="B157" t="n">
-        <v>98373</v>
+        <v>78735</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221952</v>
+        <v>6446</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16691,10 +16691,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427063</v>
+        <v>427122</v>
       </c>
       <c r="R157" t="n">
-        <v>6798634</v>
+        <v>6798636</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -16727,11 +16727,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16758,10 +16753,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126377478</v>
+        <v>126377427</v>
       </c>
       <c r="B158" t="n">
-        <v>78735</v>
+        <v>79595</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16769,21 +16764,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16793,10 +16788,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427122</v>
+        <v>427091</v>
       </c>
       <c r="R158" t="n">
-        <v>6798636</v>
+        <v>6798545</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -16855,32 +16850,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126377427</v>
+        <v>126377430</v>
       </c>
       <c r="B159" t="n">
-        <v>79595</v>
+        <v>98373</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16890,10 +16885,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427091</v>
+        <v>427063</v>
       </c>
       <c r="R159" t="n">
-        <v>6798545</v>
+        <v>6798634</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16926,6 +16921,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B7" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R7" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B8" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R8" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126340383</v>
+        <v>126340016</v>
       </c>
       <c r="B31" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,34 +3508,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427116</v>
+        <v>427570</v>
       </c>
       <c r="R31" t="n">
-        <v>6798627</v>
+        <v>6798393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,19 +3592,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126339643</v>
+        <v>126340383</v>
       </c>
       <c r="B32" t="n">
         <v>79566</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426885</v>
+        <v>427116</v>
       </c>
       <c r="R32" t="n">
-        <v>6799018</v>
+        <v>6798627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126340016</v>
+        <v>126339643</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427570</v>
+        <v>426885</v>
       </c>
       <c r="R33" t="n">
-        <v>6798393</v>
+        <v>6799018</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3806,12 +3806,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126334876</v>
+        <v>126339304</v>
       </c>
       <c r="B61" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6688,21 +6688,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6712,13 +6712,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427084</v>
+        <v>427299</v>
       </c>
       <c r="R61" t="n">
-        <v>6798578</v>
+        <v>6798540</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6772,22 +6772,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126337872</v>
+        <v>126337677</v>
       </c>
       <c r="B62" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6795,37 +6795,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427103</v>
+        <v>427092</v>
       </c>
       <c r="R62" t="n">
-        <v>6798836</v>
+        <v>6798859</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6869,22 +6869,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126339304</v>
+        <v>126340359</v>
       </c>
       <c r="B63" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,34 +6892,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427299</v>
+        <v>427116</v>
       </c>
       <c r="R63" t="n">
-        <v>6798540</v>
+        <v>6798627</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,57 +6976,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126337677</v>
+        <v>126335831</v>
       </c>
       <c r="B64" t="n">
-        <v>79595</v>
+        <v>8447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427092</v>
+        <v>427005</v>
       </c>
       <c r="R64" t="n">
-        <v>6798859</v>
+        <v>6798710</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7056,9 +7056,24 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7073,57 +7088,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126340359</v>
+        <v>126335973</v>
       </c>
       <c r="B65" t="n">
-        <v>78735</v>
+        <v>98269</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427116</v>
+        <v>427023</v>
       </c>
       <c r="R65" t="n">
-        <v>6798627</v>
+        <v>6798681</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7155,7 +7170,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7165,7 +7180,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7180,22 +7195,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126335831</v>
+        <v>126335072</v>
       </c>
       <c r="B66" t="n">
-        <v>8447</v>
+        <v>98269</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7203,37 +7218,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427005</v>
+        <v>427079</v>
       </c>
       <c r="R66" t="n">
-        <v>6798710</v>
+        <v>6798569</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7262,7 +7281,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7272,12 +7291,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Gnagspår i tallåga</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7292,44 +7306,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126335973</v>
+        <v>126334876</v>
       </c>
       <c r="B67" t="n">
-        <v>98269</v>
+        <v>78736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7339,13 +7353,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427023</v>
+        <v>427084</v>
       </c>
       <c r="R67" t="n">
-        <v>6798681</v>
+        <v>6798578</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7374,7 +7388,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7384,7 +7398,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7399,61 +7413,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126335072</v>
+        <v>126337872</v>
       </c>
       <c r="B68" t="n">
-        <v>98269</v>
+        <v>79566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219790</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427079</v>
+        <v>427103</v>
       </c>
       <c r="R68" t="n">
-        <v>6798569</v>
+        <v>6798836</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7483,19 +7493,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:33</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:33</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,12 +7510,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8898,7 +8898,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126335508</v>
+        <v>126337563</v>
       </c>
       <c r="B82" t="n">
         <v>78736</v>
@@ -8927,22 +8927,19 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427079</v>
+        <v>427101</v>
       </c>
       <c r="R82" t="n">
-        <v>6798512</v>
+        <v>6798845</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8969,52 +8966,36 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126337563</v>
+        <v>126335508</v>
       </c>
       <c r="B83" t="n">
         <v>78736</v>
@@ -9043,19 +9024,22 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427101</v>
+        <v>427079</v>
       </c>
       <c r="R83" t="n">
-        <v>6798845</v>
+        <v>6798512</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9082,29 +9066,45 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126337681</v>
+        <v>126333986</v>
       </c>
       <c r="B90" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427092</v>
+        <v>427095</v>
       </c>
       <c r="R90" t="n">
-        <v>6798859</v>
+        <v>6798448</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9840,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126333986</v>
+        <v>126337982</v>
       </c>
       <c r="B91" t="n">
-        <v>78977</v>
+        <v>78735</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9851,21 +9851,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427095</v>
+        <v>427138</v>
       </c>
       <c r="R91" t="n">
-        <v>6798448</v>
+        <v>6798830</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9908,9 +9908,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9937,32 +9947,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126337982</v>
+        <v>126335099</v>
       </c>
       <c r="B92" t="n">
-        <v>78735</v>
+        <v>98269</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9972,10 +9982,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427138</v>
+        <v>427044</v>
       </c>
       <c r="R92" t="n">
-        <v>6798830</v>
+        <v>6798644</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10005,19 +10015,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10044,45 +10044,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126335099</v>
+        <v>126335896</v>
       </c>
       <c r="B93" t="n">
-        <v>98269</v>
+        <v>78736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427044</v>
+        <v>426993</v>
       </c>
       <c r="R93" t="n">
-        <v>6798644</v>
+        <v>6798667</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,9 +10112,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10129,22 +10139,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126335896</v>
+        <v>126337681</v>
       </c>
       <c r="B94" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10152,34 +10162,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426993</v>
+        <v>427092</v>
       </c>
       <c r="R94" t="n">
-        <v>6798667</v>
+        <v>6798859</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10209,19 +10219,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10236,22 +10236,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126338455</v>
+        <v>126336279</v>
       </c>
       <c r="B95" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10283,13 +10283,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427173</v>
+        <v>427018</v>
       </c>
       <c r="R95" t="n">
-        <v>6798821</v>
+        <v>6798762</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10316,19 +10316,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10343,22 +10333,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126339416</v>
+        <v>126337979</v>
       </c>
       <c r="B96" t="n">
-        <v>78735</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10366,34 +10356,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427360</v>
+        <v>427138</v>
       </c>
       <c r="R96" t="n">
-        <v>6798573</v>
+        <v>6798830</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10425,7 +10415,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10435,7 +10425,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10450,22 +10440,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126336279</v>
+        <v>126338455</v>
       </c>
       <c r="B97" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10473,21 +10463,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10497,13 +10487,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427018</v>
+        <v>427173</v>
       </c>
       <c r="R97" t="n">
-        <v>6798762</v>
+        <v>6798821</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10530,9 +10520,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10547,22 +10547,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126337979</v>
+        <v>126339416</v>
       </c>
       <c r="B98" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10570,34 +10570,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427138</v>
+        <v>427360</v>
       </c>
       <c r="R98" t="n">
-        <v>6798830</v>
+        <v>6798573</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10654,12 +10654,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11833,10 +11833,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126338324</v>
+        <v>126337559</v>
       </c>
       <c r="B110" t="n">
-        <v>79566</v>
+        <v>79595</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11844,34 +11844,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427072</v>
+        <v>427047</v>
       </c>
       <c r="R110" t="n">
-        <v>6798879</v>
+        <v>6798896</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11928,22 +11928,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126339588</v>
+        <v>126338324</v>
       </c>
       <c r="B111" t="n">
-        <v>78736</v>
+        <v>79566</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,34 +11951,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427328</v>
+        <v>427072</v>
       </c>
       <c r="R111" t="n">
-        <v>6798426</v>
+        <v>6798879</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12035,19 +12035,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126337286</v>
+        <v>126339588</v>
       </c>
       <c r="B112" t="n">
         <v>78736</v>
@@ -12078,14 +12078,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427056</v>
+        <v>427328</v>
       </c>
       <c r="R112" t="n">
-        <v>6798834</v>
+        <v>6798426</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12142,22 +12142,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126337559</v>
+        <v>126337286</v>
       </c>
       <c r="B113" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12165,34 +12165,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427047</v>
+        <v>427056</v>
       </c>
       <c r="R113" t="n">
-        <v>6798896</v>
+        <v>6798834</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12249,12 +12249,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -14457,10 +14457,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126339616</v>
+        <v>126335603</v>
       </c>
       <c r="B135" t="n">
-        <v>78735</v>
+        <v>79566</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14468,34 +14468,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427329</v>
+        <v>427042</v>
       </c>
       <c r="R135" t="n">
-        <v>6798435</v>
+        <v>6798684</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14525,19 +14525,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14552,22 +14542,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126337227</v>
+        <v>126339616</v>
       </c>
       <c r="B136" t="n">
-        <v>79595</v>
+        <v>78735</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14575,34 +14565,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427067</v>
+        <v>427329</v>
       </c>
       <c r="R136" t="n">
-        <v>6798806</v>
+        <v>6798435</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14632,9 +14622,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14649,22 +14649,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126335337</v>
+        <v>126337227</v>
       </c>
       <c r="B137" t="n">
-        <v>58135</v>
+        <v>79595</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14672,42 +14672,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427023</v>
+        <v>427067</v>
       </c>
       <c r="R137" t="n">
-        <v>6798652</v>
+        <v>6798806</v>
       </c>
       <c r="S137" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14763,10 +14758,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126335603</v>
+        <v>126335337</v>
       </c>
       <c r="B138" t="n">
-        <v>79566</v>
+        <v>58135</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14774,37 +14769,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>229821</v>
+        <v>103018</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427042</v>
+        <v>427023</v>
       </c>
       <c r="R138" t="n">
-        <v>6798684</v>
+        <v>6798652</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126022304</v>
       </c>
       <c r="B2" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126022297</v>
       </c>
       <c r="B3" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126022294</v>
       </c>
       <c r="B4" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126022293</v>
       </c>
       <c r="B5" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126022306</v>
       </c>
       <c r="B6" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B7" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R7" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B8" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R8" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>126022299</v>
       </c>
       <c r="B9" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>126022290</v>
       </c>
       <c r="B10" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>126022291</v>
       </c>
       <c r="B11" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>126022301</v>
       </c>
       <c r="B12" t="n">
-        <v>91192</v>
+        <v>91195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>126022316</v>
       </c>
       <c r="B13" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>126022322</v>
       </c>
       <c r="B14" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>126022310</v>
       </c>
       <c r="B15" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>126022321</v>
       </c>
       <c r="B16" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>126022284</v>
       </c>
       <c r="B17" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>126022289</v>
       </c>
       <c r="B18" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78736</v>
+        <v>78647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R19" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78644</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R20" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
         <v>126022315</v>
       </c>
       <c r="B21" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>126022298</v>
       </c>
       <c r="B22" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>126022285</v>
       </c>
       <c r="B23" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>126022313</v>
       </c>
       <c r="B24" t="n">
-        <v>91715</v>
+        <v>91718</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>126022318</v>
       </c>
       <c r="B25" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022292</v>
+        <v>126022296</v>
       </c>
       <c r="B26" t="n">
-        <v>79595</v>
+        <v>79569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R26" t="n">
-        <v>6798570</v>
+        <v>6798596</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022296</v>
+        <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>79566</v>
+        <v>78739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798596</v>
+        <v>6798594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022312</v>
+        <v>126022292</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R28" t="n">
-        <v>6798594</v>
+        <v>6798570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3306,7 +3306,7 @@
         <v>126022288</v>
       </c>
       <c r="B29" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>126022317</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126340016</v>
+        <v>126340383</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>79569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,34 +3508,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427570</v>
+        <v>427116</v>
       </c>
       <c r="R31" t="n">
-        <v>6798393</v>
+        <v>6798627</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,22 +3592,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126340383</v>
+        <v>126339643</v>
       </c>
       <c r="B32" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427116</v>
+        <v>426885</v>
       </c>
       <c r="R32" t="n">
-        <v>6798627</v>
+        <v>6799018</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126339643</v>
+        <v>126340016</v>
       </c>
       <c r="B33" t="n">
-        <v>79566</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426885</v>
+        <v>427570</v>
       </c>
       <c r="R33" t="n">
-        <v>6799018</v>
+        <v>6798393</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3806,12 +3806,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>126335214</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>126334889</v>
       </c>
       <c r="B35" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>126339444</v>
       </c>
       <c r="B36" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>126340669</v>
       </c>
       <c r="B37" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>126338818</v>
       </c>
       <c r="B38" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>126338600</v>
       </c>
       <c r="B39" t="n">
-        <v>91503</v>
+        <v>91506</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>126339860</v>
       </c>
       <c r="B40" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>126334237</v>
       </c>
       <c r="B41" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>126337222</v>
       </c>
       <c r="B42" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>126336106</v>
       </c>
       <c r="B43" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126335181</v>
+        <v>126339934</v>
       </c>
       <c r="B44" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4899,14 +4899,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427044</v>
+        <v>427360</v>
       </c>
       <c r="R44" t="n">
-        <v>6798644</v>
+        <v>6798573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4936,9 +4936,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4953,22 +4963,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126339934</v>
+        <v>126335181</v>
       </c>
       <c r="B45" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4996,14 +5006,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427360</v>
+        <v>427044</v>
       </c>
       <c r="R45" t="n">
-        <v>6798573</v>
+        <v>6798644</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5033,19 +5043,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5060,22 +5060,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126334857</v>
+        <v>126337209</v>
       </c>
       <c r="B46" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5083,21 +5083,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5107,13 +5107,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427060</v>
+        <v>427026</v>
       </c>
       <c r="R46" t="n">
-        <v>6798612</v>
+        <v>6798692</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5167,22 +5167,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126337209</v>
+        <v>126334857</v>
       </c>
       <c r="B47" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5190,21 +5190,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5214,13 +5214,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427026</v>
+        <v>427060</v>
       </c>
       <c r="R47" t="n">
-        <v>6798692</v>
+        <v>6798612</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,61 +5274,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126340047</v>
+        <v>126334541</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
+        <v>78739</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427588</v>
+        <v>426962</v>
       </c>
       <c r="R48" t="n">
-        <v>6798380</v>
+        <v>6798805</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5360,7 +5356,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5370,12 +5366,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5384,64 +5375,67 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126334541</v>
+        <v>126340047</v>
       </c>
       <c r="B49" t="n">
-        <v>78736</v>
+        <v>98278</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>426962</v>
+        <v>427588</v>
       </c>
       <c r="R49" t="n">
-        <v>6798805</v>
+        <v>6798380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5473,7 +5467,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5483,7 +5477,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5492,18 +5491,19 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5513,7 +5513,7 @@
         <v>126340584</v>
       </c>
       <c r="B50" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>126336092</v>
       </c>
       <c r="B51" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>126335481</v>
       </c>
       <c r="B52" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5826,10 +5826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126339364</v>
+        <v>126339028</v>
       </c>
       <c r="B53" t="n">
-        <v>57653</v>
+        <v>78739</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,42 +5837,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427073</v>
+        <v>427113</v>
       </c>
       <c r="R53" t="n">
-        <v>6798822</v>
+        <v>6798674</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5899,9 +5894,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5916,22 +5921,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126339028</v>
+        <v>126339364</v>
       </c>
       <c r="B54" t="n">
-        <v>78736</v>
+        <v>57654</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5939,37 +5944,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427113</v>
+        <v>427073</v>
       </c>
       <c r="R54" t="n">
-        <v>6798674</v>
+        <v>6798822</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5996,19 +6006,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6023,12 +6023,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
         <v>126340128</v>
       </c>
       <c r="B55" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>126339407</v>
       </c>
       <c r="B56" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>126339573</v>
       </c>
       <c r="B57" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>126335625</v>
       </c>
       <c r="B58" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>126338668</v>
       </c>
       <c r="B59" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126334331</v>
+        <v>126339304</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6581,37 +6581,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427079</v>
+        <v>427299</v>
       </c>
       <c r="R60" t="n">
-        <v>6798569</v>
+        <v>6798540</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6665,22 +6665,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126339304</v>
+        <v>126337677</v>
       </c>
       <c r="B61" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6708,14 +6708,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427299</v>
+        <v>427092</v>
       </c>
       <c r="R61" t="n">
-        <v>6798540</v>
+        <v>6798859</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6745,19 +6745,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6772,22 +6762,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126337677</v>
+        <v>126340359</v>
       </c>
       <c r="B62" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6795,21 +6785,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6819,10 +6809,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427092</v>
+        <v>427116</v>
       </c>
       <c r="R62" t="n">
-        <v>6798859</v>
+        <v>6798627</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6852,9 +6842,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6881,10 +6881,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126340359</v>
+        <v>126334331</v>
       </c>
       <c r="B63" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6916,13 +6916,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427116</v>
+        <v>427079</v>
       </c>
       <c r="R63" t="n">
-        <v>6798627</v>
+        <v>6798569</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,12 +6976,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7103,7 +7103,7 @@
         <v>126335973</v>
       </c>
       <c r="B65" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>126335072</v>
       </c>
       <c r="B66" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>126334876</v>
       </c>
       <c r="B67" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>126337872</v>
       </c>
       <c r="B68" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7522,10 +7522,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126338801</v>
+        <v>126339529</v>
       </c>
       <c r="B69" t="n">
-        <v>78735</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,37 +7533,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426933</v>
+        <v>427360</v>
       </c>
       <c r="R69" t="n">
-        <v>6798926</v>
+        <v>6798574</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7590,19 +7590,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7617,22 +7607,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126340365</v>
+        <v>126338801</v>
       </c>
       <c r="B70" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7640,21 +7630,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7664,10 +7654,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427116</v>
+        <v>426933</v>
       </c>
       <c r="R70" t="n">
-        <v>6798627</v>
+        <v>6798926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7736,10 +7726,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126336082</v>
+        <v>126340365</v>
       </c>
       <c r="B71" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7767,17 +7757,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426993</v>
+        <v>427116</v>
       </c>
       <c r="R71" t="n">
-        <v>6798667</v>
+        <v>6798627</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7806,7 +7796,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7816,7 +7806,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7831,22 +7821,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126339773</v>
+        <v>126336082</v>
       </c>
       <c r="B72" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7878,13 +7868,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426959</v>
+        <v>426993</v>
       </c>
       <c r="R72" t="n">
-        <v>6798956</v>
+        <v>6798667</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7913,7 +7903,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7923,7 +7913,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7938,22 +7928,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126334052</v>
+        <v>126339773</v>
       </c>
       <c r="B73" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7985,10 +7975,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427079</v>
+        <v>426959</v>
       </c>
       <c r="R73" t="n">
-        <v>6798512</v>
+        <v>6798956</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8020,7 +8010,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8030,7 +8020,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8045,22 +8035,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126339757</v>
+        <v>126334052</v>
       </c>
       <c r="B74" t="n">
-        <v>78735</v>
+        <v>79598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8068,34 +8058,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426981</v>
+        <v>427079</v>
       </c>
       <c r="R74" t="n">
-        <v>6798995</v>
+        <v>6798512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8127,7 +8117,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8137,7 +8127,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8152,22 +8142,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126335972</v>
+        <v>126339757</v>
       </c>
       <c r="B75" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8175,34 +8165,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426988</v>
+        <v>426981</v>
       </c>
       <c r="R75" t="n">
-        <v>6798730</v>
+        <v>6798995</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8234,7 +8224,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8244,7 +8234,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8259,44 +8249,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126336097</v>
+        <v>126335972</v>
       </c>
       <c r="B76" t="n">
-        <v>98269</v>
+        <v>79598</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8306,10 +8296,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427038</v>
+        <v>426988</v>
       </c>
       <c r="R76" t="n">
-        <v>6798675</v>
+        <v>6798730</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8341,7 +8331,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8351,7 +8341,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8366,60 +8356,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126339529</v>
+        <v>126336097</v>
       </c>
       <c r="B77" t="n">
-        <v>79072</v>
+        <v>98278</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>967</v>
+        <v>219790</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427360</v>
+        <v>427038</v>
       </c>
       <c r="R77" t="n">
-        <v>6798574</v>
+        <v>6798675</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8446,9 +8436,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8463,12 +8463,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
         <v>126337748</v>
       </c>
       <c r="B78" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>126339121</v>
       </c>
       <c r="B79" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>126336234</v>
       </c>
       <c r="B80" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>126337970</v>
       </c>
       <c r="B81" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8898,10 +8898,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126337563</v>
+        <v>126335508</v>
       </c>
       <c r="B82" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8927,19 +8927,22 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427101</v>
+        <v>427079</v>
       </c>
       <c r="R82" t="n">
-        <v>6798845</v>
+        <v>6798512</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8966,39 +8969,55 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126335508</v>
+        <v>126337563</v>
       </c>
       <c r="B83" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9024,22 +9043,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427079</v>
+        <v>427101</v>
       </c>
       <c r="R83" t="n">
-        <v>6798512</v>
+        <v>6798845</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9066,55 +9082,39 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126335672</v>
+        <v>126337274</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>79569</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9122,34 +9122,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427042</v>
+        <v>427056</v>
       </c>
       <c r="R84" t="n">
-        <v>6798684</v>
+        <v>6798834</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9179,9 +9179,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9196,22 +9206,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126340385</v>
+        <v>126338430</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>78739</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9219,34 +9229,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427538</v>
+        <v>427157</v>
       </c>
       <c r="R85" t="n">
-        <v>6798367</v>
+        <v>6798766</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9278,7 +9288,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9288,7 +9298,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9303,22 +9313,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126338368</v>
+        <v>126340385</v>
       </c>
       <c r="B86" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9326,21 +9336,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9350,10 +9360,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427173</v>
+        <v>427538</v>
       </c>
       <c r="R86" t="n">
-        <v>6798821</v>
+        <v>6798367</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9385,7 +9395,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9395,7 +9405,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9422,10 +9432,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126337274</v>
+        <v>126338368</v>
       </c>
       <c r="B87" t="n">
-        <v>79566</v>
+        <v>78738</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9433,34 +9443,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427056</v>
+        <v>427173</v>
       </c>
       <c r="R87" t="n">
-        <v>6798834</v>
+        <v>6798821</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9492,7 +9502,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9502,7 +9512,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9517,22 +9527,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126338355</v>
+        <v>126335672</v>
       </c>
       <c r="B88" t="n">
-        <v>78736</v>
+        <v>78980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9540,34 +9550,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427171</v>
+        <v>427042</v>
       </c>
       <c r="R88" t="n">
-        <v>6798818</v>
+        <v>6798684</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9597,19 +9607,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9624,22 +9624,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126338430</v>
+        <v>126338355</v>
       </c>
       <c r="B89" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9667,14 +9667,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427157</v>
+        <v>427171</v>
       </c>
       <c r="R89" t="n">
-        <v>6798766</v>
+        <v>6798818</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9731,22 +9731,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126333986</v>
+        <v>126337982</v>
       </c>
       <c r="B90" t="n">
-        <v>78977</v>
+        <v>78738</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427095</v>
+        <v>427138</v>
       </c>
       <c r="R90" t="n">
-        <v>6798448</v>
+        <v>6798830</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9811,9 +9811,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9840,10 +9850,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126337982</v>
+        <v>126333986</v>
       </c>
       <c r="B91" t="n">
-        <v>78735</v>
+        <v>78980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9851,21 +9861,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9875,10 +9885,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427138</v>
+        <v>427095</v>
       </c>
       <c r="R91" t="n">
-        <v>6798830</v>
+        <v>6798448</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9908,19 +9918,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9950,7 +9950,7 @@
         <v>126335099</v>
       </c>
       <c r="B92" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10044,10 +10044,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126335896</v>
+        <v>126337681</v>
       </c>
       <c r="B93" t="n">
-        <v>78736</v>
+        <v>79569</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10055,34 +10055,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>426993</v>
+        <v>427092</v>
       </c>
       <c r="R93" t="n">
-        <v>6798667</v>
+        <v>6798859</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10112,19 +10112,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10139,22 +10129,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126337681</v>
+        <v>126335896</v>
       </c>
       <c r="B94" t="n">
-        <v>79566</v>
+        <v>78739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10162,34 +10152,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427092</v>
+        <v>426993</v>
       </c>
       <c r="R94" t="n">
-        <v>6798859</v>
+        <v>6798667</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10219,9 +10209,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10236,22 +10236,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126336279</v>
+        <v>126338455</v>
       </c>
       <c r="B95" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10283,13 +10283,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427018</v>
+        <v>427173</v>
       </c>
       <c r="R95" t="n">
-        <v>6798762</v>
+        <v>6798821</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10316,9 +10316,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10333,22 +10343,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126337979</v>
+        <v>126339416</v>
       </c>
       <c r="B96" t="n">
-        <v>78736</v>
+        <v>78738</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10356,34 +10366,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427138</v>
+        <v>427360</v>
       </c>
       <c r="R96" t="n">
-        <v>6798830</v>
+        <v>6798573</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10415,7 +10425,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10425,7 +10435,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10440,22 +10450,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126338455</v>
+        <v>126336279</v>
       </c>
       <c r="B97" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10463,21 +10473,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10487,13 +10497,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427173</v>
+        <v>427018</v>
       </c>
       <c r="R97" t="n">
-        <v>6798821</v>
+        <v>6798762</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10520,19 +10530,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10547,22 +10547,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126339416</v>
+        <v>126337979</v>
       </c>
       <c r="B98" t="n">
-        <v>78735</v>
+        <v>78739</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10570,34 +10570,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427360</v>
+        <v>427138</v>
       </c>
       <c r="R98" t="n">
-        <v>6798573</v>
+        <v>6798830</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10654,22 +10654,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126337016</v>
+        <v>126334576</v>
       </c>
       <c r="B99" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10677,21 +10677,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10701,13 +10701,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427012</v>
+        <v>427115</v>
       </c>
       <c r="R99" t="n">
-        <v>6798760</v>
+        <v>6798555</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10761,22 +10761,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126334576</v>
+        <v>126337810</v>
       </c>
       <c r="B100" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10804,17 +10804,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427115</v>
+        <v>427108</v>
       </c>
       <c r="R100" t="n">
-        <v>6798555</v>
+        <v>6798841</v>
       </c>
       <c r="S100" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10841,19 +10841,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10868,22 +10858,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126337810</v>
+        <v>126335762</v>
       </c>
       <c r="B101" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10911,17 +10901,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427108</v>
+        <v>426996</v>
       </c>
       <c r="R101" t="n">
-        <v>6798841</v>
+        <v>6798633</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10948,9 +10938,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10965,22 +10965,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126335762</v>
+        <v>126336252</v>
       </c>
       <c r="B102" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>426996</v>
+        <v>427008</v>
       </c>
       <c r="R102" t="n">
-        <v>6798633</v>
+        <v>6798762</v>
       </c>
       <c r="S102" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11045,19 +11045,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11072,22 +11062,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126336252</v>
+        <v>126338799</v>
       </c>
       <c r="B103" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11115,17 +11105,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427008</v>
+        <v>426933</v>
       </c>
       <c r="R103" t="n">
-        <v>6798762</v>
+        <v>6798926</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11152,9 +11142,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11169,22 +11169,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126338799</v>
+        <v>126337254</v>
       </c>
       <c r="B104" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11212,14 +11212,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>426933</v>
+        <v>427057</v>
       </c>
       <c r="R104" t="n">
-        <v>6798926</v>
+        <v>6798827</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11276,22 +11276,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126337254</v>
+        <v>126337016</v>
       </c>
       <c r="B105" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11299,34 +11299,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427057</v>
+        <v>427012</v>
       </c>
       <c r="R105" t="n">
-        <v>6798827</v>
+        <v>6798760</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11383,61 +11383,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126334915</v>
+        <v>126337975</v>
       </c>
       <c r="B106" t="n">
-        <v>98269</v>
+        <v>79598</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427060</v>
+        <v>427138</v>
       </c>
       <c r="R106" t="n">
-        <v>6798614</v>
+        <v>6798830</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11469,7 +11465,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11479,12 +11475,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11493,64 +11484,67 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126337975</v>
+        <v>126334915</v>
       </c>
       <c r="B107" t="n">
-        <v>79595</v>
+        <v>98278</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427138</v>
+        <v>427060</v>
       </c>
       <c r="R107" t="n">
-        <v>6798830</v>
+        <v>6798614</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11582,7 +11576,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11592,7 +11586,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11601,28 +11600,29 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126335795</v>
+        <v>126339015</v>
       </c>
       <c r="B108" t="n">
-        <v>78736</v>
+        <v>79569</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11630,34 +11630,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>426989</v>
+        <v>426894</v>
       </c>
       <c r="R108" t="n">
-        <v>6798666</v>
+        <v>6798935</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11714,22 +11714,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126339015</v>
+        <v>126335795</v>
       </c>
       <c r="B109" t="n">
-        <v>79566</v>
+        <v>78739</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11737,34 +11737,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>426894</v>
+        <v>426989</v>
       </c>
       <c r="R109" t="n">
-        <v>6798935</v>
+        <v>6798666</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11821,12 +11821,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11836,7 +11836,7 @@
         <v>126337559</v>
       </c>
       <c r="B110" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>126338324</v>
       </c>
       <c r="B111" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12047,10 +12047,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126339588</v>
+        <v>126337286</v>
       </c>
       <c r="B112" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12078,14 +12078,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427328</v>
+        <v>427056</v>
       </c>
       <c r="R112" t="n">
-        <v>6798426</v>
+        <v>6798834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12142,22 +12142,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126337286</v>
+        <v>126339588</v>
       </c>
       <c r="B113" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12185,14 +12185,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427056</v>
+        <v>427328</v>
       </c>
       <c r="R113" t="n">
-        <v>6798834</v>
+        <v>6798426</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12249,44 +12249,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126334762</v>
+        <v>126336022</v>
       </c>
       <c r="B114" t="n">
-        <v>78977</v>
+        <v>98278</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>426962</v>
+        <v>427026</v>
       </c>
       <c r="R114" t="n">
-        <v>6798805</v>
+        <v>6798688</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12341,12 +12341,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12361,22 +12356,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126338320</v>
+        <v>126338943</v>
       </c>
       <c r="B115" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12384,37 +12379,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427072</v>
+        <v>427026</v>
       </c>
       <c r="R115" t="n">
-        <v>6798879</v>
+        <v>6798692</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12443,7 +12438,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12453,7 +12448,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12468,22 +12463,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126339405</v>
+        <v>126339857</v>
       </c>
       <c r="B116" t="n">
-        <v>79595</v>
+        <v>78739</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12491,21 +12486,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12515,10 +12510,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>426855</v>
+        <v>427004</v>
       </c>
       <c r="R116" t="n">
-        <v>6798979</v>
+        <v>6798987</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12587,10 +12582,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126334554</v>
+        <v>126334762</v>
       </c>
       <c r="B117" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12598,21 +12593,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12622,10 +12617,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427075</v>
+        <v>426962</v>
       </c>
       <c r="R117" t="n">
-        <v>6798591</v>
+        <v>6798805</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12657,7 +12652,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12667,7 +12662,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12682,22 +12682,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126335754</v>
+        <v>126338320</v>
       </c>
       <c r="B118" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12723,19 +12723,16 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426984</v>
+        <v>427072</v>
       </c>
       <c r="R118" t="n">
-        <v>6798652</v>
+        <v>6798879</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12767,7 +12764,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12777,7 +12774,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12786,51 +12783,50 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126334241</v>
+        <v>126339405</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12840,10 +12836,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427095</v>
+        <v>426855</v>
       </c>
       <c r="R119" t="n">
-        <v>6798448</v>
+        <v>6798979</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12873,14 +12869,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12907,32 +12908,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126336022</v>
+        <v>126334554</v>
       </c>
       <c r="B120" t="n">
-        <v>98269</v>
+        <v>79598</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12942,10 +12943,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427026</v>
+        <v>427075</v>
       </c>
       <c r="R120" t="n">
-        <v>6798688</v>
+        <v>6798591</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12977,7 +12978,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12987,7 +12988,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13014,10 +13015,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126338943</v>
+        <v>126335754</v>
       </c>
       <c r="B121" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13025,37 +13026,40 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427026</v>
+        <v>426984</v>
       </c>
       <c r="R121" t="n">
-        <v>6798692</v>
+        <v>6798652</v>
       </c>
       <c r="S121" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13084,7 +13088,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13094,7 +13098,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13103,50 +13107,51 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126339857</v>
+        <v>126334241</v>
       </c>
       <c r="B122" t="n">
-        <v>78736</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13156,10 +13161,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427004</v>
+        <v>427095</v>
       </c>
       <c r="R122" t="n">
-        <v>6798987</v>
+        <v>6798448</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13189,19 +13194,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:44</t>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13228,10 +13228,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126335613</v>
+        <v>126335998</v>
       </c>
       <c r="B123" t="n">
-        <v>78736</v>
+        <v>79598</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13239,21 +13239,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427042</v>
+        <v>427015</v>
       </c>
       <c r="R123" t="n">
-        <v>6798684</v>
+        <v>6798754</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13325,10 +13325,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126338823</v>
+        <v>126335881</v>
       </c>
       <c r="B124" t="n">
-        <v>79566</v>
+        <v>78738</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13336,34 +13336,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426933</v>
+        <v>426993</v>
       </c>
       <c r="R124" t="n">
-        <v>6798926</v>
+        <v>6798667</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13420,22 +13420,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126335998</v>
+        <v>126339770</v>
       </c>
       <c r="B125" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13443,37 +13443,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427015</v>
+        <v>427450</v>
       </c>
       <c r="R125" t="n">
-        <v>6798754</v>
+        <v>6798525</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13517,22 +13517,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126335881</v>
+        <v>126335613</v>
       </c>
       <c r="B126" t="n">
-        <v>78735</v>
+        <v>78739</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13540,34 +13540,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426993</v>
+        <v>427042</v>
       </c>
       <c r="R126" t="n">
-        <v>6798667</v>
+        <v>6798684</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13597,19 +13597,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13624,22 +13614,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126339770</v>
+        <v>126338823</v>
       </c>
       <c r="B127" t="n">
-        <v>78735</v>
+        <v>79569</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13647,37 +13637,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427450</v>
+        <v>426933</v>
       </c>
       <c r="R127" t="n">
-        <v>6798525</v>
+        <v>6798926</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13704,9 +13694,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13721,12 +13721,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -13736,7 +13736,7 @@
         <v>126335594</v>
       </c>
       <c r="B128" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>126337688</v>
       </c>
       <c r="B129" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>126334548</v>
       </c>
       <c r="B130" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14034,10 +14034,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126335567</v>
+        <v>126335852</v>
       </c>
       <c r="B131" t="n">
-        <v>78736</v>
+        <v>57817</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14045,37 +14045,42 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427022</v>
+        <v>427053</v>
       </c>
       <c r="R131" t="n">
-        <v>6798674</v>
+        <v>6798729</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14102,19 +14107,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14129,22 +14124,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126335852</v>
+        <v>126335567</v>
       </c>
       <c r="B132" t="n">
-        <v>57816</v>
+        <v>78739</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14152,42 +14147,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427053</v>
+        <v>427022</v>
       </c>
       <c r="R132" t="n">
-        <v>6798729</v>
+        <v>6798674</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14214,9 +14204,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14231,12 +14231,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
         <v>126334764</v>
       </c>
       <c r="B133" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>126340434</v>
       </c>
       <c r="B134" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14457,10 +14457,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126335603</v>
+        <v>126335337</v>
       </c>
       <c r="B135" t="n">
-        <v>79566</v>
+        <v>58138</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14468,37 +14468,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>103018</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427042</v>
+        <v>427023</v>
       </c>
       <c r="R135" t="n">
-        <v>6798684</v>
+        <v>6798652</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14554,10 +14559,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126339616</v>
+        <v>126335603</v>
       </c>
       <c r="B136" t="n">
-        <v>78735</v>
+        <v>79569</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14565,34 +14570,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427329</v>
+        <v>427042</v>
       </c>
       <c r="R136" t="n">
-        <v>6798435</v>
+        <v>6798684</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14622,19 +14627,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14649,22 +14644,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126337227</v>
+        <v>126339616</v>
       </c>
       <c r="B137" t="n">
-        <v>79595</v>
+        <v>78738</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14672,34 +14667,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427067</v>
+        <v>427329</v>
       </c>
       <c r="R137" t="n">
-        <v>6798806</v>
+        <v>6798435</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14729,9 +14724,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14746,22 +14751,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126335337</v>
+        <v>126337227</v>
       </c>
       <c r="B138" t="n">
-        <v>58135</v>
+        <v>79598</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14769,42 +14774,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103018</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427023</v>
+        <v>427067</v>
       </c>
       <c r="R138" t="n">
-        <v>6798652</v>
+        <v>6798806</v>
       </c>
       <c r="S138" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>126364364</v>
       </c>
       <c r="B139" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>126366166</v>
       </c>
       <c r="B140" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>126364681</v>
       </c>
       <c r="B141" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>126365118</v>
       </c>
       <c r="B142" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>126377455</v>
       </c>
       <c r="B143" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>126377429</v>
       </c>
       <c r="B144" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15487,32 +15487,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126377421</v>
+        <v>126377431</v>
       </c>
       <c r="B145" t="n">
-        <v>79595</v>
+        <v>98382</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15522,10 +15522,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427122</v>
+        <v>427033</v>
       </c>
       <c r="R145" t="n">
-        <v>6798636</v>
+        <v>6798599</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -15558,6 +15558,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15584,32 +15589,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126377431</v>
+        <v>126377421</v>
       </c>
       <c r="B146" t="n">
-        <v>98373</v>
+        <v>79598</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15619,10 +15624,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427033</v>
+        <v>427122</v>
       </c>
       <c r="R146" t="n">
-        <v>6798599</v>
+        <v>6798636</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -15655,11 +15660,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15686,10 +15686,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126377425</v>
+        <v>126377508</v>
       </c>
       <c r="B147" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,21 +15697,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15721,10 +15721,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427080</v>
+        <v>427079</v>
       </c>
       <c r="R147" t="n">
-        <v>6798785</v>
+        <v>6798568</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15783,10 +15783,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126377508</v>
+        <v>126377425</v>
       </c>
       <c r="B148" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15794,21 +15794,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427079</v>
+        <v>427080</v>
       </c>
       <c r="R148" t="n">
-        <v>6798568</v>
+        <v>6798785</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15883,7 +15883,7 @@
         <v>126377459</v>
       </c>
       <c r="B149" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15980,7 +15980,7 @@
         <v>126377458</v>
       </c>
       <c r="B150" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16074,10 +16074,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126377479</v>
+        <v>126377457</v>
       </c>
       <c r="B151" t="n">
-        <v>78735</v>
+        <v>78739</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16085,21 +16085,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16109,10 +16109,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427035</v>
+        <v>427145</v>
       </c>
       <c r="R151" t="n">
-        <v>6798632</v>
+        <v>6798817</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -16171,10 +16171,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126377457</v>
+        <v>126377479</v>
       </c>
       <c r="B152" t="n">
-        <v>78736</v>
+        <v>78738</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427145</v>
+        <v>427035</v>
       </c>
       <c r="R152" t="n">
-        <v>6798817</v>
+        <v>6798632</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -16271,7 +16271,7 @@
         <v>126377423</v>
       </c>
       <c r="B153" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>126377456</v>
       </c>
       <c r="B154" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>126377507</v>
       </c>
       <c r="B155" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>126377424</v>
       </c>
       <c r="B156" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>126377478</v>
       </c>
       <c r="B157" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>126377427</v>
       </c>
       <c r="B158" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>126377430</v>
       </c>
       <c r="B159" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>126377426</v>
       </c>
       <c r="B160" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022322</v>
+        <v>126022310</v>
       </c>
       <c r="B14" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426961</v>
+        <v>426877</v>
       </c>
       <c r="R14" t="n">
-        <v>6798659</v>
+        <v>6798560</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022310</v>
+        <v>126022322</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426877</v>
+        <v>426961</v>
       </c>
       <c r="R15" t="n">
-        <v>6798560</v>
+        <v>6798659</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022296</v>
+        <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R26" t="n">
-        <v>6798596</v>
+        <v>6798570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022312</v>
+        <v>126022296</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>79569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798594</v>
+        <v>6798596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B28" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R28" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126335214</v>
+        <v>126334889</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3829,21 +3829,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427080</v>
+        <v>427084</v>
       </c>
       <c r="R34" t="n">
-        <v>6798606</v>
+        <v>6798578</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3913,19 +3913,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126334889</v>
+        <v>126339444</v>
       </c>
       <c r="B35" t="n">
         <v>79598</v>
@@ -3956,17 +3956,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427084</v>
+        <v>426858</v>
       </c>
       <c r="R35" t="n">
-        <v>6798578</v>
+        <v>6799009</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4020,22 +4020,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126339444</v>
+        <v>126340669</v>
       </c>
       <c r="B36" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4043,34 +4043,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>426858</v>
+        <v>427162</v>
       </c>
       <c r="R36" t="n">
-        <v>6799009</v>
+        <v>6798406</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4127,19 +4127,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126340669</v>
+        <v>126338818</v>
       </c>
       <c r="B37" t="n">
         <v>78738</v>
@@ -4170,14 +4170,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427162</v>
+        <v>427244</v>
       </c>
       <c r="R37" t="n">
-        <v>6798406</v>
+        <v>6798791</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4207,19 +4207,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4234,22 +4224,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126338818</v>
+        <v>126335214</v>
       </c>
       <c r="B38" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4257,37 +4247,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427244</v>
+        <v>427080</v>
       </c>
       <c r="R38" t="n">
-        <v>6798791</v>
+        <v>6798606</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4314,9 +4304,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4331,12 +4331,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126339028</v>
+        <v>126339364</v>
       </c>
       <c r="B53" t="n">
-        <v>78739</v>
+        <v>57654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,37 +5837,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427113</v>
+        <v>427073</v>
       </c>
       <c r="R53" t="n">
-        <v>6798674</v>
+        <v>6798822</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5894,19 +5899,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5921,22 +5916,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126339364</v>
+        <v>126339028</v>
       </c>
       <c r="B54" t="n">
-        <v>57654</v>
+        <v>78739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,42 +5939,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427073</v>
+        <v>427113</v>
       </c>
       <c r="R54" t="n">
-        <v>6798822</v>
+        <v>6798674</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6006,9 +5996,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6023,12 +6023,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6570,32 +6570,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126339304</v>
+        <v>126335973</v>
       </c>
       <c r="B60" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427299</v>
+        <v>427023</v>
       </c>
       <c r="R60" t="n">
-        <v>6798540</v>
+        <v>6798681</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6677,48 +6677,52 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126337677</v>
+        <v>126335072</v>
       </c>
       <c r="B61" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427092</v>
+        <v>427079</v>
       </c>
       <c r="R61" t="n">
-        <v>6798859</v>
+        <v>6798569</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6745,9 +6749,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6762,22 +6776,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126340359</v>
+        <v>126334876</v>
       </c>
       <c r="B62" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6785,37 +6799,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427116</v>
+        <v>427084</v>
       </c>
       <c r="R62" t="n">
-        <v>6798627</v>
+        <v>6798578</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6844,7 +6858,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6854,7 +6868,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6869,22 +6883,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126334331</v>
+        <v>126337872</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6892,34 +6906,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427079</v>
+        <v>427103</v>
       </c>
       <c r="R63" t="n">
-        <v>6798569</v>
+        <v>6798836</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6949,19 +6963,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6976,44 +6980,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126335831</v>
+        <v>126339304</v>
       </c>
       <c r="B64" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7023,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427005</v>
+        <v>427299</v>
       </c>
       <c r="R64" t="n">
-        <v>6798710</v>
+        <v>6798540</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7058,7 +7062,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7068,12 +7072,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Gnagspår i tallåga</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7088,57 +7087,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126335973</v>
+        <v>126337677</v>
       </c>
       <c r="B65" t="n">
-        <v>98278</v>
+        <v>79598</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427023</v>
+        <v>427092</v>
       </c>
       <c r="R65" t="n">
-        <v>6798681</v>
+        <v>6798859</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7168,19 +7167,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7195,64 +7184,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126335072</v>
+        <v>126340359</v>
       </c>
       <c r="B66" t="n">
-        <v>98278</v>
+        <v>78738</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427079</v>
+        <v>427116</v>
       </c>
       <c r="R66" t="n">
-        <v>6798569</v>
+        <v>6798627</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7281,7 +7266,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7291,7 +7276,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7306,22 +7291,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126334876</v>
+        <v>126334331</v>
       </c>
       <c r="B67" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7329,34 +7314,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427084</v>
+        <v>427079</v>
       </c>
       <c r="R67" t="n">
-        <v>6798578</v>
+        <v>6798569</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7388,7 +7373,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7398,7 +7383,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7413,60 +7398,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126337872</v>
+        <v>126335831</v>
       </c>
       <c r="B68" t="n">
-        <v>79569</v>
+        <v>8447</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427103</v>
+        <v>427005</v>
       </c>
       <c r="R68" t="n">
-        <v>6798836</v>
+        <v>6798710</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7493,9 +7478,24 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,12 +7510,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -9111,10 +9111,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126337274</v>
+        <v>126338355</v>
       </c>
       <c r="B84" t="n">
-        <v>79569</v>
+        <v>78739</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9122,34 +9122,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427056</v>
+        <v>427171</v>
       </c>
       <c r="R84" t="n">
-        <v>6798834</v>
+        <v>6798818</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9206,22 +9206,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126338430</v>
+        <v>126337274</v>
       </c>
       <c r="B85" t="n">
-        <v>78739</v>
+        <v>79569</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9229,34 +9229,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427157</v>
+        <v>427056</v>
       </c>
       <c r="R85" t="n">
-        <v>6798766</v>
+        <v>6798834</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9313,22 +9313,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126340385</v>
+        <v>126338430</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9336,34 +9336,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427538</v>
+        <v>427157</v>
       </c>
       <c r="R86" t="n">
-        <v>6798367</v>
+        <v>6798766</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9420,22 +9420,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126338368</v>
+        <v>126340385</v>
       </c>
       <c r="B87" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9443,21 +9443,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9467,10 +9467,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427173</v>
+        <v>427538</v>
       </c>
       <c r="R87" t="n">
-        <v>6798821</v>
+        <v>6798367</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9539,10 +9539,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126335672</v>
+        <v>126338368</v>
       </c>
       <c r="B88" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9550,34 +9550,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427042</v>
+        <v>427173</v>
       </c>
       <c r="R88" t="n">
-        <v>6798684</v>
+        <v>6798821</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9607,9 +9607,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9624,22 +9634,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126338355</v>
+        <v>126335672</v>
       </c>
       <c r="B89" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9647,34 +9657,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427171</v>
+        <v>427042</v>
       </c>
       <c r="R89" t="n">
-        <v>6798818</v>
+        <v>6798684</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9704,19 +9714,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9731,12 +9731,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9850,10 +9850,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126333986</v>
+        <v>126337681</v>
       </c>
       <c r="B91" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9861,21 +9861,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9885,10 +9885,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427095</v>
+        <v>427092</v>
       </c>
       <c r="R91" t="n">
-        <v>6798448</v>
+        <v>6798859</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9947,45 +9947,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126335099</v>
+        <v>126335896</v>
       </c>
       <c r="B92" t="n">
-        <v>98278</v>
+        <v>78739</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427044</v>
+        <v>426993</v>
       </c>
       <c r="R92" t="n">
-        <v>6798644</v>
+        <v>6798667</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10015,9 +10015,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10032,22 +10042,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126337681</v>
+        <v>126333986</v>
       </c>
       <c r="B93" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10055,21 +10065,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10079,10 +10089,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427092</v>
+        <v>427095</v>
       </c>
       <c r="R93" t="n">
-        <v>6798859</v>
+        <v>6798448</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10141,45 +10151,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126335896</v>
+        <v>126335099</v>
       </c>
       <c r="B94" t="n">
-        <v>78739</v>
+        <v>98278</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>426993</v>
+        <v>427044</v>
       </c>
       <c r="R94" t="n">
-        <v>6798667</v>
+        <v>6798644</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10209,19 +10219,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10236,12 +10236,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11395,45 +11395,49 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126337975</v>
+        <v>126334915</v>
       </c>
       <c r="B106" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427138</v>
+        <v>427060</v>
       </c>
       <c r="R106" t="n">
-        <v>6798830</v>
+        <v>6798614</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11465,7 +11469,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11475,7 +11479,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11484,67 +11493,64 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126334915</v>
+        <v>126337975</v>
       </c>
       <c r="B107" t="n">
-        <v>98278</v>
+        <v>79598</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427060</v>
+        <v>427138</v>
       </c>
       <c r="R107" t="n">
-        <v>6798614</v>
+        <v>6798830</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11576,7 +11582,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11586,12 +11592,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11600,19 +11601,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12261,45 +12261,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126336022</v>
+        <v>126338320</v>
       </c>
       <c r="B114" t="n">
-        <v>98278</v>
+        <v>79598</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427026</v>
+        <v>427072</v>
       </c>
       <c r="R114" t="n">
-        <v>6798688</v>
+        <v>6798879</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12356,22 +12356,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126338943</v>
+        <v>126339405</v>
       </c>
       <c r="B115" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12379,37 +12379,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427026</v>
+        <v>426855</v>
       </c>
       <c r="R115" t="n">
-        <v>6798692</v>
+        <v>6798979</v>
       </c>
       <c r="S115" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12463,22 +12463,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126339857</v>
+        <v>126334554</v>
       </c>
       <c r="B116" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12486,34 +12486,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427004</v>
+        <v>427075</v>
       </c>
       <c r="R116" t="n">
-        <v>6798987</v>
+        <v>6798591</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12570,22 +12570,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126334762</v>
+        <v>126335754</v>
       </c>
       <c r="B117" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12593,34 +12593,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426962</v>
+        <v>426984</v>
       </c>
       <c r="R117" t="n">
-        <v>6798805</v>
+        <v>6798652</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12652,7 +12655,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12662,12 +12665,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12676,28 +12674,29 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126338320</v>
+        <v>126334762</v>
       </c>
       <c r="B118" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12705,34 +12704,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427072</v>
+        <v>426962</v>
       </c>
       <c r="R118" t="n">
-        <v>6798879</v>
+        <v>6798805</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12764,7 +12763,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12774,7 +12773,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12789,44 +12793,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126339405</v>
+        <v>126334241</v>
       </c>
       <c r="B119" t="n">
-        <v>79598</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12836,10 +12840,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426855</v>
+        <v>427095</v>
       </c>
       <c r="R119" t="n">
-        <v>6798979</v>
+        <v>6798448</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12869,19 +12873,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:44</t>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12908,10 +12907,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126334554</v>
+        <v>126338943</v>
       </c>
       <c r="B120" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12919,21 +12918,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12943,13 +12942,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427075</v>
+        <v>427026</v>
       </c>
       <c r="R120" t="n">
-        <v>6798591</v>
+        <v>6798692</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12978,7 +12977,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12988,7 +12987,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13003,60 +13002,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126335754</v>
+        <v>126336022</v>
       </c>
       <c r="B121" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426984</v>
+        <v>427026</v>
       </c>
       <c r="R121" t="n">
-        <v>6798652</v>
+        <v>6798688</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13088,7 +13084,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13098,7 +13094,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13107,7 +13103,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13126,32 +13121,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126334241</v>
+        <v>126339857</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13161,10 +13156,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427095</v>
+        <v>427004</v>
       </c>
       <c r="R122" t="n">
-        <v>6798448</v>
+        <v>6798987</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13194,14 +13189,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13733,10 +13733,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126335594</v>
+        <v>126335852</v>
       </c>
       <c r="B128" t="n">
-        <v>79598</v>
+        <v>57817</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13744,37 +13744,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427042</v>
+        <v>427053</v>
       </c>
       <c r="R128" t="n">
-        <v>6798684</v>
+        <v>6798729</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13830,10 +13835,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126337688</v>
+        <v>126335567</v>
       </c>
       <c r="B129" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13841,34 +13846,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427092</v>
+        <v>427022</v>
       </c>
       <c r="R129" t="n">
-        <v>6798859</v>
+        <v>6798674</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13898,9 +13903,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13915,19 +13930,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126334548</v>
+        <v>126335594</v>
       </c>
       <c r="B130" t="n">
         <v>79598</v>
@@ -13958,14 +13973,14 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>426962</v>
+        <v>427042</v>
       </c>
       <c r="R130" t="n">
-        <v>6798805</v>
+        <v>6798684</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13995,19 +14010,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14022,22 +14027,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126335852</v>
+        <v>126337688</v>
       </c>
       <c r="B131" t="n">
-        <v>57817</v>
+        <v>78738</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14045,42 +14050,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427053</v>
+        <v>427092</v>
       </c>
       <c r="R131" t="n">
-        <v>6798729</v>
+        <v>6798859</v>
       </c>
       <c r="S131" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14136,10 +14136,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126335567</v>
+        <v>126334548</v>
       </c>
       <c r="B132" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14147,21 +14147,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14171,10 +14171,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427022</v>
+        <v>426962</v>
       </c>
       <c r="R132" t="n">
-        <v>6798674</v>
+        <v>6798805</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14231,22 +14231,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126334764</v>
+        <v>126339616</v>
       </c>
       <c r="B133" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14254,21 +14254,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427055</v>
+        <v>427329</v>
       </c>
       <c r="R133" t="n">
-        <v>6798616</v>
+        <v>6798435</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14313,7 +14313,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14350,10 +14350,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126340434</v>
+        <v>126337227</v>
       </c>
       <c r="B134" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14361,34 +14361,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427486</v>
+        <v>427067</v>
       </c>
       <c r="R134" t="n">
-        <v>6798404</v>
+        <v>6798806</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14418,19 +14418,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14445,22 +14435,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126335337</v>
+        <v>126334764</v>
       </c>
       <c r="B135" t="n">
-        <v>58138</v>
+        <v>78980</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14468,42 +14458,37 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427023</v>
+        <v>427055</v>
       </c>
       <c r="R135" t="n">
-        <v>6798652</v>
+        <v>6798616</v>
       </c>
       <c r="S135" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14530,9 +14515,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14547,22 +14542,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126335603</v>
+        <v>126340434</v>
       </c>
       <c r="B136" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14570,34 +14565,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427042</v>
+        <v>427486</v>
       </c>
       <c r="R136" t="n">
-        <v>6798684</v>
+        <v>6798404</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14627,9 +14622,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14644,22 +14649,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126339616</v>
+        <v>126335603</v>
       </c>
       <c r="B137" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14667,34 +14672,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427329</v>
+        <v>427042</v>
       </c>
       <c r="R137" t="n">
-        <v>6798435</v>
+        <v>6798684</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14724,19 +14729,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14751,22 +14746,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126337227</v>
+        <v>126335337</v>
       </c>
       <c r="B138" t="n">
-        <v>79598</v>
+        <v>58138</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14774,37 +14769,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427067</v>
+        <v>427023</v>
       </c>
       <c r="R138" t="n">
-        <v>6798806</v>
+        <v>6798652</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126022303</v>
+        <v>126022309</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426807</v>
+        <v>426813</v>
       </c>
       <c r="R7" t="n">
-        <v>6798629</v>
+        <v>6798701</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126022309</v>
+        <v>126022303</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426813</v>
+        <v>426807</v>
       </c>
       <c r="R8" t="n">
-        <v>6798701</v>
+        <v>6798629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126022310</v>
+        <v>126022322</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426877</v>
+        <v>426961</v>
       </c>
       <c r="R14" t="n">
-        <v>6798560</v>
+        <v>6798659</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1945,10 +1945,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126022322</v>
+        <v>126022310</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1956,21 +1956,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426961</v>
+        <v>426877</v>
       </c>
       <c r="R15" t="n">
-        <v>6798659</v>
+        <v>6798560</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B19" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R19" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R20" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R26" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022296</v>
+        <v>126022292</v>
       </c>
       <c r="B27" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R27" t="n">
-        <v>6798596</v>
+        <v>6798570</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,10 +3206,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126022312</v>
+        <v>126022296</v>
       </c>
       <c r="B28" t="n">
-        <v>78739</v>
+        <v>79569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3217,21 +3217,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3244,7 +3244,7 @@
         <v>426982</v>
       </c>
       <c r="R28" t="n">
-        <v>6798594</v>
+        <v>6798596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126340383</v>
+        <v>126340016</v>
       </c>
       <c r="B31" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,34 +3508,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427116</v>
+        <v>427570</v>
       </c>
       <c r="R31" t="n">
-        <v>6798627</v>
+        <v>6798393</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,19 +3592,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126339643</v>
+        <v>126340383</v>
       </c>
       <c r="B32" t="n">
         <v>79569</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>426885</v>
+        <v>427116</v>
       </c>
       <c r="R32" t="n">
-        <v>6799018</v>
+        <v>6798627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126340016</v>
+        <v>126339643</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427570</v>
+        <v>426885</v>
       </c>
       <c r="R33" t="n">
-        <v>6798393</v>
+        <v>6799018</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3806,12 +3806,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126338818</v>
+        <v>126335214</v>
       </c>
       <c r="B37" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4150,37 +4150,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427244</v>
+        <v>427080</v>
       </c>
       <c r="R37" t="n">
-        <v>6798791</v>
+        <v>6798606</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4207,9 +4207,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4224,22 +4234,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126335214</v>
+        <v>126338818</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>78738</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4247,37 +4257,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427080</v>
+        <v>427244</v>
       </c>
       <c r="R38" t="n">
-        <v>6798606</v>
+        <v>6798791</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4304,19 +4314,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>11:38</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>11:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4331,44 +4331,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126338600</v>
+        <v>126337222</v>
       </c>
       <c r="B39" t="n">
-        <v>91506</v>
+        <v>79569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>426972</v>
+        <v>427067</v>
       </c>
       <c r="R39" t="n">
-        <v>6798921</v>
+        <v>6798806</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4411,19 +4411,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4450,10 +4440,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126339860</v>
+        <v>126336106</v>
       </c>
       <c r="B40" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,34 +4451,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427301</v>
+        <v>426970</v>
       </c>
       <c r="R40" t="n">
-        <v>6798343</v>
+        <v>6798728</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4520,7 +4510,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4530,7 +4520,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4545,60 +4535,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126334237</v>
+        <v>126338600</v>
       </c>
       <c r="B41" t="n">
-        <v>79598</v>
+        <v>91506</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427084</v>
+        <v>426972</v>
       </c>
       <c r="R41" t="n">
-        <v>6798524</v>
+        <v>6798921</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4627,7 +4617,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4637,7 +4627,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4652,22 +4642,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126337222</v>
+        <v>126339860</v>
       </c>
       <c r="B42" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,34 +4665,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427067</v>
+        <v>427301</v>
       </c>
       <c r="R42" t="n">
-        <v>6798806</v>
+        <v>6798343</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4732,9 +4722,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4749,22 +4749,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126336106</v>
+        <v>126334237</v>
       </c>
       <c r="B43" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>426970</v>
+        <v>427084</v>
       </c>
       <c r="R43" t="n">
-        <v>6798728</v>
+        <v>6798524</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4856,12 +4856,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5072,48 +5072,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126337209</v>
+        <v>126340047</v>
       </c>
       <c r="B46" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427026</v>
+        <v>427588</v>
       </c>
       <c r="R46" t="n">
-        <v>6798692</v>
+        <v>6798380</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5142,7 +5146,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5152,7 +5156,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,28 +5170,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126334857</v>
+        <v>126334541</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5190,21 +5200,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5214,10 +5224,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427060</v>
+        <v>426962</v>
       </c>
       <c r="R47" t="n">
-        <v>6798612</v>
+        <v>6798805</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5249,7 +5259,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5259,7 +5269,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5274,22 +5284,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126334541</v>
+        <v>126337209</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5297,21 +5307,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5321,13 +5331,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>426962</v>
+        <v>427026</v>
       </c>
       <c r="R48" t="n">
-        <v>6798805</v>
+        <v>6798692</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5356,7 +5366,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5366,7 +5376,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5381,61 +5391,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126340047</v>
+        <v>126334857</v>
       </c>
       <c r="B49" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427588</v>
+        <v>427060</v>
       </c>
       <c r="R49" t="n">
-        <v>6798380</v>
+        <v>6798612</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5467,7 +5473,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5477,12 +5483,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Våt sänka, högörtsgranskog med lite äldre tallar och granar.</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5491,7 +5492,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126340584</v>
+        <v>126339364</v>
       </c>
       <c r="B50" t="n">
-        <v>78738</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,34 +5521,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427242</v>
+        <v>427073</v>
       </c>
       <c r="R50" t="n">
-        <v>6798350</v>
+        <v>6798822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,19 +5583,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,22 +5600,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126336092</v>
+        <v>126339028</v>
       </c>
       <c r="B51" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5628,37 +5623,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427026</v>
+        <v>427113</v>
       </c>
       <c r="R51" t="n">
-        <v>6798692</v>
+        <v>6798674</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5697,7 +5692,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5712,22 +5707,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126335481</v>
+        <v>126340584</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>78738</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5735,39 +5730,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427042</v>
+        <v>427242</v>
       </c>
       <c r="R52" t="n">
-        <v>6798684</v>
+        <v>6798350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5797,9 +5787,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5814,22 +5814,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126339364</v>
+        <v>126336092</v>
       </c>
       <c r="B53" t="n">
-        <v>57654</v>
+        <v>78738</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,42 +5837,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427073</v>
+        <v>427026</v>
       </c>
       <c r="R53" t="n">
-        <v>6798822</v>
+        <v>6798692</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5899,9 +5894,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5916,22 +5921,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126339028</v>
+        <v>126335481</v>
       </c>
       <c r="B54" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5939,37 +5944,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427113</v>
+        <v>427042</v>
       </c>
       <c r="R54" t="n">
-        <v>6798674</v>
+        <v>6798684</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5996,19 +6006,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6023,12 +6023,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126339407</v>
+        <v>126338668</v>
       </c>
       <c r="B56" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6153,34 +6153,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427359</v>
+        <v>426958</v>
       </c>
       <c r="R56" t="n">
-        <v>6798572</v>
+        <v>6798928</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6237,22 +6237,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126339573</v>
+        <v>126335625</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>96614</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6260,21 +6260,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6284,13 +6284,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>426933</v>
+        <v>427079</v>
       </c>
       <c r="R57" t="n">
-        <v>6798926</v>
+        <v>6798569</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,22 +6344,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126335625</v>
+        <v>126339407</v>
       </c>
       <c r="B58" t="n">
-        <v>96614</v>
+        <v>78739</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6367,37 +6367,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427079</v>
+        <v>427359</v>
       </c>
       <c r="R58" t="n">
-        <v>6798569</v>
+        <v>6798572</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6451,22 +6451,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126338668</v>
+        <v>126339573</v>
       </c>
       <c r="B59" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6474,21 +6474,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426958</v>
+        <v>426933</v>
       </c>
       <c r="R59" t="n">
-        <v>6798928</v>
+        <v>6798926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126335973</v>
+        <v>126335831</v>
       </c>
       <c r="B60" t="n">
-        <v>98278</v>
+        <v>8447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6581,21 +6581,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219790</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427023</v>
+        <v>427005</v>
       </c>
       <c r="R60" t="n">
-        <v>6798681</v>
+        <v>6798710</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6650,7 +6650,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6665,19 +6670,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126335072</v>
+        <v>126335973</v>
       </c>
       <c r="B61" t="n">
         <v>98278</v>
@@ -6705,24 +6710,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427079</v>
+        <v>427023</v>
       </c>
       <c r="R61" t="n">
-        <v>6798569</v>
+        <v>6798681</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6751,7 +6752,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6761,7 +6762,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6776,57 +6777,61 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126334876</v>
+        <v>126335072</v>
       </c>
       <c r="B62" t="n">
-        <v>78739</v>
+        <v>98278</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427084</v>
+        <v>427079</v>
       </c>
       <c r="R62" t="n">
-        <v>6798578</v>
+        <v>6798569</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6858,7 +6863,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -6868,7 +6873,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6883,22 +6888,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126337872</v>
+        <v>126334331</v>
       </c>
       <c r="B63" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6906,34 +6911,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427103</v>
+        <v>427079</v>
       </c>
       <c r="R63" t="n">
-        <v>6798836</v>
+        <v>6798569</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6963,9 +6968,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6980,12 +6995,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7303,10 +7318,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126334331</v>
+        <v>126334876</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7314,34 +7329,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427079</v>
+        <v>427084</v>
       </c>
       <c r="R67" t="n">
-        <v>6798569</v>
+        <v>6798578</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7373,7 +7388,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7383,7 +7398,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7398,60 +7413,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126335831</v>
+        <v>126337872</v>
       </c>
       <c r="B68" t="n">
-        <v>8447</v>
+        <v>79569</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427005</v>
+        <v>427103</v>
       </c>
       <c r="R68" t="n">
-        <v>6798710</v>
+        <v>6798836</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7478,24 +7493,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gnagspår i tallåga</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7510,22 +7510,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126339529</v>
+        <v>126338801</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>78738</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,37 +7533,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427360</v>
+        <v>426933</v>
       </c>
       <c r="R69" t="n">
-        <v>6798574</v>
+        <v>6798926</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7590,9 +7590,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,22 +7617,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126338801</v>
+        <v>126340365</v>
       </c>
       <c r="B70" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7630,21 +7640,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7654,10 +7664,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426933</v>
+        <v>427116</v>
       </c>
       <c r="R70" t="n">
-        <v>6798926</v>
+        <v>6798627</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7726,7 +7736,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126340365</v>
+        <v>126336082</v>
       </c>
       <c r="B71" t="n">
         <v>79598</v>
@@ -7757,17 +7767,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427116</v>
+        <v>426993</v>
       </c>
       <c r="R71" t="n">
-        <v>6798627</v>
+        <v>6798667</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7796,7 +7806,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7806,7 +7816,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7821,19 +7831,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126336082</v>
+        <v>126339773</v>
       </c>
       <c r="B72" t="n">
         <v>79598</v>
@@ -7868,13 +7878,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426993</v>
+        <v>426959</v>
       </c>
       <c r="R72" t="n">
-        <v>6798667</v>
+        <v>6798956</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7903,7 +7913,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7913,7 +7923,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7928,19 +7938,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126339773</v>
+        <v>126334052</v>
       </c>
       <c r="B73" t="n">
         <v>79598</v>
@@ -7975,10 +7985,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426959</v>
+        <v>427079</v>
       </c>
       <c r="R73" t="n">
-        <v>6798956</v>
+        <v>6798512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,7 +8020,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8020,7 +8030,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8035,22 +8045,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126334052</v>
+        <v>126339757</v>
       </c>
       <c r="B74" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,34 +8068,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427079</v>
+        <v>426981</v>
       </c>
       <c r="R74" t="n">
-        <v>6798512</v>
+        <v>6798995</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8117,7 +8127,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8127,7 +8137,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,22 +8152,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126339757</v>
+        <v>126335972</v>
       </c>
       <c r="B75" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8165,34 +8175,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426981</v>
+        <v>426988</v>
       </c>
       <c r="R75" t="n">
-        <v>6798995</v>
+        <v>6798730</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8224,7 +8234,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8234,7 +8244,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8249,22 +8259,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126335972</v>
+        <v>126339529</v>
       </c>
       <c r="B76" t="n">
-        <v>79598</v>
+        <v>79075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8272,37 +8282,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426988</v>
+        <v>427360</v>
       </c>
       <c r="R76" t="n">
-        <v>6798730</v>
+        <v>6798574</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8329,19 +8339,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8356,12 +8356,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8475,10 +8475,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126337748</v>
+        <v>126335508</v>
       </c>
       <c r="B78" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8486,37 +8486,40 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427082</v>
+        <v>427079</v>
       </c>
       <c r="R78" t="n">
-        <v>6798910</v>
+        <v>6798512</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8545,7 +8548,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8555,7 +8558,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8564,6 +8572,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8582,10 +8591,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126339121</v>
+        <v>126337563</v>
       </c>
       <c r="B79" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8593,34 +8602,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427243</v>
+        <v>427101</v>
       </c>
       <c r="R79" t="n">
-        <v>6798666</v>
+        <v>6798845</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8650,19 +8659,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8677,22 +8676,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126336234</v>
+        <v>126337748</v>
       </c>
       <c r="B80" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8700,21 +8699,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8724,13 +8723,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427008</v>
+        <v>427082</v>
       </c>
       <c r="R80" t="n">
-        <v>6798762</v>
+        <v>6798910</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8757,9 +8756,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8774,22 +8783,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126337970</v>
+        <v>126339121</v>
       </c>
       <c r="B81" t="n">
-        <v>57654</v>
+        <v>79598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8797,39 +8806,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427138</v>
+        <v>427243</v>
       </c>
       <c r="R81" t="n">
-        <v>6798830</v>
+        <v>6798666</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8861,7 +8865,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8871,7 +8875,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8886,22 +8890,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126335508</v>
+        <v>126336234</v>
       </c>
       <c r="B82" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8909,37 +8913,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427079</v>
+        <v>427008</v>
       </c>
       <c r="R82" t="n">
-        <v>6798512</v>
+        <v>6798762</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -8969,55 +8970,39 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126337563</v>
+        <v>126337970</v>
       </c>
       <c r="B83" t="n">
-        <v>78739</v>
+        <v>57654</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9025,34 +9010,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427101</v>
+        <v>427138</v>
       </c>
       <c r="R83" t="n">
-        <v>6798845</v>
+        <v>6798830</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9082,9 +9072,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9099,22 +9099,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126338355</v>
+        <v>126335672</v>
       </c>
       <c r="B84" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9122,34 +9122,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427171</v>
+        <v>427042</v>
       </c>
       <c r="R84" t="n">
-        <v>6798818</v>
+        <v>6798684</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9179,19 +9179,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9206,22 +9196,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126337274</v>
+        <v>126340385</v>
       </c>
       <c r="B85" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9229,34 +9219,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427056</v>
+        <v>427538</v>
       </c>
       <c r="R85" t="n">
-        <v>6798834</v>
+        <v>6798367</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9288,7 +9278,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9298,7 +9288,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9313,22 +9303,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126338430</v>
+        <v>126338368</v>
       </c>
       <c r="B86" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9336,34 +9326,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427157</v>
+        <v>427173</v>
       </c>
       <c r="R86" t="n">
-        <v>6798766</v>
+        <v>6798821</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9395,7 +9385,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9405,7 +9395,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9420,22 +9410,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126340385</v>
+        <v>126338355</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9443,21 +9433,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9467,10 +9457,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427538</v>
+        <v>427171</v>
       </c>
       <c r="R87" t="n">
-        <v>6798367</v>
+        <v>6798818</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9502,7 +9492,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9512,7 +9502,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9539,10 +9529,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126338368</v>
+        <v>126337274</v>
       </c>
       <c r="B88" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9550,34 +9540,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427173</v>
+        <v>427056</v>
       </c>
       <c r="R88" t="n">
-        <v>6798821</v>
+        <v>6798834</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9609,7 +9599,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9619,7 +9609,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9634,22 +9624,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126335672</v>
+        <v>126338430</v>
       </c>
       <c r="B89" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9657,21 +9647,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9681,10 +9671,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427042</v>
+        <v>427157</v>
       </c>
       <c r="R89" t="n">
-        <v>6798684</v>
+        <v>6798766</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9714,9 +9704,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9731,22 +9731,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126337982</v>
+        <v>126333986</v>
       </c>
       <c r="B90" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9754,21 +9754,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9778,10 +9778,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427138</v>
+        <v>427095</v>
       </c>
       <c r="R90" t="n">
-        <v>6798830</v>
+        <v>6798448</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9811,19 +9811,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9850,10 +9840,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126337681</v>
+        <v>126337982</v>
       </c>
       <c r="B91" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9861,21 +9851,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9885,10 +9875,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427092</v>
+        <v>427138</v>
       </c>
       <c r="R91" t="n">
-        <v>6798859</v>
+        <v>6798830</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9918,9 +9908,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9947,45 +9947,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126335896</v>
+        <v>126335099</v>
       </c>
       <c r="B92" t="n">
-        <v>78739</v>
+        <v>98278</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>426993</v>
+        <v>427044</v>
       </c>
       <c r="R92" t="n">
-        <v>6798667</v>
+        <v>6798644</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10015,19 +10015,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10042,22 +10032,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126333986</v>
+        <v>126337681</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10065,21 +10055,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10089,10 +10079,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427095</v>
+        <v>427092</v>
       </c>
       <c r="R93" t="n">
-        <v>6798448</v>
+        <v>6798859</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10151,45 +10141,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126335099</v>
+        <v>126335896</v>
       </c>
       <c r="B94" t="n">
-        <v>98278</v>
+        <v>78739</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427044</v>
+        <v>426993</v>
       </c>
       <c r="R94" t="n">
-        <v>6798644</v>
+        <v>6798667</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10219,9 +10209,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10236,12 +10236,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10773,10 +10773,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126337810</v>
+        <v>126337016</v>
       </c>
       <c r="B100" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10784,34 +10784,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427108</v>
+        <v>427012</v>
       </c>
       <c r="R100" t="n">
-        <v>6798841</v>
+        <v>6798760</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10841,9 +10841,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10858,19 +10868,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126335762</v>
+        <v>126337810</v>
       </c>
       <c r="B101" t="n">
         <v>79598</v>
@@ -10901,17 +10911,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>426996</v>
+        <v>427108</v>
       </c>
       <c r="R101" t="n">
-        <v>6798633</v>
+        <v>6798841</v>
       </c>
       <c r="S101" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10938,19 +10948,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10965,19 +10965,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126336252</v>
+        <v>126335762</v>
       </c>
       <c r="B102" t="n">
         <v>79598</v>
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427008</v>
+        <v>426996</v>
       </c>
       <c r="R102" t="n">
-        <v>6798762</v>
+        <v>6798633</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11045,9 +11045,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11062,19 +11072,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126338799</v>
+        <v>126336252</v>
       </c>
       <c r="B103" t="n">
         <v>79598</v>
@@ -11105,17 +11115,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>426933</v>
+        <v>427008</v>
       </c>
       <c r="R103" t="n">
-        <v>6798926</v>
+        <v>6798762</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11142,19 +11152,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11169,19 +11169,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126337254</v>
+        <v>126338799</v>
       </c>
       <c r="B104" t="n">
         <v>79598</v>
@@ -11212,14 +11212,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427057</v>
+        <v>426933</v>
       </c>
       <c r="R104" t="n">
-        <v>6798827</v>
+        <v>6798926</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11276,22 +11276,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126337016</v>
+        <v>126337254</v>
       </c>
       <c r="B105" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11299,34 +11299,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427012</v>
+        <v>427057</v>
       </c>
       <c r="R105" t="n">
-        <v>6798760</v>
+        <v>6798827</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11383,61 +11383,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126334915</v>
+        <v>126337975</v>
       </c>
       <c r="B106" t="n">
-        <v>98278</v>
+        <v>79598</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427060</v>
+        <v>427138</v>
       </c>
       <c r="R106" t="n">
-        <v>6798614</v>
+        <v>6798830</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11469,7 +11465,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11479,12 +11475,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11493,64 +11484,67 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126337975</v>
+        <v>126334915</v>
       </c>
       <c r="B107" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427138</v>
+        <v>427060</v>
       </c>
       <c r="R107" t="n">
-        <v>6798830</v>
+        <v>6798614</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11582,7 +11576,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11592,7 +11586,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Längs bäcken/fuktrstråket. Området bör ej köras sönder (avverkningsanmälan finns)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11601,18 +11600,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11833,10 +11833,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126337559</v>
+        <v>126338324</v>
       </c>
       <c r="B110" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11844,34 +11844,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427047</v>
+        <v>427072</v>
       </c>
       <c r="R110" t="n">
-        <v>6798896</v>
+        <v>6798879</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11928,22 +11928,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126338324</v>
+        <v>126337286</v>
       </c>
       <c r="B111" t="n">
-        <v>79569</v>
+        <v>78739</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,34 +11951,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427072</v>
+        <v>427056</v>
       </c>
       <c r="R111" t="n">
-        <v>6798879</v>
+        <v>6798834</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12035,19 +12035,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126337286</v>
+        <v>126339588</v>
       </c>
       <c r="B112" t="n">
         <v>78739</v>
@@ -12078,14 +12078,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427056</v>
+        <v>427328</v>
       </c>
       <c r="R112" t="n">
-        <v>6798834</v>
+        <v>6798426</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12142,22 +12142,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126339588</v>
+        <v>126337559</v>
       </c>
       <c r="B113" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12165,21 +12165,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12189,10 +12189,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427328</v>
+        <v>427047</v>
       </c>
       <c r="R113" t="n">
-        <v>6798426</v>
+        <v>6798896</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12261,32 +12261,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126338320</v>
+        <v>126334241</v>
       </c>
       <c r="B114" t="n">
-        <v>79598</v>
+        <v>8447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427072</v>
+        <v>427095</v>
       </c>
       <c r="R114" t="n">
-        <v>6798879</v>
+        <v>6798448</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12329,19 +12329,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>13:44</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12368,45 +12363,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126339405</v>
+        <v>126336022</v>
       </c>
       <c r="B115" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>426855</v>
+        <v>427026</v>
       </c>
       <c r="R115" t="n">
-        <v>6798979</v>
+        <v>6798688</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12438,7 +12433,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12448,7 +12443,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12463,22 +12458,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126334554</v>
+        <v>126338943</v>
       </c>
       <c r="B116" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12486,21 +12481,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12510,13 +12505,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427075</v>
+        <v>427026</v>
       </c>
       <c r="R116" t="n">
-        <v>6798591</v>
+        <v>6798692</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12545,7 +12540,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12555,7 +12550,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12570,22 +12565,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126335754</v>
+        <v>126339857</v>
       </c>
       <c r="B117" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12593,37 +12588,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>426984</v>
+        <v>427004</v>
       </c>
       <c r="R117" t="n">
-        <v>6798652</v>
+        <v>6798987</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12655,7 +12647,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12665,7 +12657,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12674,29 +12666,28 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126334762</v>
+        <v>126338320</v>
       </c>
       <c r="B118" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12704,34 +12695,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>426962</v>
+        <v>427072</v>
       </c>
       <c r="R118" t="n">
-        <v>6798805</v>
+        <v>6798879</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12763,7 +12754,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -12773,12 +12764,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12793,44 +12779,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126334241</v>
+        <v>126339405</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>79598</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12840,10 +12826,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427095</v>
+        <v>426855</v>
       </c>
       <c r="R119" t="n">
-        <v>6798448</v>
+        <v>6798979</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12873,14 +12859,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12907,10 +12898,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126338943</v>
+        <v>126334554</v>
       </c>
       <c r="B120" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12918,21 +12909,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12942,13 +12933,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427026</v>
+        <v>427075</v>
       </c>
       <c r="R120" t="n">
-        <v>6798692</v>
+        <v>6798591</v>
       </c>
       <c r="S120" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12977,7 +12968,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12987,7 +12978,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13002,44 +12993,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126336022</v>
+        <v>126334762</v>
       </c>
       <c r="B121" t="n">
-        <v>98278</v>
+        <v>78980</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13049,10 +13040,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427026</v>
+        <v>426962</v>
       </c>
       <c r="R121" t="n">
-        <v>6798688</v>
+        <v>6798805</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13084,7 +13075,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13094,7 +13085,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13109,22 +13105,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126339857</v>
+        <v>126335754</v>
       </c>
       <c r="B122" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13132,34 +13128,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427004</v>
+        <v>426984</v>
       </c>
       <c r="R122" t="n">
-        <v>6798987</v>
+        <v>6798652</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13191,7 +13190,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13201,7 +13200,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13210,18 +13209,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13733,10 +13733,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126335852</v>
+        <v>126335567</v>
       </c>
       <c r="B128" t="n">
-        <v>57817</v>
+        <v>78739</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13744,42 +13744,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427053</v>
+        <v>427022</v>
       </c>
       <c r="R128" t="n">
-        <v>6798729</v>
+        <v>6798674</v>
       </c>
       <c r="S128" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13806,9 +13801,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13823,22 +13828,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126335567</v>
+        <v>126335594</v>
       </c>
       <c r="B129" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13846,34 +13851,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427022</v>
+        <v>427042</v>
       </c>
       <c r="R129" t="n">
-        <v>6798674</v>
+        <v>6798684</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13903,19 +13908,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13930,22 +13925,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126335594</v>
+        <v>126337688</v>
       </c>
       <c r="B130" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13953,21 +13948,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13977,10 +13972,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427042</v>
+        <v>427092</v>
       </c>
       <c r="R130" t="n">
-        <v>6798684</v>
+        <v>6798859</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14039,10 +14034,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126337688</v>
+        <v>126334548</v>
       </c>
       <c r="B131" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14050,34 +14045,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427092</v>
+        <v>426962</v>
       </c>
       <c r="R131" t="n">
-        <v>6798859</v>
+        <v>6798805</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14107,9 +14102,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14124,22 +14129,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126334548</v>
+        <v>126335852</v>
       </c>
       <c r="B132" t="n">
-        <v>79598</v>
+        <v>57817</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14147,37 +14152,42 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>426962</v>
+        <v>427053</v>
       </c>
       <c r="R132" t="n">
-        <v>6798805</v>
+        <v>6798729</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14204,19 +14214,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14231,22 +14231,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126339616</v>
+        <v>126335603</v>
       </c>
       <c r="B133" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14254,34 +14254,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427329</v>
+        <v>427042</v>
       </c>
       <c r="R133" t="n">
-        <v>6798435</v>
+        <v>6798684</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14311,19 +14311,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>14:50</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14338,22 +14328,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126337227</v>
+        <v>126339616</v>
       </c>
       <c r="B134" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14361,34 +14351,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427067</v>
+        <v>427329</v>
       </c>
       <c r="R134" t="n">
-        <v>6798806</v>
+        <v>6798435</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14418,9 +14408,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14435,12 +14435,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -14661,10 +14661,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126335603</v>
+        <v>126337227</v>
       </c>
       <c r="B137" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14672,21 +14672,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14696,10 +14696,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427042</v>
+        <v>427067</v>
       </c>
       <c r="R137" t="n">
-        <v>6798684</v>
+        <v>6798806</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15487,32 +15487,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126377431</v>
+        <v>126377421</v>
       </c>
       <c r="B145" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15522,10 +15522,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427033</v>
+        <v>427122</v>
       </c>
       <c r="R145" t="n">
-        <v>6798599</v>
+        <v>6798636</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -15558,11 +15558,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15589,32 +15584,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126377421</v>
+        <v>126377431</v>
       </c>
       <c r="B146" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15624,10 +15619,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427122</v>
+        <v>427033</v>
       </c>
       <c r="R146" t="n">
-        <v>6798636</v>
+        <v>6798599</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -15660,6 +15655,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15686,10 +15686,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126377508</v>
+        <v>126377425</v>
       </c>
       <c r="B147" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,21 +15697,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15721,10 +15721,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427079</v>
+        <v>427080</v>
       </c>
       <c r="R147" t="n">
-        <v>6798568</v>
+        <v>6798785</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15783,10 +15783,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126377425</v>
+        <v>126377508</v>
       </c>
       <c r="B148" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15794,21 +15794,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427080</v>
+        <v>427079</v>
       </c>
       <c r="R148" t="n">
-        <v>6798785</v>
+        <v>6798568</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -16074,10 +16074,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126377457</v>
+        <v>126377479</v>
       </c>
       <c r="B151" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16085,21 +16085,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16109,10 +16109,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427145</v>
+        <v>427035</v>
       </c>
       <c r="R151" t="n">
-        <v>6798817</v>
+        <v>6798632</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -16171,10 +16171,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126377479</v>
+        <v>126377457</v>
       </c>
       <c r="B152" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427035</v>
+        <v>427145</v>
       </c>
       <c r="R152" t="n">
-        <v>6798632</v>
+        <v>6798817</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -16559,32 +16559,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126377424</v>
+        <v>126377430</v>
       </c>
       <c r="B156" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16594,10 +16594,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427113</v>
+        <v>427063</v>
       </c>
       <c r="R156" t="n">
-        <v>6798838</v>
+        <v>6798634</v>
       </c>
       <c r="S156" t="n">
         <v>1</v>
@@ -16630,6 +16630,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16656,10 +16661,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126377478</v>
+        <v>126377424</v>
       </c>
       <c r="B157" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16667,21 +16672,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16691,10 +16696,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427122</v>
+        <v>427113</v>
       </c>
       <c r="R157" t="n">
-        <v>6798636</v>
+        <v>6798838</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -16753,10 +16758,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126377427</v>
+        <v>126377478</v>
       </c>
       <c r="B158" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16764,21 +16769,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16788,10 +16793,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427091</v>
+        <v>427122</v>
       </c>
       <c r="R158" t="n">
-        <v>6798545</v>
+        <v>6798636</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -16850,32 +16855,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126377430</v>
+        <v>126377427</v>
       </c>
       <c r="B159" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16885,10 +16890,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427063</v>
+        <v>427091</v>
       </c>
       <c r="R159" t="n">
-        <v>6798634</v>
+        <v>6798545</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16921,11 +16926,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD159" t="b">

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R19" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R20" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022312</v>
+        <v>126022292</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R26" t="n">
-        <v>6798594</v>
+        <v>6798570</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B27" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R27" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -6035,45 +6035,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126340128</v>
+        <v>126338668</v>
       </c>
       <c r="B55" t="n">
-        <v>98278</v>
+        <v>78738</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427631</v>
+        <v>426958</v>
       </c>
       <c r="R55" t="n">
-        <v>6798401</v>
+        <v>6798928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6130,22 +6130,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126338668</v>
+        <v>126335625</v>
       </c>
       <c r="B56" t="n">
-        <v>78738</v>
+        <v>96614</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>426958</v>
+        <v>427079</v>
       </c>
       <c r="R56" t="n">
-        <v>6798928</v>
+        <v>6798569</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6237,22 +6237,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126335625</v>
+        <v>126339407</v>
       </c>
       <c r="B57" t="n">
-        <v>96614</v>
+        <v>78739</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6260,37 +6260,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427079</v>
+        <v>427359</v>
       </c>
       <c r="R57" t="n">
-        <v>6798569</v>
+        <v>6798572</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,19 +6344,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126339407</v>
+        <v>126339573</v>
       </c>
       <c r="B58" t="n">
         <v>78739</v>
@@ -6387,14 +6387,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427359</v>
+        <v>426933</v>
       </c>
       <c r="R58" t="n">
-        <v>6798572</v>
+        <v>6798926</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6451,57 +6451,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126339573</v>
+        <v>126340128</v>
       </c>
       <c r="B59" t="n">
-        <v>78739</v>
+        <v>98278</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>426933</v>
+        <v>427631</v>
       </c>
       <c r="R59" t="n">
-        <v>6798926</v>
+        <v>6798401</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6558,12 +6558,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -11833,10 +11833,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126338324</v>
+        <v>126337559</v>
       </c>
       <c r="B110" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11844,34 +11844,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427072</v>
+        <v>427047</v>
       </c>
       <c r="R110" t="n">
-        <v>6798879</v>
+        <v>6798896</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11928,22 +11928,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126337286</v>
+        <v>126338324</v>
       </c>
       <c r="B111" t="n">
-        <v>78739</v>
+        <v>79569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11951,34 +11951,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427056</v>
+        <v>427072</v>
       </c>
       <c r="R111" t="n">
-        <v>6798834</v>
+        <v>6798879</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12035,19 +12035,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126339588</v>
+        <v>126337286</v>
       </c>
       <c r="B112" t="n">
         <v>78739</v>
@@ -12078,14 +12078,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427328</v>
+        <v>427056</v>
       </c>
       <c r="R112" t="n">
-        <v>6798426</v>
+        <v>6798834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12142,22 +12142,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126337559</v>
+        <v>126339588</v>
       </c>
       <c r="B113" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12165,21 +12165,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12189,10 +12189,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427047</v>
+        <v>427328</v>
       </c>
       <c r="R113" t="n">
-        <v>6798896</v>
+        <v>6798426</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13733,10 +13733,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126335567</v>
+        <v>126335852</v>
       </c>
       <c r="B128" t="n">
-        <v>78739</v>
+        <v>57817</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13744,37 +13744,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427022</v>
+        <v>427053</v>
       </c>
       <c r="R128" t="n">
-        <v>6798674</v>
+        <v>6798729</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13801,19 +13806,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13828,22 +13823,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126335594</v>
+        <v>126335567</v>
       </c>
       <c r="B129" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13851,34 +13846,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427042</v>
+        <v>427022</v>
       </c>
       <c r="R129" t="n">
-        <v>6798684</v>
+        <v>6798674</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13908,9 +13903,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13925,22 +13930,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126337688</v>
+        <v>126335594</v>
       </c>
       <c r="B130" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13948,21 +13953,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13972,10 +13977,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427092</v>
+        <v>427042</v>
       </c>
       <c r="R130" t="n">
-        <v>6798859</v>
+        <v>6798684</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14034,10 +14039,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126334548</v>
+        <v>126337688</v>
       </c>
       <c r="B131" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14045,34 +14050,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>426962</v>
+        <v>427092</v>
       </c>
       <c r="R131" t="n">
-        <v>6798805</v>
+        <v>6798859</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14102,19 +14107,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14129,22 +14124,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126335852</v>
+        <v>126334548</v>
       </c>
       <c r="B132" t="n">
-        <v>57817</v>
+        <v>79598</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14152,42 +14147,37 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427053</v>
+        <v>426962</v>
       </c>
       <c r="R132" t="n">
-        <v>6798729</v>
+        <v>6798805</v>
       </c>
       <c r="S132" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14214,9 +14204,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14231,12 +14231,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -15487,32 +15487,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126377421</v>
+        <v>126377431</v>
       </c>
       <c r="B145" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15522,10 +15522,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427122</v>
+        <v>427033</v>
       </c>
       <c r="R145" t="n">
-        <v>6798636</v>
+        <v>6798599</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -15558,6 +15558,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15584,32 +15589,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126377431</v>
+        <v>126377421</v>
       </c>
       <c r="B146" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15619,10 +15624,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427033</v>
+        <v>427122</v>
       </c>
       <c r="R146" t="n">
-        <v>6798599</v>
+        <v>6798636</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -15655,11 +15660,6 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16074,10 +16074,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126377479</v>
+        <v>126377457</v>
       </c>
       <c r="B151" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16085,21 +16085,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16109,10 +16109,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427035</v>
+        <v>427145</v>
       </c>
       <c r="R151" t="n">
-        <v>6798632</v>
+        <v>6798817</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -16171,10 +16171,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126377457</v>
+        <v>126377479</v>
       </c>
       <c r="B152" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427145</v>
+        <v>427035</v>
       </c>
       <c r="R152" t="n">
-        <v>6798817</v>
+        <v>6798632</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B19" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R19" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B20" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R20" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126340016</v>
+        <v>126340383</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3508,34 +3508,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427570</v>
+        <v>427116</v>
       </c>
       <c r="R31" t="n">
-        <v>6798393</v>
+        <v>6798627</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3592,19 +3592,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126340383</v>
+        <v>126339643</v>
       </c>
       <c r="B32" t="n">
         <v>79569</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427116</v>
+        <v>426885</v>
       </c>
       <c r="R32" t="n">
-        <v>6798627</v>
+        <v>6799018</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126339643</v>
+        <v>126340016</v>
       </c>
       <c r="B33" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3722,34 +3722,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>426885</v>
+        <v>427570</v>
       </c>
       <c r="R33" t="n">
-        <v>6799018</v>
+        <v>6798393</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3806,12 +3806,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126337222</v>
+        <v>126339860</v>
       </c>
       <c r="B39" t="n">
-        <v>79569</v>
+        <v>79598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427067</v>
+        <v>427301</v>
       </c>
       <c r="R39" t="n">
-        <v>6798806</v>
+        <v>6798343</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4411,9 +4411,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4428,22 +4438,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126336106</v>
+        <v>126334237</v>
       </c>
       <c r="B40" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4451,37 +4461,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>426970</v>
+        <v>427084</v>
       </c>
       <c r="R40" t="n">
-        <v>6798728</v>
+        <v>6798524</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4510,7 +4520,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4520,7 +4530,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4535,12 +4545,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4654,10 +4664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126339860</v>
+        <v>126337222</v>
       </c>
       <c r="B42" t="n">
-        <v>79598</v>
+        <v>79569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4665,34 +4675,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427301</v>
+        <v>427067</v>
       </c>
       <c r="R42" t="n">
-        <v>6798343</v>
+        <v>6798806</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4722,19 +4732,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4749,22 +4749,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126334237</v>
+        <v>126336106</v>
       </c>
       <c r="B43" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4772,37 +4772,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427084</v>
+        <v>426970</v>
       </c>
       <c r="R43" t="n">
-        <v>6798524</v>
+        <v>6798728</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4856,12 +4856,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126334541</v>
+        <v>126337209</v>
       </c>
       <c r="B47" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5200,21 +5200,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5224,13 +5224,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>426962</v>
+        <v>427026</v>
       </c>
       <c r="R47" t="n">
-        <v>6798805</v>
+        <v>6798692</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5284,22 +5284,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126337209</v>
+        <v>126334857</v>
       </c>
       <c r="B48" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5331,13 +5331,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427026</v>
+        <v>427060</v>
       </c>
       <c r="R48" t="n">
-        <v>6798692</v>
+        <v>6798612</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5391,22 +5391,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126334857</v>
+        <v>126334541</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5414,21 +5414,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427060</v>
+        <v>426962</v>
       </c>
       <c r="R49" t="n">
-        <v>6798612</v>
+        <v>6798805</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5498,22 +5498,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126339364</v>
+        <v>126340584</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>78738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,39 +5521,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427073</v>
+        <v>427242</v>
       </c>
       <c r="R50" t="n">
-        <v>6798822</v>
+        <v>6798350</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5583,9 +5578,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5600,22 +5605,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126339028</v>
+        <v>126336092</v>
       </c>
       <c r="B51" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5623,37 +5628,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427113</v>
+        <v>427026</v>
       </c>
       <c r="R51" t="n">
-        <v>6798674</v>
+        <v>6798692</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5682,7 +5687,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5692,7 +5697,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5707,22 +5712,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126340584</v>
+        <v>126335481</v>
       </c>
       <c r="B52" t="n">
-        <v>78738</v>
+        <v>57657</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,34 +5735,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427242</v>
+        <v>427042</v>
       </c>
       <c r="R52" t="n">
-        <v>6798350</v>
+        <v>6798684</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5787,19 +5797,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5814,22 +5814,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126336092</v>
+        <v>126339364</v>
       </c>
       <c r="B53" t="n">
-        <v>78738</v>
+        <v>57654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,37 +5837,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427026</v>
+        <v>427073</v>
       </c>
       <c r="R53" t="n">
-        <v>6798692</v>
+        <v>6798822</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5894,19 +5899,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5921,22 +5916,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126335481</v>
+        <v>126339028</v>
       </c>
       <c r="B54" t="n">
-        <v>57657</v>
+        <v>78739</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5944,42 +5939,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427042</v>
+        <v>427113</v>
       </c>
       <c r="R54" t="n">
-        <v>6798684</v>
+        <v>6798674</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6006,9 +5996,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6023,57 +6023,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126338668</v>
+        <v>126340128</v>
       </c>
       <c r="B55" t="n">
-        <v>78738</v>
+        <v>98278</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>426958</v>
+        <v>427631</v>
       </c>
       <c r="R55" t="n">
-        <v>6798928</v>
+        <v>6798401</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6130,22 +6130,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126335625</v>
+        <v>126338668</v>
       </c>
       <c r="B56" t="n">
-        <v>96614</v>
+        <v>78738</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6153,21 +6153,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427079</v>
+        <v>426958</v>
       </c>
       <c r="R56" t="n">
-        <v>6798569</v>
+        <v>6798928</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6237,22 +6237,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126339407</v>
+        <v>126335625</v>
       </c>
       <c r="B57" t="n">
-        <v>78739</v>
+        <v>96614</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6260,37 +6260,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427359</v>
+        <v>427079</v>
       </c>
       <c r="R57" t="n">
-        <v>6798572</v>
+        <v>6798569</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6344,19 +6344,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126339573</v>
+        <v>126339407</v>
       </c>
       <c r="B58" t="n">
         <v>78739</v>
@@ -6387,14 +6387,14 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>426933</v>
+        <v>427359</v>
       </c>
       <c r="R58" t="n">
-        <v>6798926</v>
+        <v>6798572</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6451,57 +6451,57 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126340128</v>
+        <v>126339573</v>
       </c>
       <c r="B59" t="n">
-        <v>98278</v>
+        <v>78739</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427631</v>
+        <v>426933</v>
       </c>
       <c r="R59" t="n">
-        <v>6798401</v>
+        <v>6798926</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6558,12 +6558,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7522,10 +7522,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126338801</v>
+        <v>126339529</v>
       </c>
       <c r="B69" t="n">
-        <v>78738</v>
+        <v>79075</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,37 +7533,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>426933</v>
+        <v>427360</v>
       </c>
       <c r="R69" t="n">
-        <v>6798926</v>
+        <v>6798574</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7590,19 +7590,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7617,22 +7607,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126340365</v>
+        <v>126338801</v>
       </c>
       <c r="B70" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7640,21 +7630,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7664,10 +7654,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427116</v>
+        <v>426933</v>
       </c>
       <c r="R70" t="n">
-        <v>6798627</v>
+        <v>6798926</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7736,7 +7726,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126336082</v>
+        <v>126340365</v>
       </c>
       <c r="B71" t="n">
         <v>79598</v>
@@ -7767,17 +7757,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>426993</v>
+        <v>427116</v>
       </c>
       <c r="R71" t="n">
-        <v>6798667</v>
+        <v>6798627</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7806,7 +7796,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7816,7 +7806,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7831,19 +7821,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126339773</v>
+        <v>126336082</v>
       </c>
       <c r="B72" t="n">
         <v>79598</v>
@@ -7878,13 +7868,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426959</v>
+        <v>426993</v>
       </c>
       <c r="R72" t="n">
-        <v>6798956</v>
+        <v>6798667</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7913,7 +7903,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7923,7 +7913,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7938,19 +7928,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126334052</v>
+        <v>126339773</v>
       </c>
       <c r="B73" t="n">
         <v>79598</v>
@@ -7985,10 +7975,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427079</v>
+        <v>426959</v>
       </c>
       <c r="R73" t="n">
-        <v>6798512</v>
+        <v>6798956</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8020,7 +8010,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8030,7 +8020,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8045,22 +8035,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126339757</v>
+        <v>126334052</v>
       </c>
       <c r="B74" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8068,34 +8058,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>426981</v>
+        <v>427079</v>
       </c>
       <c r="R74" t="n">
-        <v>6798995</v>
+        <v>6798512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8127,7 +8117,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8137,7 +8127,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8152,22 +8142,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126335972</v>
+        <v>126339757</v>
       </c>
       <c r="B75" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8175,34 +8165,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426988</v>
+        <v>426981</v>
       </c>
       <c r="R75" t="n">
-        <v>6798730</v>
+        <v>6798995</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8234,7 +8224,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8244,7 +8234,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8259,22 +8249,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126339529</v>
+        <v>126335972</v>
       </c>
       <c r="B76" t="n">
-        <v>79075</v>
+        <v>79598</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8282,37 +8272,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427360</v>
+        <v>426988</v>
       </c>
       <c r="R76" t="n">
-        <v>6798574</v>
+        <v>6798730</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8339,9 +8329,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8356,12 +8356,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -12261,48 +12261,48 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126334241</v>
+        <v>126338943</v>
       </c>
       <c r="B114" t="n">
-        <v>8447</v>
+        <v>78739</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427095</v>
+        <v>427026</v>
       </c>
       <c r="R114" t="n">
-        <v>6798448</v>
+        <v>6798692</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12329,14 +12329,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12351,57 +12356,57 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126336022</v>
+        <v>126339857</v>
       </c>
       <c r="B115" t="n">
-        <v>98278</v>
+        <v>78739</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427026</v>
+        <v>427004</v>
       </c>
       <c r="R115" t="n">
-        <v>6798688</v>
+        <v>6798987</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12433,7 +12438,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12443,7 +12448,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12458,60 +12463,60 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126338943</v>
+        <v>126334241</v>
       </c>
       <c r="B116" t="n">
-        <v>78739</v>
+        <v>8447</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427026</v>
+        <v>427095</v>
       </c>
       <c r="R116" t="n">
-        <v>6798692</v>
+        <v>6798448</v>
       </c>
       <c r="S116" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12538,19 +12543,14 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:25</t>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Hackhål på högstubbe, spår efter Mindre Märgborre</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12565,22 +12565,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126339857</v>
+        <v>126338320</v>
       </c>
       <c r="B117" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12588,21 +12588,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427004</v>
+        <v>427072</v>
       </c>
       <c r="R117" t="n">
-        <v>6798987</v>
+        <v>6798879</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12684,7 +12684,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126338320</v>
+        <v>126339405</v>
       </c>
       <c r="B118" t="n">
         <v>79598</v>
@@ -12719,10 +12719,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427072</v>
+        <v>426855</v>
       </c>
       <c r="R118" t="n">
-        <v>6798879</v>
+        <v>6798979</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12791,7 +12791,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126339405</v>
+        <v>126334554</v>
       </c>
       <c r="B119" t="n">
         <v>79598</v>
@@ -12822,14 +12822,14 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>426855</v>
+        <v>427075</v>
       </c>
       <c r="R119" t="n">
-        <v>6798979</v>
+        <v>6798591</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12886,22 +12886,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126334554</v>
+        <v>126334762</v>
       </c>
       <c r="B120" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427075</v>
+        <v>426962</v>
       </c>
       <c r="R120" t="n">
-        <v>6798591</v>
+        <v>6798805</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -12978,7 +12978,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Inom en radie 50 m</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12993,22 +12998,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126334762</v>
+        <v>126335754</v>
       </c>
       <c r="B121" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13016,34 +13021,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>426962</v>
+        <v>426984</v>
       </c>
       <c r="R121" t="n">
-        <v>6798805</v>
+        <v>6798652</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13075,7 +13083,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13085,12 +13093,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Inom en radie 50 m</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13099,66 +13102,64 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126335754</v>
+        <v>126336022</v>
       </c>
       <c r="B122" t="n">
-        <v>79598</v>
+        <v>98278</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>426984</v>
+        <v>427026</v>
       </c>
       <c r="R122" t="n">
-        <v>6798652</v>
+        <v>6798688</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13190,7 +13191,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13200,7 +13201,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13209,7 +13210,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13228,10 +13228,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126335998</v>
+        <v>126335613</v>
       </c>
       <c r="B123" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13239,21 +13239,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427015</v>
+        <v>427042</v>
       </c>
       <c r="R123" t="n">
-        <v>6798754</v>
+        <v>6798684</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13325,10 +13325,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126335881</v>
+        <v>126338823</v>
       </c>
       <c r="B124" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13336,34 +13336,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426993</v>
+        <v>426933</v>
       </c>
       <c r="R124" t="n">
-        <v>6798667</v>
+        <v>6798926</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13420,22 +13420,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126339770</v>
+        <v>126335998</v>
       </c>
       <c r="B125" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13443,37 +13443,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427450</v>
+        <v>427015</v>
       </c>
       <c r="R125" t="n">
-        <v>6798525</v>
+        <v>6798754</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13517,22 +13517,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126335613</v>
+        <v>126335881</v>
       </c>
       <c r="B126" t="n">
-        <v>78739</v>
+        <v>78738</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13540,34 +13540,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427042</v>
+        <v>426993</v>
       </c>
       <c r="R126" t="n">
-        <v>6798684</v>
+        <v>6798667</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13597,9 +13597,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13614,22 +13624,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126338823</v>
+        <v>126339770</v>
       </c>
       <c r="B127" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13637,37 +13647,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>426933</v>
+        <v>427450</v>
       </c>
       <c r="R127" t="n">
-        <v>6798926</v>
+        <v>6798525</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13694,19 +13704,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13721,12 +13721,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -15686,10 +15686,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126377425</v>
+        <v>126377459</v>
       </c>
       <c r="B147" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,21 +15697,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15721,10 +15721,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427080</v>
+        <v>427033</v>
       </c>
       <c r="R147" t="n">
-        <v>6798785</v>
+        <v>6798631</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15783,10 +15783,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126377508</v>
+        <v>126377458</v>
       </c>
       <c r="B148" t="n">
-        <v>78980</v>
+        <v>78739</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15794,21 +15794,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15818,10 +15818,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427079</v>
+        <v>427105</v>
       </c>
       <c r="R148" t="n">
-        <v>6798568</v>
+        <v>6798838</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15880,10 +15880,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126377459</v>
+        <v>126377425</v>
       </c>
       <c r="B149" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15891,21 +15891,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427033</v>
+        <v>427080</v>
       </c>
       <c r="R149" t="n">
-        <v>6798631</v>
+        <v>6798785</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15977,10 +15977,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126377458</v>
+        <v>126377508</v>
       </c>
       <c r="B150" t="n">
-        <v>78739</v>
+        <v>78980</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15988,21 +15988,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16012,10 +16012,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427105</v>
+        <v>427079</v>
       </c>
       <c r="R150" t="n">
-        <v>6798838</v>
+        <v>6798568</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -2333,10 +2333,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126022311</v>
+        <v>126022320</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>78647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,10 +2368,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426970</v>
+        <v>426905</v>
       </c>
       <c r="R19" t="n">
-        <v>6798599</v>
+        <v>6798570</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2430,10 +2430,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126022320</v>
+        <v>126022311</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>78739</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2441,21 +2441,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426905</v>
+        <v>426970</v>
       </c>
       <c r="R20" t="n">
-        <v>6798570</v>
+        <v>6798599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126022292</v>
+        <v>126022312</v>
       </c>
       <c r="B26" t="n">
-        <v>79598</v>
+        <v>78739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426906</v>
+        <v>426982</v>
       </c>
       <c r="R26" t="n">
-        <v>6798570</v>
+        <v>6798594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,10 +3109,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126022312</v>
+        <v>126022292</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3120,21 +3120,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426982</v>
+        <v>426906</v>
       </c>
       <c r="R27" t="n">
-        <v>6798594</v>
+        <v>6798570</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126340584</v>
+        <v>126339364</v>
       </c>
       <c r="B50" t="n">
-        <v>78738</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5521,34 +5521,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427242</v>
+        <v>427073</v>
       </c>
       <c r="R50" t="n">
-        <v>6798350</v>
+        <v>6798822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5578,19 +5583,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5605,22 +5600,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126336092</v>
+        <v>126339028</v>
       </c>
       <c r="B51" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5628,37 +5623,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427026</v>
+        <v>427113</v>
       </c>
       <c r="R51" t="n">
-        <v>6798692</v>
+        <v>6798674</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5687,7 +5682,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5697,7 +5692,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5712,22 +5707,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126335481</v>
+        <v>126340584</v>
       </c>
       <c r="B52" t="n">
-        <v>57657</v>
+        <v>78738</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5735,39 +5730,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427042</v>
+        <v>427242</v>
       </c>
       <c r="R52" t="n">
-        <v>6798684</v>
+        <v>6798350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5797,9 +5787,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5814,22 +5814,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126339364</v>
+        <v>126336092</v>
       </c>
       <c r="B53" t="n">
-        <v>57654</v>
+        <v>78738</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,42 +5837,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427073</v>
+        <v>427026</v>
       </c>
       <c r="R53" t="n">
-        <v>6798822</v>
+        <v>6798692</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5899,9 +5894,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5916,22 +5921,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126339028</v>
+        <v>126335481</v>
       </c>
       <c r="B54" t="n">
-        <v>78739</v>
+        <v>57657</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5939,37 +5944,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427113</v>
+        <v>427042</v>
       </c>
       <c r="R54" t="n">
-        <v>6798674</v>
+        <v>6798684</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5996,19 +6006,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6023,12 +6023,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7522,10 +7522,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126339529</v>
+        <v>126338801</v>
       </c>
       <c r="B69" t="n">
-        <v>79075</v>
+        <v>78738</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,37 +7533,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>967</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427360</v>
+        <v>426933</v>
       </c>
       <c r="R69" t="n">
-        <v>6798574</v>
+        <v>6798926</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7590,9 +7590,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7607,22 +7617,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126338801</v>
+        <v>126340365</v>
       </c>
       <c r="B70" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7630,21 +7640,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7654,10 +7664,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>426933</v>
+        <v>427116</v>
       </c>
       <c r="R70" t="n">
-        <v>6798926</v>
+        <v>6798627</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7726,7 +7736,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126340365</v>
+        <v>126336082</v>
       </c>
       <c r="B71" t="n">
         <v>79598</v>
@@ -7757,17 +7767,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427116</v>
+        <v>426993</v>
       </c>
       <c r="R71" t="n">
-        <v>6798627</v>
+        <v>6798667</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7796,7 +7806,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7806,7 +7816,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7821,19 +7831,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126336082</v>
+        <v>126339773</v>
       </c>
       <c r="B72" t="n">
         <v>79598</v>
@@ -7868,13 +7878,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>426993</v>
+        <v>426959</v>
       </c>
       <c r="R72" t="n">
-        <v>6798667</v>
+        <v>6798956</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7903,7 +7913,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -7913,7 +7923,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7928,19 +7938,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126339773</v>
+        <v>126334052</v>
       </c>
       <c r="B73" t="n">
         <v>79598</v>
@@ -7975,10 +7985,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>426959</v>
+        <v>427079</v>
       </c>
       <c r="R73" t="n">
-        <v>6798956</v>
+        <v>6798512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8010,7 +8020,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8020,7 +8030,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8035,22 +8045,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126334052</v>
+        <v>126339757</v>
       </c>
       <c r="B74" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8058,34 +8068,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427079</v>
+        <v>426981</v>
       </c>
       <c r="R74" t="n">
-        <v>6798512</v>
+        <v>6798995</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8117,7 +8127,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8127,7 +8137,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8142,22 +8152,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126339757</v>
+        <v>126335972</v>
       </c>
       <c r="B75" t="n">
-        <v>78738</v>
+        <v>79598</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8165,34 +8175,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>426981</v>
+        <v>426988</v>
       </c>
       <c r="R75" t="n">
-        <v>6798995</v>
+        <v>6798730</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8224,7 +8234,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8234,7 +8244,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8249,22 +8259,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126335972</v>
+        <v>126339529</v>
       </c>
       <c r="B76" t="n">
-        <v>79598</v>
+        <v>79075</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8272,37 +8282,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>426988</v>
+        <v>427360</v>
       </c>
       <c r="R76" t="n">
-        <v>6798730</v>
+        <v>6798574</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8329,19 +8339,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8356,12 +8356,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -13228,10 +13228,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126335613</v>
+        <v>126335998</v>
       </c>
       <c r="B123" t="n">
-        <v>78739</v>
+        <v>79598</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13239,21 +13239,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427042</v>
+        <v>427015</v>
       </c>
       <c r="R123" t="n">
-        <v>6798684</v>
+        <v>6798754</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13325,10 +13325,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126338823</v>
+        <v>126335881</v>
       </c>
       <c r="B124" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13336,34 +13336,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>426933</v>
+        <v>426993</v>
       </c>
       <c r="R124" t="n">
-        <v>6798926</v>
+        <v>6798667</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13420,22 +13420,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126335998</v>
+        <v>126339770</v>
       </c>
       <c r="B125" t="n">
-        <v>79598</v>
+        <v>78738</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13443,37 +13443,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Gryvlan, Gryvlan, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427015</v>
+        <v>427450</v>
       </c>
       <c r="R125" t="n">
-        <v>6798754</v>
+        <v>6798525</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13517,22 +13517,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126335881</v>
+        <v>126335613</v>
       </c>
       <c r="B126" t="n">
-        <v>78738</v>
+        <v>78739</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13540,34 +13540,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>426993</v>
+        <v>427042</v>
       </c>
       <c r="R126" t="n">
-        <v>6798667</v>
+        <v>6798684</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13597,19 +13597,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13624,22 +13614,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126339770</v>
+        <v>126338823</v>
       </c>
       <c r="B127" t="n">
-        <v>78738</v>
+        <v>79569</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13647,37 +13637,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gryvlan, Gryvlan, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427450</v>
+        <v>426933</v>
       </c>
       <c r="R127" t="n">
-        <v>6798525</v>
+        <v>6798926</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13704,9 +13694,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13721,12 +13721,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -14243,10 +14243,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126335603</v>
+        <v>126339616</v>
       </c>
       <c r="B133" t="n">
-        <v>79569</v>
+        <v>78738</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14254,34 +14254,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427042</v>
+        <v>427329</v>
       </c>
       <c r="R133" t="n">
-        <v>6798684</v>
+        <v>6798435</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14311,9 +14311,19 @@
           <t>2025-07-01</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14328,22 +14338,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126339616</v>
+        <v>126334764</v>
       </c>
       <c r="B134" t="n">
-        <v>78738</v>
+        <v>78980</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14351,21 +14361,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14375,10 +14385,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427329</v>
+        <v>427055</v>
       </c>
       <c r="R134" t="n">
-        <v>6798435</v>
+        <v>6798616</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14410,7 +14420,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14420,7 +14430,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14447,7 +14457,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126334764</v>
+        <v>126340434</v>
       </c>
       <c r="B135" t="n">
         <v>78980</v>
@@ -14482,10 +14492,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427055</v>
+        <v>427486</v>
       </c>
       <c r="R135" t="n">
-        <v>6798616</v>
+        <v>6798404</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14517,7 +14527,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14527,7 +14537,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14554,10 +14564,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126340434</v>
+        <v>126337227</v>
       </c>
       <c r="B136" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14565,34 +14575,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+          <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427486</v>
+        <v>427067</v>
       </c>
       <c r="R136" t="n">
-        <v>6798404</v>
+        <v>6798806</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14622,19 +14632,9 @@
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>15:31</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14649,22 +14649,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126337227</v>
+        <v>126335337</v>
       </c>
       <c r="B137" t="n">
-        <v>79598</v>
+        <v>58138</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14672,37 +14672,42 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>103018</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427067</v>
+        <v>427023</v>
       </c>
       <c r="R137" t="n">
-        <v>6798806</v>
+        <v>6798652</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14758,10 +14763,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126335337</v>
+        <v>126335603</v>
       </c>
       <c r="B138" t="n">
-        <v>58138</v>
+        <v>79569</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14769,42 +14774,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103018</v>
+        <v>229821</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Mjölkbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427023</v>
+        <v>427042</v>
       </c>
       <c r="R138" t="n">
-        <v>6798652</v>
+        <v>6798684</v>
       </c>
       <c r="S138" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15487,32 +15487,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126377431</v>
+        <v>126377421</v>
       </c>
       <c r="B145" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15522,10 +15522,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427033</v>
+        <v>427122</v>
       </c>
       <c r="R145" t="n">
-        <v>6798599</v>
+        <v>6798636</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -15558,11 +15558,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15589,32 +15584,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126377421</v>
+        <v>126377431</v>
       </c>
       <c r="B146" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15624,10 +15619,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427122</v>
+        <v>427033</v>
       </c>
       <c r="R146" t="n">
-        <v>6798636</v>
+        <v>6798599</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -15660,6 +15655,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD146" t="b">

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY162"/>
+  <dimension ref="A1:AY163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17052,7 +17052,7 @@
         <v>126338143</v>
       </c>
       <c r="B161" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>126339359</v>
       </c>
       <c r="B162" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17260,6 +17260,113 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>126334320</v>
+      </c>
+      <c r="B163" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Mjölkbäcken, Mjölkbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>427078</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6798541</v>
+      </c>
+      <c r="S163" t="n">
+        <v>15</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -17052,7 +17052,7 @@
         <v>126338143</v>
       </c>
       <c r="B161" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>126339359</v>
       </c>
       <c r="B162" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>126334320</v>
       </c>
       <c r="B163" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>

--- a/artfynd/A 26140-2025 artfynd.xlsx
+++ b/artfynd/A 26140-2025 artfynd.xlsx
@@ -17052,7 +17052,7 @@
         <v>126338143</v>
       </c>
       <c r="B161" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>126339359</v>
       </c>
       <c r="B162" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>126334320</v>
       </c>
       <c r="B163" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
